--- a/TMVA/FOM_small.xlsx
+++ b/TMVA/FOM_small.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\purol\OneDrive\바탕 화면\github\Belle2_script\TMVA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BE06370-89E6-419A-A839-51B380C1A024}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20A9AE22-58EC-40F9-A32C-A4CEAA3DB55F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -349,1242 +349,1242 @@
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A1">
-        <v>0.83297900000000002</v>
+        <v>0.823268</v>
       </c>
       <c r="B1">
-        <v>0.83725799999999995</v>
+        <v>0.82479000000000002</v>
       </c>
       <c r="C1">
-        <v>0.84330700000000003</v>
+        <v>0.82944200000000001</v>
       </c>
       <c r="D1">
-        <v>0.84710200000000002</v>
+        <v>0.82950900000000005</v>
       </c>
       <c r="E1">
-        <v>0.84910600000000003</v>
+        <v>0.83832399999999996</v>
       </c>
       <c r="F1">
-        <v>0.85445300000000002</v>
+        <v>0.84323099999999995</v>
       </c>
       <c r="G1">
-        <v>0.85428599999999999</v>
+        <v>0.84924299999999997</v>
       </c>
       <c r="H1">
-        <v>0.85632699999999995</v>
+        <v>0.850796</v>
       </c>
       <c r="I1">
-        <v>0.85537799999999997</v>
+        <v>0.85426899999999995</v>
       </c>
       <c r="J1">
-        <v>0.85674899999999998</v>
+        <v>0.85575100000000004</v>
       </c>
       <c r="K1">
-        <v>0.86172899999999997</v>
+        <v>0.86499000000000004</v>
       </c>
       <c r="L1">
-        <v>0.86741800000000002</v>
+        <v>0.87121300000000002</v>
       </c>
       <c r="M1">
-        <v>0.87132299999999996</v>
+        <v>0.87645399999999996</v>
       </c>
       <c r="N1">
-        <v>0.87978299999999998</v>
+        <v>0.88135600000000003</v>
       </c>
       <c r="O1">
-        <v>0.88140300000000005</v>
+        <v>0.88877600000000001</v>
       </c>
       <c r="P1">
-        <v>0.89596299999999995</v>
+        <v>0.89078800000000002</v>
       </c>
       <c r="Q1">
-        <v>0.89958899999999997</v>
+        <v>0.90229499999999996</v>
       </c>
       <c r="R1">
-        <v>0.88675000000000004</v>
+        <v>0.91644899999999996</v>
       </c>
       <c r="S1">
-        <v>0.89656199999999997</v>
+        <v>0.906412</v>
       </c>
       <c r="T1">
-        <v>0.90540600000000004</v>
+        <v>0.89570899999999998</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A2">
-        <v>0.82872800000000002</v>
+        <v>0.82362100000000005</v>
       </c>
       <c r="B2">
-        <v>0.83295300000000005</v>
+        <v>0.82367800000000002</v>
       </c>
       <c r="C2">
-        <v>0.83924900000000002</v>
+        <v>0.82878099999999999</v>
       </c>
       <c r="D2">
-        <v>0.84341200000000005</v>
+        <v>0.82845999999999997</v>
       </c>
       <c r="E2">
-        <v>0.84591700000000003</v>
+        <v>0.83765999999999996</v>
       </c>
       <c r="F2">
-        <v>0.85168900000000003</v>
+        <v>0.84193799999999996</v>
       </c>
       <c r="G2">
-        <v>0.85261399999999998</v>
+        <v>0.84792000000000001</v>
       </c>
       <c r="H2">
-        <v>0.85523099999999996</v>
+        <v>0.84871099999999999</v>
       </c>
       <c r="I2">
-        <v>0.85511000000000004</v>
+        <v>0.85295900000000002</v>
       </c>
       <c r="J2">
-        <v>0.85680500000000004</v>
+        <v>0.85411700000000002</v>
       </c>
       <c r="K2">
-        <v>0.86144900000000002</v>
+        <v>0.86377700000000002</v>
       </c>
       <c r="L2">
-        <v>0.86775599999999997</v>
+        <v>0.86916700000000002</v>
       </c>
       <c r="M2">
-        <v>0.87262399999999996</v>
+        <v>0.87284499999999998</v>
       </c>
       <c r="N2">
-        <v>0.88226599999999999</v>
+        <v>0.878722</v>
       </c>
       <c r="O2">
-        <v>0.88480599999999998</v>
+        <v>0.88741599999999998</v>
       </c>
       <c r="P2">
-        <v>0.89884900000000001</v>
+        <v>0.89037100000000002</v>
       </c>
       <c r="Q2">
-        <v>0.90284699999999996</v>
+        <v>0.90000899999999995</v>
       </c>
       <c r="R2">
-        <v>0.89004899999999998</v>
+        <v>0.91592799999999996</v>
       </c>
       <c r="S2">
-        <v>0.89814799999999995</v>
+        <v>0.90503699999999998</v>
       </c>
       <c r="T2">
-        <v>0.90856999999999999</v>
+        <v>0.89387899999999998</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A3">
-        <v>0.83615300000000004</v>
+        <v>0.82824399999999998</v>
       </c>
       <c r="B3">
-        <v>0.84106300000000001</v>
+        <v>0.82846699999999995</v>
       </c>
       <c r="C3">
-        <v>0.84800200000000003</v>
+        <v>0.83395699999999995</v>
       </c>
       <c r="D3">
-        <v>0.85288900000000001</v>
+        <v>0.83410399999999996</v>
       </c>
       <c r="E3">
-        <v>0.85498799999999997</v>
+        <v>0.84296599999999999</v>
       </c>
       <c r="F3">
-        <v>0.86106400000000005</v>
+        <v>0.84836800000000001</v>
       </c>
       <c r="G3">
-        <v>0.861097</v>
+        <v>0.85507200000000005</v>
       </c>
       <c r="H3">
-        <v>0.86357600000000001</v>
+        <v>0.85665400000000003</v>
       </c>
       <c r="I3">
-        <v>0.86299099999999995</v>
+        <v>0.86185</v>
       </c>
       <c r="J3">
-        <v>0.86435799999999996</v>
+        <v>0.86288799999999999</v>
       </c>
       <c r="K3">
-        <v>0.87040600000000001</v>
+        <v>0.87186799999999998</v>
       </c>
       <c r="L3">
-        <v>0.87695299999999998</v>
+        <v>0.87719199999999997</v>
       </c>
       <c r="M3">
-        <v>0.88089499999999998</v>
+        <v>0.87987099999999996</v>
       </c>
       <c r="N3">
-        <v>0.890351</v>
+        <v>0.88709300000000002</v>
       </c>
       <c r="O3">
-        <v>0.89252500000000001</v>
+        <v>0.89728699999999995</v>
       </c>
       <c r="P3">
-        <v>0.90442400000000001</v>
+        <v>0.90017100000000005</v>
       </c>
       <c r="Q3">
-        <v>0.90878199999999998</v>
+        <v>0.91038300000000005</v>
       </c>
       <c r="R3">
-        <v>0.89758000000000004</v>
+        <v>0.92667699999999997</v>
       </c>
       <c r="S3">
-        <v>0.90581299999999998</v>
+        <v>0.91903299999999999</v>
       </c>
       <c r="T3">
-        <v>0.91691699999999998</v>
+        <v>0.89985599999999999</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A4">
-        <v>0.84000600000000003</v>
+        <v>0.83932300000000004</v>
       </c>
       <c r="B4">
-        <v>0.84481899999999999</v>
+        <v>0.84013400000000005</v>
       </c>
       <c r="C4">
-        <v>0.85184300000000002</v>
+        <v>0.84545599999999999</v>
       </c>
       <c r="D4">
-        <v>0.85725099999999999</v>
+        <v>0.84606700000000001</v>
       </c>
       <c r="E4">
-        <v>0.85994400000000004</v>
+        <v>0.85518000000000005</v>
       </c>
       <c r="F4">
-        <v>0.86504000000000003</v>
+        <v>0.85973999999999995</v>
       </c>
       <c r="G4">
-        <v>0.86382800000000004</v>
+        <v>0.86765199999999998</v>
       </c>
       <c r="H4">
-        <v>0.86677199999999999</v>
+        <v>0.86878500000000003</v>
       </c>
       <c r="I4">
-        <v>0.867309</v>
+        <v>0.87350000000000005</v>
       </c>
       <c r="J4">
-        <v>0.86854399999999998</v>
+        <v>0.87268199999999996</v>
       </c>
       <c r="K4">
-        <v>0.87526899999999996</v>
+        <v>0.88109400000000004</v>
       </c>
       <c r="L4">
-        <v>0.88279099999999999</v>
+        <v>0.88654999999999995</v>
       </c>
       <c r="M4">
-        <v>0.88557799999999998</v>
+        <v>0.88920500000000002</v>
       </c>
       <c r="N4">
-        <v>0.89307499999999995</v>
+        <v>0.89274200000000004</v>
       </c>
       <c r="O4">
-        <v>0.89512000000000003</v>
+        <v>0.90286200000000005</v>
       </c>
       <c r="P4">
-        <v>0.90903999999999996</v>
+        <v>0.90552500000000002</v>
       </c>
       <c r="Q4">
-        <v>0.91173599999999999</v>
+        <v>0.916543</v>
       </c>
       <c r="R4">
-        <v>0.89926200000000001</v>
+        <v>0.93412200000000001</v>
       </c>
       <c r="S4">
-        <v>0.90652200000000005</v>
+        <v>0.92749599999999999</v>
       </c>
       <c r="T4">
-        <v>0.91902799999999996</v>
+        <v>0.90778400000000004</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A5">
-        <v>0.85062800000000005</v>
+        <v>0.849719</v>
       </c>
       <c r="B5">
-        <v>0.856182</v>
+        <v>0.85102900000000004</v>
       </c>
       <c r="C5">
-        <v>0.86352600000000002</v>
+        <v>0.85690999999999995</v>
       </c>
       <c r="D5">
-        <v>0.869753</v>
+        <v>0.85728700000000002</v>
       </c>
       <c r="E5">
-        <v>0.87254100000000001</v>
+        <v>0.86536999999999997</v>
       </c>
       <c r="F5">
-        <v>0.87846199999999997</v>
+        <v>0.86986300000000005</v>
       </c>
       <c r="G5">
-        <v>0.87695299999999998</v>
+        <v>0.87789600000000001</v>
       </c>
       <c r="H5">
-        <v>0.87892899999999996</v>
+        <v>0.87895100000000004</v>
       </c>
       <c r="I5">
-        <v>0.88085000000000002</v>
+        <v>0.88391799999999998</v>
       </c>
       <c r="J5">
-        <v>0.88291900000000001</v>
+        <v>0.88239199999999995</v>
       </c>
       <c r="K5">
-        <v>0.88891799999999999</v>
+        <v>0.89133799999999996</v>
       </c>
       <c r="L5">
-        <v>0.89688400000000001</v>
+        <v>0.89716700000000005</v>
       </c>
       <c r="M5">
-        <v>0.89925500000000003</v>
+        <v>0.89984200000000003</v>
       </c>
       <c r="N5">
-        <v>0.90720999999999996</v>
+        <v>0.90336300000000003</v>
       </c>
       <c r="O5">
-        <v>0.90953799999999996</v>
+        <v>0.91545299999999996</v>
       </c>
       <c r="P5">
-        <v>0.92517799999999994</v>
+        <v>0.91893499999999995</v>
       </c>
       <c r="Q5">
-        <v>0.92899200000000004</v>
+        <v>0.92997600000000002</v>
       </c>
       <c r="R5">
-        <v>0.91601999999999995</v>
+        <v>0.94921999999999995</v>
       </c>
       <c r="S5">
-        <v>0.92269699999999999</v>
+        <v>0.94540199999999996</v>
       </c>
       <c r="T5">
-        <v>0.93846799999999997</v>
+        <v>0.92902600000000002</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A6">
-        <v>0.85139600000000004</v>
+        <v>0.85868299999999997</v>
       </c>
       <c r="B6">
-        <v>0.85764099999999999</v>
+        <v>0.86019500000000004</v>
       </c>
       <c r="C6">
-        <v>0.86575199999999997</v>
+        <v>0.86687199999999998</v>
       </c>
       <c r="D6">
-        <v>0.87152200000000002</v>
+        <v>0.86757200000000001</v>
       </c>
       <c r="E6">
-        <v>0.874143</v>
+        <v>0.874556</v>
       </c>
       <c r="F6">
-        <v>0.87982700000000003</v>
+        <v>0.87768800000000002</v>
       </c>
       <c r="G6">
-        <v>0.878104</v>
+        <v>0.886015</v>
       </c>
       <c r="H6">
-        <v>0.88055300000000003</v>
+        <v>0.88848700000000003</v>
       </c>
       <c r="I6">
-        <v>0.88308299999999995</v>
+        <v>0.89361699999999999</v>
       </c>
       <c r="J6">
-        <v>0.88279099999999999</v>
+        <v>0.89288900000000004</v>
       </c>
       <c r="K6">
-        <v>0.88976900000000003</v>
+        <v>0.89948700000000004</v>
       </c>
       <c r="L6">
-        <v>0.89735299999999996</v>
+        <v>0.90724499999999997</v>
       </c>
       <c r="M6">
-        <v>0.89867300000000006</v>
+        <v>0.91162100000000001</v>
       </c>
       <c r="N6">
-        <v>0.90778199999999998</v>
+        <v>0.91549000000000003</v>
       </c>
       <c r="O6">
-        <v>0.91103599999999996</v>
+        <v>0.92527499999999996</v>
       </c>
       <c r="P6">
-        <v>0.92910099999999995</v>
+        <v>0.92875600000000003</v>
       </c>
       <c r="Q6">
-        <v>0.93386100000000005</v>
+        <v>0.93903199999999998</v>
       </c>
       <c r="R6">
-        <v>0.91925000000000001</v>
+        <v>0.95955699999999999</v>
       </c>
       <c r="S6">
-        <v>0.93063499999999999</v>
+        <v>0.95767100000000005</v>
       </c>
       <c r="T6">
-        <v>0.94708800000000004</v>
+        <v>0.94183399999999995</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A7">
-        <v>0.86661699999999997</v>
+        <v>0.85341900000000004</v>
       </c>
       <c r="B7">
-        <v>0.87209400000000004</v>
+        <v>0.85537200000000002</v>
       </c>
       <c r="C7">
-        <v>0.88154999999999994</v>
+        <v>0.86235799999999996</v>
       </c>
       <c r="D7">
-        <v>0.88773599999999997</v>
+        <v>0.86383399999999999</v>
       </c>
       <c r="E7">
-        <v>0.89047799999999999</v>
+        <v>0.87026099999999995</v>
       </c>
       <c r="F7">
-        <v>0.89559100000000003</v>
+        <v>0.874089</v>
       </c>
       <c r="G7">
-        <v>0.89329000000000003</v>
+        <v>0.88085000000000002</v>
       </c>
       <c r="H7">
-        <v>0.89686900000000003</v>
+        <v>0.88383299999999998</v>
       </c>
       <c r="I7">
-        <v>0.89454599999999995</v>
+        <v>0.88996799999999998</v>
       </c>
       <c r="J7">
-        <v>0.89566199999999996</v>
+        <v>0.88922599999999996</v>
       </c>
       <c r="K7">
-        <v>0.90402000000000005</v>
+        <v>0.89542699999999997</v>
       </c>
       <c r="L7">
-        <v>0.91170799999999996</v>
+        <v>0.90413299999999996</v>
       </c>
       <c r="M7">
-        <v>0.913107</v>
+        <v>0.91036600000000001</v>
       </c>
       <c r="N7">
-        <v>0.92308900000000005</v>
+        <v>0.91549100000000005</v>
       </c>
       <c r="O7">
-        <v>0.92708299999999999</v>
+        <v>0.92395499999999997</v>
       </c>
       <c r="P7">
-        <v>0.94403700000000002</v>
+        <v>0.92523100000000003</v>
       </c>
       <c r="Q7">
-        <v>0.94717899999999999</v>
+        <v>0.93678099999999997</v>
       </c>
       <c r="R7">
-        <v>0.934693</v>
+        <v>0.95722700000000005</v>
       </c>
       <c r="S7">
-        <v>0.94209399999999999</v>
+        <v>0.95373399999999997</v>
       </c>
       <c r="T7">
-        <v>0.95739799999999997</v>
+        <v>0.93907200000000002</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A8">
-        <v>0.87014899999999995</v>
+        <v>0.86265099999999995</v>
       </c>
       <c r="B8">
-        <v>0.87641500000000006</v>
+        <v>0.86331100000000005</v>
       </c>
       <c r="C8">
-        <v>0.88654500000000003</v>
+        <v>0.87130700000000005</v>
       </c>
       <c r="D8">
-        <v>0.89362399999999997</v>
+        <v>0.87280100000000005</v>
       </c>
       <c r="E8">
-        <v>0.897428</v>
+        <v>0.88029500000000005</v>
       </c>
       <c r="F8">
-        <v>0.90243399999999996</v>
+        <v>0.88526199999999999</v>
       </c>
       <c r="G8">
-        <v>0.900814</v>
+        <v>0.89205699999999999</v>
       </c>
       <c r="H8">
-        <v>0.90430900000000003</v>
+        <v>0.89502999999999999</v>
       </c>
       <c r="I8">
-        <v>0.90126899999999999</v>
+        <v>0.89964699999999997</v>
       </c>
       <c r="J8">
-        <v>0.90321399999999996</v>
+        <v>0.89884900000000001</v>
       </c>
       <c r="K8">
-        <v>0.91178199999999998</v>
+        <v>0.906663</v>
       </c>
       <c r="L8">
-        <v>0.92085700000000004</v>
+        <v>0.912856</v>
       </c>
       <c r="M8">
-        <v>0.92223299999999997</v>
+        <v>0.92036200000000001</v>
       </c>
       <c r="N8">
-        <v>0.93184500000000003</v>
+        <v>0.92573300000000003</v>
       </c>
       <c r="O8">
-        <v>0.93777500000000003</v>
+        <v>0.93612200000000001</v>
       </c>
       <c r="P8">
-        <v>0.95508700000000002</v>
+        <v>0.93747100000000005</v>
       </c>
       <c r="Q8">
-        <v>0.95971099999999998</v>
+        <v>0.95125800000000005</v>
       </c>
       <c r="R8">
-        <v>0.95010300000000003</v>
+        <v>0.96773500000000001</v>
       </c>
       <c r="S8">
-        <v>0.95739600000000002</v>
+        <v>0.96919599999999995</v>
       </c>
       <c r="T8">
-        <v>0.97698200000000002</v>
+        <v>0.96260299999999999</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A9">
-        <v>0.86993699999999996</v>
+        <v>0.87067600000000001</v>
       </c>
       <c r="B9">
-        <v>0.87651400000000002</v>
+        <v>0.87182400000000004</v>
       </c>
       <c r="C9">
-        <v>0.88727599999999995</v>
+        <v>0.881131</v>
       </c>
       <c r="D9">
-        <v>0.89398699999999998</v>
+        <v>0.88324999999999998</v>
       </c>
       <c r="E9">
-        <v>0.89837100000000003</v>
+        <v>0.89091299999999995</v>
       </c>
       <c r="F9">
-        <v>0.90402000000000005</v>
+        <v>0.894428</v>
       </c>
       <c r="G9">
-        <v>0.902563</v>
+        <v>0.902779</v>
       </c>
       <c r="H9">
-        <v>0.90601699999999996</v>
+        <v>0.90580799999999995</v>
       </c>
       <c r="I9">
-        <v>0.90392600000000001</v>
+        <v>0.91195899999999996</v>
       </c>
       <c r="J9">
-        <v>0.90524000000000004</v>
+        <v>0.91051899999999997</v>
       </c>
       <c r="K9">
-        <v>0.91387600000000002</v>
+        <v>0.91871199999999997</v>
       </c>
       <c r="L9">
-        <v>0.92304200000000003</v>
+        <v>0.92352500000000004</v>
       </c>
       <c r="M9">
-        <v>0.92475799999999997</v>
+        <v>0.93168499999999999</v>
       </c>
       <c r="N9">
-        <v>0.93669199999999997</v>
+        <v>0.93892399999999998</v>
       </c>
       <c r="O9">
-        <v>0.94428999999999996</v>
+        <v>0.94830300000000001</v>
       </c>
       <c r="P9">
-        <v>0.96355199999999996</v>
+        <v>0.94620099999999996</v>
       </c>
       <c r="Q9">
-        <v>0.96913000000000005</v>
+        <v>0.96191599999999999</v>
       </c>
       <c r="R9">
-        <v>0.96361300000000005</v>
+        <v>0.98190100000000002</v>
       </c>
       <c r="S9">
-        <v>0.96472800000000003</v>
+        <v>0.98264099999999999</v>
       </c>
       <c r="T9">
-        <v>0.98136199999999996</v>
+        <v>0.98221000000000003</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A10">
-        <v>0.88594799999999996</v>
+        <v>0.88814000000000004</v>
       </c>
       <c r="B10">
-        <v>0.89052200000000004</v>
+        <v>0.88985400000000003</v>
       </c>
       <c r="C10">
-        <v>0.90157200000000004</v>
+        <v>0.90152399999999999</v>
       </c>
       <c r="D10">
-        <v>0.90873999999999999</v>
+        <v>0.90173700000000001</v>
       </c>
       <c r="E10">
-        <v>0.91479999999999995</v>
+        <v>0.91100999999999999</v>
       </c>
       <c r="F10">
-        <v>0.91917599999999999</v>
+        <v>0.91274599999999995</v>
       </c>
       <c r="G10">
-        <v>0.915709</v>
+        <v>0.91743600000000003</v>
       </c>
       <c r="H10">
-        <v>0.92051799999999995</v>
+        <v>0.921323</v>
       </c>
       <c r="I10">
-        <v>0.91744199999999998</v>
+        <v>0.92931600000000003</v>
       </c>
       <c r="J10">
-        <v>0.92025699999999999</v>
+        <v>0.92578800000000006</v>
       </c>
       <c r="K10">
-        <v>0.9294</v>
+        <v>0.93439000000000005</v>
       </c>
       <c r="L10">
-        <v>0.94148900000000002</v>
+        <v>0.93608599999999997</v>
       </c>
       <c r="M10">
-        <v>0.94162900000000005</v>
+        <v>0.94674100000000005</v>
       </c>
       <c r="N10">
-        <v>0.95592200000000005</v>
+        <v>0.95375399999999999</v>
       </c>
       <c r="O10">
-        <v>0.96127499999999999</v>
+        <v>0.96691400000000005</v>
       </c>
       <c r="P10">
-        <v>0.98635499999999998</v>
+        <v>0.967893</v>
       </c>
       <c r="Q10">
-        <v>0.99067300000000003</v>
+        <v>0.98492400000000002</v>
       </c>
       <c r="R10">
-        <v>0.983491</v>
+        <v>1.0083869999999999</v>
       </c>
       <c r="S10">
-        <v>0.98041400000000001</v>
+        <v>1.002704</v>
       </c>
       <c r="T10">
-        <v>0.99166799999999999</v>
+        <v>0.99166900000000002</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A11">
-        <v>0.89710800000000002</v>
+        <v>0.89600400000000002</v>
       </c>
       <c r="B11">
-        <v>0.90172099999999999</v>
+        <v>0.89738600000000002</v>
       </c>
       <c r="C11">
-        <v>0.91339000000000004</v>
+        <v>0.909246</v>
       </c>
       <c r="D11">
-        <v>0.91978700000000002</v>
+        <v>0.91040900000000002</v>
       </c>
       <c r="E11">
-        <v>0.92556400000000005</v>
+        <v>0.91965200000000003</v>
       </c>
       <c r="F11">
-        <v>0.93088899999999997</v>
+        <v>0.92225400000000002</v>
       </c>
       <c r="G11">
-        <v>0.92827800000000005</v>
+        <v>0.92852000000000001</v>
       </c>
       <c r="H11">
-        <v>0.93478499999999998</v>
+        <v>0.92930500000000005</v>
       </c>
       <c r="I11">
-        <v>0.93047100000000005</v>
+        <v>0.93771300000000002</v>
       </c>
       <c r="J11">
-        <v>0.93495700000000004</v>
+        <v>0.93421500000000002</v>
       </c>
       <c r="K11">
-        <v>0.94508999999999999</v>
+        <v>0.94446099999999999</v>
       </c>
       <c r="L11">
-        <v>0.95940899999999996</v>
+        <v>0.94551499999999999</v>
       </c>
       <c r="M11">
-        <v>0.95885600000000004</v>
+        <v>0.956762</v>
       </c>
       <c r="N11">
-        <v>0.97345800000000005</v>
+        <v>0.96202500000000002</v>
       </c>
       <c r="O11">
-        <v>0.97986600000000001</v>
+        <v>0.978298</v>
       </c>
       <c r="P11">
-        <v>1.00682</v>
+        <v>0.97944500000000001</v>
       </c>
       <c r="Q11">
-        <v>1.012329</v>
+        <v>0.99430099999999999</v>
       </c>
       <c r="R11">
-        <v>1.0011429999999999</v>
+        <v>1.0152460000000001</v>
       </c>
       <c r="S11">
-        <v>0.99657499999999999</v>
+        <v>1.014966</v>
       </c>
       <c r="T11">
-        <v>1.0040709999999999</v>
+        <v>1.002837</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A12">
-        <v>0.90686500000000003</v>
+        <v>0.89802199999999999</v>
       </c>
       <c r="B12">
-        <v>0.91254800000000003</v>
+        <v>0.89848300000000003</v>
       </c>
       <c r="C12">
-        <v>0.92458600000000002</v>
+        <v>0.90535699999999997</v>
       </c>
       <c r="D12">
-        <v>0.93254099999999995</v>
+        <v>0.90681800000000001</v>
       </c>
       <c r="E12">
-        <v>0.94011900000000004</v>
+        <v>0.91723500000000002</v>
       </c>
       <c r="F12">
-        <v>0.94508499999999995</v>
+        <v>0.92083300000000001</v>
       </c>
       <c r="G12">
-        <v>0.94157400000000002</v>
+        <v>0.92874199999999996</v>
       </c>
       <c r="H12">
-        <v>0.95046299999999995</v>
+        <v>0.92832800000000004</v>
       </c>
       <c r="I12">
-        <v>0.94380600000000003</v>
+        <v>0.93847800000000003</v>
       </c>
       <c r="J12">
-        <v>0.94915099999999997</v>
+        <v>0.93629200000000001</v>
       </c>
       <c r="K12">
-        <v>0.95610499999999998</v>
+        <v>0.94459400000000004</v>
       </c>
       <c r="L12">
-        <v>0.96953199999999995</v>
+        <v>0.94482600000000005</v>
       </c>
       <c r="M12">
-        <v>0.97071300000000005</v>
+        <v>0.95817799999999997</v>
       </c>
       <c r="N12">
-        <v>0.98936900000000005</v>
+        <v>0.96566200000000002</v>
       </c>
       <c r="O12">
-        <v>0.99420500000000001</v>
+        <v>0.97760499999999995</v>
       </c>
       <c r="P12">
-        <v>1.023641</v>
+        <v>0.98174600000000001</v>
       </c>
       <c r="Q12">
-        <v>1.032599</v>
+        <v>0.99294400000000005</v>
       </c>
       <c r="R12">
-        <v>1.020821</v>
+        <v>1.0019610000000001</v>
       </c>
       <c r="S12">
-        <v>1.0138579999999999</v>
+        <v>1.0036560000000001</v>
       </c>
       <c r="T12">
-        <v>1.0093080000000001</v>
+        <v>0.99613600000000002</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A13">
-        <v>0.91123500000000002</v>
+        <v>0.91249899999999995</v>
       </c>
       <c r="B13">
-        <v>0.91801600000000005</v>
+        <v>0.91220199999999996</v>
       </c>
       <c r="C13">
-        <v>0.93183800000000006</v>
+        <v>0.91880600000000001</v>
       </c>
       <c r="D13">
-        <v>0.93968600000000002</v>
+        <v>0.91963899999999998</v>
       </c>
       <c r="E13">
-        <v>0.94709900000000002</v>
+        <v>0.92803899999999995</v>
       </c>
       <c r="F13">
-        <v>0.95150800000000002</v>
+        <v>0.93123199999999995</v>
       </c>
       <c r="G13">
-        <v>0.94824699999999995</v>
+        <v>0.94127899999999998</v>
       </c>
       <c r="H13">
-        <v>0.95939700000000006</v>
+        <v>0.939608</v>
       </c>
       <c r="I13">
-        <v>0.95239200000000002</v>
+        <v>0.95293300000000003</v>
       </c>
       <c r="J13">
-        <v>0.956762</v>
+        <v>0.95280500000000001</v>
       </c>
       <c r="K13">
-        <v>0.96645400000000004</v>
+        <v>0.96042000000000005</v>
       </c>
       <c r="L13">
-        <v>0.98155899999999996</v>
+        <v>0.95532300000000003</v>
       </c>
       <c r="M13">
-        <v>0.97569300000000003</v>
+        <v>0.96938400000000002</v>
       </c>
       <c r="N13">
-        <v>0.99088399999999999</v>
+        <v>0.97806300000000002</v>
       </c>
       <c r="O13">
-        <v>0.99328899999999998</v>
+        <v>0.98905100000000001</v>
       </c>
       <c r="P13">
-        <v>1.0156609999999999</v>
+        <v>0.99701499999999998</v>
       </c>
       <c r="Q13">
-        <v>1.024969</v>
+        <v>1.0151269999999999</v>
       </c>
       <c r="R13">
-        <v>1.015158</v>
+        <v>1.0146869999999999</v>
       </c>
       <c r="S13">
-        <v>1.009941</v>
+        <v>1.0117480000000001</v>
       </c>
       <c r="T13">
-        <v>1.0093669999999999</v>
+        <v>0.998695</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A14">
-        <v>0.93083300000000002</v>
+        <v>0.93017000000000005</v>
       </c>
       <c r="B14">
-        <v>0.93678099999999997</v>
+        <v>0.930867</v>
       </c>
       <c r="C14">
-        <v>0.95044300000000004</v>
+        <v>0.93986899999999995</v>
       </c>
       <c r="D14">
-        <v>0.96094999999999997</v>
+        <v>0.94231799999999999</v>
       </c>
       <c r="E14">
-        <v>0.96665100000000004</v>
+        <v>0.95281499999999997</v>
       </c>
       <c r="F14">
-        <v>0.97307299999999997</v>
+        <v>0.95562999999999998</v>
       </c>
       <c r="G14">
-        <v>0.97047600000000001</v>
+        <v>0.96466300000000005</v>
       </c>
       <c r="H14">
-        <v>0.97886700000000004</v>
+        <v>0.96385399999999999</v>
       </c>
       <c r="I14">
-        <v>0.97196499999999997</v>
+        <v>0.97419</v>
       </c>
       <c r="J14">
-        <v>0.97967899999999997</v>
+        <v>0.97102599999999994</v>
       </c>
       <c r="K14">
-        <v>0.99553599999999998</v>
+        <v>0.98153100000000004</v>
       </c>
       <c r="L14">
-        <v>1.0099260000000001</v>
+        <v>0.97835799999999995</v>
       </c>
       <c r="M14">
-        <v>1.002875</v>
+        <v>0.99266600000000005</v>
       </c>
       <c r="N14">
-        <v>1.019407</v>
+        <v>1.0006619999999999</v>
       </c>
       <c r="O14">
-        <v>1.0259119999999999</v>
+        <v>1.01701</v>
       </c>
       <c r="P14">
-        <v>1.0495490000000001</v>
+        <v>1.024124</v>
       </c>
       <c r="Q14">
-        <v>1.06142</v>
+        <v>1.0500210000000001</v>
       </c>
       <c r="R14">
-        <v>1.055844</v>
+        <v>1.0589770000000001</v>
       </c>
       <c r="S14">
-        <v>1.0421879999999999</v>
+        <v>1.0581389999999999</v>
       </c>
       <c r="T14">
-        <v>1.049256</v>
+        <v>1.0602400000000001</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A15">
-        <v>0.93922499999999998</v>
+        <v>0.95564899999999997</v>
       </c>
       <c r="B15">
-        <v>0.94516299999999998</v>
+        <v>0.95526299999999997</v>
       </c>
       <c r="C15">
-        <v>0.96292999999999995</v>
+        <v>0.96037899999999998</v>
       </c>
       <c r="D15">
-        <v>0.97415300000000005</v>
+        <v>0.96499800000000002</v>
       </c>
       <c r="E15">
-        <v>0.97955899999999996</v>
+        <v>0.97921199999999997</v>
       </c>
       <c r="F15">
-        <v>0.985707</v>
+        <v>0.98386300000000004</v>
       </c>
       <c r="G15">
-        <v>0.98468500000000003</v>
+        <v>0.98964799999999997</v>
       </c>
       <c r="H15">
-        <v>0.99680000000000002</v>
+        <v>0.99085500000000004</v>
       </c>
       <c r="I15">
-        <v>0.98974399999999996</v>
+        <v>0.99987999999999999</v>
       </c>
       <c r="J15">
-        <v>1.0014190000000001</v>
+        <v>0.99993699999999996</v>
       </c>
       <c r="K15">
-        <v>1.0105679999999999</v>
+        <v>1.0089669999999999</v>
       </c>
       <c r="L15">
-        <v>1.020502</v>
+        <v>1.0011270000000001</v>
       </c>
       <c r="M15">
-        <v>1.0116499999999999</v>
+        <v>1.017485</v>
       </c>
       <c r="N15">
-        <v>1.028122</v>
+        <v>1.0306519999999999</v>
       </c>
       <c r="O15">
-        <v>1.035183</v>
+        <v>1.044387</v>
       </c>
       <c r="P15">
-        <v>1.0625169999999999</v>
+        <v>1.05358</v>
       </c>
       <c r="Q15">
-        <v>1.079553</v>
+        <v>1.0743689999999999</v>
       </c>
       <c r="R15">
-        <v>1.0829519999999999</v>
+        <v>1.093853</v>
       </c>
       <c r="S15">
-        <v>1.075348</v>
+        <v>1.0889489999999999</v>
       </c>
       <c r="T15">
-        <v>1.0723259999999999</v>
+        <v>1.103043</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A16">
-        <v>0.93959000000000004</v>
+        <v>0.92101100000000002</v>
       </c>
       <c r="B16">
-        <v>0.94281000000000004</v>
+        <v>0.92175099999999999</v>
       </c>
       <c r="C16">
-        <v>0.96203499999999997</v>
+        <v>0.92279199999999995</v>
       </c>
       <c r="D16">
-        <v>0.97072599999999998</v>
+        <v>0.92968600000000001</v>
       </c>
       <c r="E16">
-        <v>0.97269499999999998</v>
+        <v>0.94566600000000001</v>
       </c>
       <c r="F16">
-        <v>0.97861299999999996</v>
+        <v>0.951905</v>
       </c>
       <c r="G16">
-        <v>0.98052099999999998</v>
+        <v>0.95869300000000002</v>
       </c>
       <c r="H16">
-        <v>0.99059799999999998</v>
+        <v>0.95775299999999997</v>
       </c>
       <c r="I16">
-        <v>0.98371200000000003</v>
+        <v>0.96606400000000003</v>
       </c>
       <c r="J16">
-        <v>0.99644299999999997</v>
+        <v>0.96862400000000004</v>
       </c>
       <c r="K16">
-        <v>1.006345</v>
+        <v>0.98144799999999999</v>
       </c>
       <c r="L16">
-        <v>1.0161899999999999</v>
+        <v>0.97640000000000005</v>
       </c>
       <c r="M16">
-        <v>1.0080519999999999</v>
+        <v>0.99307199999999995</v>
       </c>
       <c r="N16">
-        <v>1.0273540000000001</v>
+        <v>1.0118720000000001</v>
       </c>
       <c r="O16">
-        <v>1.039731</v>
+        <v>1.0295049999999999</v>
       </c>
       <c r="P16">
-        <v>1.0686059999999999</v>
+        <v>1.0457289999999999</v>
       </c>
       <c r="Q16">
-        <v>1.0927340000000001</v>
+        <v>1.063469</v>
       </c>
       <c r="R16">
-        <v>1.111054</v>
+        <v>1.078244</v>
       </c>
       <c r="S16">
-        <v>1.1045119999999999</v>
+        <v>1.0764819999999999</v>
       </c>
       <c r="T16">
-        <v>1.089512</v>
+        <v>1.088203</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A17">
-        <v>0.941693</v>
+        <v>0.93583300000000003</v>
       </c>
       <c r="B17">
-        <v>0.94711999999999996</v>
+        <v>0.93914699999999995</v>
       </c>
       <c r="C17">
-        <v>0.961758</v>
+        <v>0.93951499999999999</v>
       </c>
       <c r="D17">
-        <v>0.97075800000000001</v>
+        <v>0.94795799999999997</v>
       </c>
       <c r="E17">
-        <v>0.97515499999999999</v>
+        <v>0.96257000000000004</v>
       </c>
       <c r="F17">
-        <v>0.98454200000000003</v>
+        <v>0.96819</v>
       </c>
       <c r="G17">
-        <v>0.98414000000000001</v>
+        <v>0.98000299999999996</v>
       </c>
       <c r="H17">
-        <v>1.0009269999999999</v>
+        <v>0.97679300000000002</v>
       </c>
       <c r="I17">
-        <v>0.99360099999999996</v>
+        <v>0.97734100000000002</v>
       </c>
       <c r="J17">
-        <v>1.004257</v>
+        <v>0.98449900000000001</v>
       </c>
       <c r="K17">
-        <v>1.0127550000000001</v>
+        <v>1.000556</v>
       </c>
       <c r="L17">
-        <v>1.019461</v>
+        <v>0.991645</v>
       </c>
       <c r="M17">
-        <v>1.007409</v>
+        <v>1.0074149999999999</v>
       </c>
       <c r="N17">
-        <v>1.019201</v>
+        <v>1.0334540000000001</v>
       </c>
       <c r="O17">
-        <v>1.0359160000000001</v>
+        <v>1.051849</v>
       </c>
       <c r="P17">
-        <v>1.0768530000000001</v>
+        <v>1.0693520000000001</v>
       </c>
       <c r="Q17">
-        <v>1.10348</v>
+        <v>1.0830169999999999</v>
       </c>
       <c r="R17">
-        <v>1.1344590000000001</v>
+        <v>1.1121110000000001</v>
       </c>
       <c r="S17">
-        <v>1.1374040000000001</v>
+        <v>1.1163460000000001</v>
       </c>
       <c r="T17">
-        <v>1.108711</v>
+        <v>1.116447</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A18">
-        <v>0.91506600000000005</v>
+        <v>0.90221300000000004</v>
       </c>
       <c r="B18">
-        <v>0.91766700000000001</v>
+        <v>0.90901900000000002</v>
       </c>
       <c r="C18">
-        <v>0.93949400000000005</v>
+        <v>0.91045100000000001</v>
       </c>
       <c r="D18">
-        <v>0.95388300000000004</v>
+        <v>0.91731700000000005</v>
       </c>
       <c r="E18">
-        <v>0.95571300000000003</v>
+        <v>0.932284</v>
       </c>
       <c r="F18">
-        <v>0.97170599999999996</v>
+        <v>0.92943699999999996</v>
       </c>
       <c r="G18">
-        <v>0.96760299999999999</v>
+        <v>0.94733000000000001</v>
       </c>
       <c r="H18">
-        <v>0.983097</v>
+        <v>0.94618599999999997</v>
       </c>
       <c r="I18">
-        <v>0.97587000000000002</v>
+        <v>0.95067800000000002</v>
       </c>
       <c r="J18">
-        <v>0.99555499999999997</v>
+        <v>0.95774199999999998</v>
       </c>
       <c r="K18">
-        <v>1.003835</v>
+        <v>0.97850999999999999</v>
       </c>
       <c r="L18">
-        <v>1.012248</v>
+        <v>0.97117399999999998</v>
       </c>
       <c r="M18">
-        <v>1.001779</v>
+        <v>0.98229100000000003</v>
       </c>
       <c r="N18">
-        <v>1.00692</v>
+        <v>1.008148</v>
       </c>
       <c r="O18">
-        <v>1.020613</v>
+        <v>1.031425</v>
       </c>
       <c r="P18">
-        <v>1.0604119999999999</v>
+        <v>1.054443</v>
       </c>
       <c r="Q18">
-        <v>1.08815</v>
+        <v>1.0734399999999999</v>
       </c>
       <c r="R18">
-        <v>1.1399589999999999</v>
+        <v>1.090724</v>
       </c>
       <c r="S18">
-        <v>1.1452910000000001</v>
+        <v>1.096714</v>
       </c>
       <c r="T18">
-        <v>1.1471910000000001</v>
+        <v>1.1179250000000001</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A19">
-        <v>0.93777900000000003</v>
+        <v>0.925813</v>
       </c>
       <c r="B19">
-        <v>0.93434799999999996</v>
+        <v>0.92349499999999995</v>
       </c>
       <c r="C19">
-        <v>0.95701599999999998</v>
+        <v>0.92117499999999997</v>
       </c>
       <c r="D19">
-        <v>0.95301000000000002</v>
+        <v>0.91792700000000005</v>
       </c>
       <c r="E19">
-        <v>0.94899999999999995</v>
+        <v>0.93702600000000003</v>
       </c>
       <c r="F19">
-        <v>0.95686899999999997</v>
+        <v>0.93560600000000005</v>
       </c>
       <c r="G19">
-        <v>0.95433299999999999</v>
+        <v>0.95268200000000003</v>
       </c>
       <c r="H19">
-        <v>0.96410799999999997</v>
+        <v>0.95783300000000005</v>
       </c>
       <c r="I19">
-        <v>0.95743100000000003</v>
+        <v>0.96376600000000001</v>
       </c>
       <c r="J19">
-        <v>0.97665800000000003</v>
+        <v>0.97101800000000005</v>
       </c>
       <c r="K19">
-        <v>0.97191700000000003</v>
+        <v>1.0043949999999999</v>
       </c>
       <c r="L19">
-        <v>0.99631199999999998</v>
+        <v>0.99819100000000005</v>
       </c>
       <c r="M19">
-        <v>0.98603499999999999</v>
+        <v>1.019722</v>
       </c>
       <c r="N19">
-        <v>0.99107199999999995</v>
+        <v>1.054243</v>
       </c>
       <c r="O19">
-        <v>0.98172499999999996</v>
+        <v>1.0776939999999999</v>
       </c>
       <c r="P19">
-        <v>1.0160229999999999</v>
+        <v>1.1026</v>
       </c>
       <c r="Q19">
-        <v>1.0395760000000001</v>
+        <v>1.145778</v>
       </c>
       <c r="R19">
-        <v>1.0581769999999999</v>
+        <v>1.169071</v>
       </c>
       <c r="S19">
-        <v>1.0736209999999999</v>
+        <v>1.253717</v>
       </c>
       <c r="T19">
-        <v>1.0892930000000001</v>
+        <v>1.2395830000000001</v>
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A20">
-        <v>0.811253</v>
+        <v>0.81850599999999996</v>
       </c>
       <c r="B20">
-        <v>0.808527</v>
+        <v>0.81609399999999999</v>
       </c>
       <c r="C20">
-        <v>0.849441</v>
+        <v>0.81367900000000004</v>
       </c>
       <c r="D20">
-        <v>0.84755800000000003</v>
+        <v>0.81206900000000004</v>
       </c>
       <c r="E20">
-        <v>0.84661600000000004</v>
+        <v>0.80965200000000004</v>
       </c>
       <c r="F20">
-        <v>0.89042900000000003</v>
+        <v>0.80884599999999995</v>
       </c>
       <c r="G20">
-        <v>0.88847100000000001</v>
+        <v>0.86837699999999995</v>
       </c>
       <c r="H20">
-        <v>0.94303499999999996</v>
+        <v>0.86666799999999999</v>
       </c>
       <c r="I20">
-        <v>0.93896100000000005</v>
+        <v>0.86238999999999999</v>
       </c>
       <c r="J20">
-        <v>0.93385799999999997</v>
+        <v>0.89637100000000003</v>
       </c>
       <c r="K20">
-        <v>0.92976800000000004</v>
+        <v>0.93660399999999999</v>
       </c>
       <c r="L20">
-        <v>0.92772100000000002</v>
+        <v>0.93203199999999997</v>
       </c>
       <c r="M20">
-        <v>0.92259599999999997</v>
+        <v>0.92562</v>
       </c>
       <c r="N20">
-        <v>0.91437400000000002</v>
+        <v>1.0251699999999999</v>
       </c>
       <c r="O20">
-        <v>0.91025299999999998</v>
+        <v>1.014303</v>
       </c>
       <c r="P20">
-        <v>0.89888500000000005</v>
+        <v>1.0043839999999999</v>
       </c>
       <c r="Q20">
-        <v>0.95736500000000002</v>
+        <v>0.98943400000000004</v>
       </c>
       <c r="R20">
-        <v>1.02826</v>
+        <v>0.96734799999999999</v>
       </c>
       <c r="S20">
-        <v>1.012303</v>
+        <v>1.2121630000000001</v>
       </c>
       <c r="T20">
-        <v>1.2286999999999999</v>
+        <v>1.150015</v>
       </c>
     </row>
   </sheetData>

--- a/TMVA/FOM_small.xlsx
+++ b/TMVA/FOM_small.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24701"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\purol\OneDrive\바탕 화면\github\Belle2_script\TMVA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20A9AE22-58EC-40F9-A32C-A4CEAA3DB55F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F94B995-4F38-41F4-8178-E275611BCD24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -349,1242 +349,1242 @@
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A1">
-        <v>0.823268</v>
+        <v>0.76303100000000001</v>
       </c>
       <c r="B1">
-        <v>0.82479000000000002</v>
+        <v>0.76717900000000006</v>
       </c>
       <c r="C1">
-        <v>0.82944200000000001</v>
+        <v>0.77315599999999995</v>
       </c>
       <c r="D1">
-        <v>0.82950900000000005</v>
+        <v>0.77193699999999998</v>
       </c>
       <c r="E1">
-        <v>0.83832399999999996</v>
+        <v>0.77916399999999997</v>
       </c>
       <c r="F1">
-        <v>0.84323099999999995</v>
+        <v>0.777721</v>
       </c>
       <c r="G1">
-        <v>0.84924299999999997</v>
+        <v>0.78299799999999997</v>
       </c>
       <c r="H1">
-        <v>0.850796</v>
+        <v>0.78242599999999995</v>
       </c>
       <c r="I1">
-        <v>0.85426899999999995</v>
+        <v>0.78178899999999996</v>
       </c>
       <c r="J1">
-        <v>0.85575100000000004</v>
+        <v>0.78102800000000006</v>
       </c>
       <c r="K1">
-        <v>0.86499000000000004</v>
+        <v>0.79250399999999999</v>
       </c>
       <c r="L1">
-        <v>0.87121300000000002</v>
+        <v>0.79783099999999996</v>
       </c>
       <c r="M1">
-        <v>0.87645399999999996</v>
+        <v>0.79895899999999997</v>
       </c>
       <c r="N1">
-        <v>0.88135600000000003</v>
+        <v>0.796574</v>
       </c>
       <c r="O1">
-        <v>0.88877600000000001</v>
+        <v>0.79680499999999999</v>
       </c>
       <c r="P1">
-        <v>0.89078800000000002</v>
+        <v>0.79417199999999999</v>
       </c>
       <c r="Q1">
-        <v>0.90229499999999996</v>
+        <v>0.80876800000000004</v>
       </c>
       <c r="R1">
-        <v>0.91644899999999996</v>
+        <v>0.80239899999999997</v>
       </c>
       <c r="S1">
-        <v>0.906412</v>
+        <v>0.81112700000000004</v>
       </c>
       <c r="T1">
-        <v>0.89570899999999998</v>
+        <v>0.76530600000000004</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A2">
-        <v>0.82362100000000005</v>
+        <v>0.76319099999999995</v>
       </c>
       <c r="B2">
-        <v>0.82367800000000002</v>
+        <v>0.76688699999999999</v>
       </c>
       <c r="C2">
-        <v>0.82878099999999999</v>
+        <v>0.77227500000000004</v>
       </c>
       <c r="D2">
-        <v>0.82845999999999997</v>
+        <v>0.77059100000000003</v>
       </c>
       <c r="E2">
-        <v>0.83765999999999996</v>
+        <v>0.77803</v>
       </c>
       <c r="F2">
-        <v>0.84193799999999996</v>
+        <v>0.77711300000000005</v>
       </c>
       <c r="G2">
-        <v>0.84792000000000001</v>
+        <v>0.78183999999999998</v>
       </c>
       <c r="H2">
-        <v>0.84871099999999999</v>
+        <v>0.78199399999999997</v>
       </c>
       <c r="I2">
-        <v>0.85295900000000002</v>
+        <v>0.78066599999999997</v>
       </c>
       <c r="J2">
-        <v>0.85411700000000002</v>
+        <v>0.77902499999999997</v>
       </c>
       <c r="K2">
-        <v>0.86377700000000002</v>
+        <v>0.79094299999999995</v>
       </c>
       <c r="L2">
-        <v>0.86916700000000002</v>
+        <v>0.79646499999999998</v>
       </c>
       <c r="M2">
-        <v>0.87284499999999998</v>
+        <v>0.79790799999999995</v>
       </c>
       <c r="N2">
-        <v>0.878722</v>
+        <v>0.79695099999999996</v>
       </c>
       <c r="O2">
-        <v>0.88741599999999998</v>
+        <v>0.79877699999999996</v>
       </c>
       <c r="P2">
-        <v>0.89037100000000002</v>
+        <v>0.79669699999999999</v>
       </c>
       <c r="Q2">
-        <v>0.90000899999999995</v>
+        <v>0.81138399999999999</v>
       </c>
       <c r="R2">
-        <v>0.91592799999999996</v>
+        <v>0.80667100000000003</v>
       </c>
       <c r="S2">
-        <v>0.90503699999999998</v>
+        <v>0.81292699999999996</v>
       </c>
       <c r="T2">
-        <v>0.89387899999999998</v>
+        <v>0.76719199999999999</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A3">
-        <v>0.82824399999999998</v>
+        <v>0.76848300000000003</v>
       </c>
       <c r="B3">
-        <v>0.82846699999999995</v>
+        <v>0.77278199999999997</v>
       </c>
       <c r="C3">
-        <v>0.83395699999999995</v>
+        <v>0.77874299999999996</v>
       </c>
       <c r="D3">
-        <v>0.83410399999999996</v>
+        <v>0.77732699999999999</v>
       </c>
       <c r="E3">
-        <v>0.84296599999999999</v>
+        <v>0.78492600000000001</v>
       </c>
       <c r="F3">
-        <v>0.84836800000000001</v>
+        <v>0.78452</v>
       </c>
       <c r="G3">
-        <v>0.85507200000000005</v>
+        <v>0.79018999999999995</v>
       </c>
       <c r="H3">
-        <v>0.85665400000000003</v>
+        <v>0.79064999999999996</v>
       </c>
       <c r="I3">
-        <v>0.86185</v>
+        <v>0.78991500000000003</v>
       </c>
       <c r="J3">
-        <v>0.86288799999999999</v>
+        <v>0.78878300000000001</v>
       </c>
       <c r="K3">
-        <v>0.87186799999999998</v>
+        <v>0.79983599999999999</v>
       </c>
       <c r="L3">
-        <v>0.87719199999999997</v>
+        <v>0.80628100000000003</v>
       </c>
       <c r="M3">
-        <v>0.87987099999999996</v>
+        <v>0.80883700000000003</v>
       </c>
       <c r="N3">
-        <v>0.88709300000000002</v>
+        <v>0.809531</v>
       </c>
       <c r="O3">
-        <v>0.89728699999999995</v>
+        <v>0.80988199999999999</v>
       </c>
       <c r="P3">
-        <v>0.90017100000000005</v>
+        <v>0.80793599999999999</v>
       </c>
       <c r="Q3">
-        <v>0.91038300000000005</v>
+        <v>0.82203800000000005</v>
       </c>
       <c r="R3">
-        <v>0.92667699999999997</v>
+        <v>0.81820400000000004</v>
       </c>
       <c r="S3">
-        <v>0.91903299999999999</v>
+        <v>0.82355999999999996</v>
       </c>
       <c r="T3">
-        <v>0.89985599999999999</v>
+        <v>0.78308199999999994</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A4">
-        <v>0.83932300000000004</v>
+        <v>0.77410000000000001</v>
       </c>
       <c r="B4">
-        <v>0.84013400000000005</v>
+        <v>0.77617499999999995</v>
       </c>
       <c r="C4">
-        <v>0.84545599999999999</v>
+        <v>0.78073300000000001</v>
       </c>
       <c r="D4">
-        <v>0.84606700000000001</v>
+        <v>0.77954800000000002</v>
       </c>
       <c r="E4">
-        <v>0.85518000000000005</v>
+        <v>0.78691999999999995</v>
       </c>
       <c r="F4">
-        <v>0.85973999999999995</v>
+        <v>0.78696100000000002</v>
       </c>
       <c r="G4">
-        <v>0.86765199999999998</v>
+        <v>0.79294100000000001</v>
       </c>
       <c r="H4">
-        <v>0.86878500000000003</v>
+        <v>0.79393100000000005</v>
       </c>
       <c r="I4">
-        <v>0.87350000000000005</v>
+        <v>0.79438399999999998</v>
       </c>
       <c r="J4">
-        <v>0.87268199999999996</v>
+        <v>0.79400199999999999</v>
       </c>
       <c r="K4">
-        <v>0.88109400000000004</v>
+        <v>0.80581199999999997</v>
       </c>
       <c r="L4">
-        <v>0.88654999999999995</v>
+        <v>0.81063200000000002</v>
       </c>
       <c r="M4">
-        <v>0.88920500000000002</v>
+        <v>0.81374899999999994</v>
       </c>
       <c r="N4">
-        <v>0.89274200000000004</v>
+        <v>0.81377900000000003</v>
       </c>
       <c r="O4">
-        <v>0.90286200000000005</v>
+        <v>0.81520599999999999</v>
       </c>
       <c r="P4">
-        <v>0.90552500000000002</v>
+        <v>0.81277100000000002</v>
       </c>
       <c r="Q4">
-        <v>0.916543</v>
+        <v>0.82717399999999996</v>
       </c>
       <c r="R4">
-        <v>0.93412200000000001</v>
+        <v>0.823214</v>
       </c>
       <c r="S4">
-        <v>0.92749599999999999</v>
+        <v>0.82879700000000001</v>
       </c>
       <c r="T4">
-        <v>0.90778400000000004</v>
+        <v>0.78959299999999999</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A5">
-        <v>0.849719</v>
+        <v>0.78969500000000004</v>
       </c>
       <c r="B5">
-        <v>0.85102900000000004</v>
+        <v>0.792381</v>
       </c>
       <c r="C5">
-        <v>0.85690999999999995</v>
+        <v>0.79723100000000002</v>
       </c>
       <c r="D5">
-        <v>0.85728700000000002</v>
+        <v>0.79647999999999997</v>
       </c>
       <c r="E5">
-        <v>0.86536999999999997</v>
+        <v>0.80440500000000004</v>
       </c>
       <c r="F5">
-        <v>0.86986300000000005</v>
+        <v>0.80386800000000003</v>
       </c>
       <c r="G5">
-        <v>0.87789600000000001</v>
+        <v>0.81095600000000001</v>
       </c>
       <c r="H5">
-        <v>0.87895100000000004</v>
+        <v>0.81183499999999997</v>
       </c>
       <c r="I5">
-        <v>0.88391799999999998</v>
+        <v>0.81208199999999997</v>
       </c>
       <c r="J5">
-        <v>0.88239199999999995</v>
+        <v>0.812384</v>
       </c>
       <c r="K5">
-        <v>0.89133799999999996</v>
+        <v>0.826515</v>
       </c>
       <c r="L5">
-        <v>0.89716700000000005</v>
+        <v>0.83024100000000001</v>
       </c>
       <c r="M5">
-        <v>0.89984200000000003</v>
+        <v>0.83331</v>
       </c>
       <c r="N5">
-        <v>0.90336300000000003</v>
+        <v>0.83246900000000001</v>
       </c>
       <c r="O5">
-        <v>0.91545299999999996</v>
+        <v>0.83157499999999995</v>
       </c>
       <c r="P5">
-        <v>0.91893499999999995</v>
+        <v>0.82969899999999996</v>
       </c>
       <c r="Q5">
-        <v>0.92997600000000002</v>
+        <v>0.84552300000000002</v>
       </c>
       <c r="R5">
-        <v>0.94921999999999995</v>
+        <v>0.83451600000000004</v>
       </c>
       <c r="S5">
-        <v>0.94540199999999996</v>
+        <v>0.83774000000000004</v>
       </c>
       <c r="T5">
-        <v>0.92902600000000002</v>
+        <v>0.803041</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A6">
-        <v>0.85868299999999997</v>
+        <v>0.79650900000000002</v>
       </c>
       <c r="B6">
-        <v>0.86019500000000004</v>
+        <v>0.79988300000000001</v>
       </c>
       <c r="C6">
-        <v>0.86687199999999998</v>
+        <v>0.80443699999999996</v>
       </c>
       <c r="D6">
-        <v>0.86757200000000001</v>
+        <v>0.80422800000000005</v>
       </c>
       <c r="E6">
-        <v>0.874556</v>
+        <v>0.81328900000000004</v>
       </c>
       <c r="F6">
-        <v>0.87768800000000002</v>
+        <v>0.81356300000000004</v>
       </c>
       <c r="G6">
-        <v>0.886015</v>
+        <v>0.81952700000000001</v>
       </c>
       <c r="H6">
-        <v>0.88848700000000003</v>
+        <v>0.81937000000000004</v>
       </c>
       <c r="I6">
-        <v>0.89361699999999999</v>
+        <v>0.82031799999999999</v>
       </c>
       <c r="J6">
-        <v>0.89288900000000004</v>
+        <v>0.82006500000000004</v>
       </c>
       <c r="K6">
-        <v>0.89948700000000004</v>
+        <v>0.83673200000000003</v>
       </c>
       <c r="L6">
-        <v>0.90724499999999997</v>
+        <v>0.84148400000000001</v>
       </c>
       <c r="M6">
-        <v>0.91162100000000001</v>
+        <v>0.84578299999999995</v>
       </c>
       <c r="N6">
-        <v>0.91549000000000003</v>
+        <v>0.84350899999999995</v>
       </c>
       <c r="O6">
-        <v>0.92527499999999996</v>
+        <v>0.84414</v>
       </c>
       <c r="P6">
-        <v>0.92875600000000003</v>
+        <v>0.84304400000000002</v>
       </c>
       <c r="Q6">
-        <v>0.93903199999999998</v>
+        <v>0.86116599999999999</v>
       </c>
       <c r="R6">
-        <v>0.95955699999999999</v>
+        <v>0.84917200000000004</v>
       </c>
       <c r="S6">
-        <v>0.95767100000000005</v>
+        <v>0.85472000000000004</v>
       </c>
       <c r="T6">
-        <v>0.94183399999999995</v>
+        <v>0.824214</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A7">
-        <v>0.85341900000000004</v>
+        <v>0.80183199999999999</v>
       </c>
       <c r="B7">
-        <v>0.85537200000000002</v>
+        <v>0.80593000000000004</v>
       </c>
       <c r="C7">
-        <v>0.86235799999999996</v>
+        <v>0.81152000000000002</v>
       </c>
       <c r="D7">
-        <v>0.86383399999999999</v>
+        <v>0.812249</v>
       </c>
       <c r="E7">
-        <v>0.87026099999999995</v>
+        <v>0.82123699999999999</v>
       </c>
       <c r="F7">
-        <v>0.874089</v>
+        <v>0.82101500000000005</v>
       </c>
       <c r="G7">
-        <v>0.88085000000000002</v>
+        <v>0.82556799999999997</v>
       </c>
       <c r="H7">
-        <v>0.88383299999999998</v>
+        <v>0.82643</v>
       </c>
       <c r="I7">
-        <v>0.88996799999999998</v>
+        <v>0.82722499999999999</v>
       </c>
       <c r="J7">
-        <v>0.88922599999999996</v>
+        <v>0.82591499999999995</v>
       </c>
       <c r="K7">
-        <v>0.89542699999999997</v>
+        <v>0.84109999999999996</v>
       </c>
       <c r="L7">
-        <v>0.90413299999999996</v>
+        <v>0.84538999999999997</v>
       </c>
       <c r="M7">
-        <v>0.91036600000000001</v>
+        <v>0.84775199999999995</v>
       </c>
       <c r="N7">
-        <v>0.91549100000000005</v>
+        <v>0.846221</v>
       </c>
       <c r="O7">
-        <v>0.92395499999999997</v>
+        <v>0.84484199999999998</v>
       </c>
       <c r="P7">
-        <v>0.92523100000000003</v>
+        <v>0.84445400000000004</v>
       </c>
       <c r="Q7">
-        <v>0.93678099999999997</v>
+        <v>0.86527299999999996</v>
       </c>
       <c r="R7">
-        <v>0.95722700000000005</v>
+        <v>0.85533899999999996</v>
       </c>
       <c r="S7">
-        <v>0.95373399999999997</v>
+        <v>0.86013799999999996</v>
       </c>
       <c r="T7">
-        <v>0.93907200000000002</v>
+        <v>0.83543599999999996</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A8">
-        <v>0.86265099999999995</v>
+        <v>0.80659000000000003</v>
       </c>
       <c r="B8">
-        <v>0.86331100000000005</v>
+        <v>0.81147800000000003</v>
       </c>
       <c r="C8">
-        <v>0.87130700000000005</v>
+        <v>0.81650500000000004</v>
       </c>
       <c r="D8">
-        <v>0.87280100000000005</v>
+        <v>0.81786700000000001</v>
       </c>
       <c r="E8">
-        <v>0.88029500000000005</v>
+        <v>0.82808999999999999</v>
       </c>
       <c r="F8">
-        <v>0.88526199999999999</v>
+        <v>0.82744499999999999</v>
       </c>
       <c r="G8">
-        <v>0.89205699999999999</v>
+        <v>0.83127799999999996</v>
       </c>
       <c r="H8">
-        <v>0.89502999999999999</v>
+        <v>0.83173699999999995</v>
       </c>
       <c r="I8">
-        <v>0.89964699999999997</v>
+        <v>0.833457</v>
       </c>
       <c r="J8">
-        <v>0.89884900000000001</v>
+        <v>0.83309599999999995</v>
       </c>
       <c r="K8">
-        <v>0.906663</v>
+        <v>0.85052799999999995</v>
       </c>
       <c r="L8">
-        <v>0.912856</v>
+        <v>0.85741599999999996</v>
       </c>
       <c r="M8">
-        <v>0.92036200000000001</v>
+        <v>0.86128000000000005</v>
       </c>
       <c r="N8">
-        <v>0.92573300000000003</v>
+        <v>0.85800699999999996</v>
       </c>
       <c r="O8">
-        <v>0.93612200000000001</v>
+        <v>0.85480699999999998</v>
       </c>
       <c r="P8">
-        <v>0.93747100000000005</v>
+        <v>0.85337300000000005</v>
       </c>
       <c r="Q8">
-        <v>0.95125800000000005</v>
+        <v>0.87690900000000005</v>
       </c>
       <c r="R8">
-        <v>0.96773500000000001</v>
+        <v>0.86629999999999996</v>
       </c>
       <c r="S8">
-        <v>0.96919599999999995</v>
+        <v>0.87399499999999997</v>
       </c>
       <c r="T8">
-        <v>0.96260299999999999</v>
+        <v>0.855904</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A9">
-        <v>0.87067600000000001</v>
+        <v>0.82120400000000005</v>
       </c>
       <c r="B9">
-        <v>0.87182400000000004</v>
+        <v>0.82729699999999995</v>
       </c>
       <c r="C9">
-        <v>0.881131</v>
+        <v>0.83237499999999998</v>
       </c>
       <c r="D9">
-        <v>0.88324999999999998</v>
+        <v>0.83204</v>
       </c>
       <c r="E9">
-        <v>0.89091299999999995</v>
+        <v>0.84277400000000002</v>
       </c>
       <c r="F9">
-        <v>0.894428</v>
+        <v>0.84290699999999996</v>
       </c>
       <c r="G9">
-        <v>0.902779</v>
+        <v>0.84511800000000004</v>
       </c>
       <c r="H9">
-        <v>0.90580799999999995</v>
+        <v>0.84668900000000002</v>
       </c>
       <c r="I9">
-        <v>0.91195899999999996</v>
+        <v>0.84931199999999996</v>
       </c>
       <c r="J9">
-        <v>0.91051899999999997</v>
+        <v>0.84875</v>
       </c>
       <c r="K9">
-        <v>0.91871199999999997</v>
+        <v>0.86773</v>
       </c>
       <c r="L9">
-        <v>0.92352500000000004</v>
+        <v>0.87555400000000005</v>
       </c>
       <c r="M9">
-        <v>0.93168499999999999</v>
+        <v>0.87747600000000003</v>
       </c>
       <c r="N9">
-        <v>0.93892399999999998</v>
+        <v>0.87362099999999998</v>
       </c>
       <c r="O9">
-        <v>0.94830300000000001</v>
+        <v>0.87304800000000005</v>
       </c>
       <c r="P9">
-        <v>0.94620099999999996</v>
+        <v>0.86774600000000002</v>
       </c>
       <c r="Q9">
-        <v>0.96191599999999999</v>
+        <v>0.892818</v>
       </c>
       <c r="R9">
-        <v>0.98190100000000002</v>
+        <v>0.88549699999999998</v>
       </c>
       <c r="S9">
-        <v>0.98264099999999999</v>
+        <v>0.90316600000000002</v>
       </c>
       <c r="T9">
-        <v>0.98221000000000003</v>
+        <v>0.86868000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A10">
-        <v>0.88814000000000004</v>
+        <v>0.82703099999999996</v>
       </c>
       <c r="B10">
-        <v>0.88985400000000003</v>
+        <v>0.83124799999999999</v>
       </c>
       <c r="C10">
-        <v>0.90152399999999999</v>
+        <v>0.836059</v>
       </c>
       <c r="D10">
-        <v>0.90173700000000001</v>
+        <v>0.83609699999999998</v>
       </c>
       <c r="E10">
-        <v>0.91100999999999999</v>
+        <v>0.84836100000000003</v>
       </c>
       <c r="F10">
-        <v>0.91274599999999995</v>
+        <v>0.84767199999999998</v>
       </c>
       <c r="G10">
-        <v>0.91743600000000003</v>
+        <v>0.85047799999999996</v>
       </c>
       <c r="H10">
-        <v>0.921323</v>
+        <v>0.85107500000000003</v>
       </c>
       <c r="I10">
-        <v>0.92931600000000003</v>
+        <v>0.85275800000000002</v>
       </c>
       <c r="J10">
-        <v>0.92578800000000006</v>
+        <v>0.85131900000000005</v>
       </c>
       <c r="K10">
-        <v>0.93439000000000005</v>
+        <v>0.87273000000000001</v>
       </c>
       <c r="L10">
-        <v>0.93608599999999997</v>
+        <v>0.88175000000000003</v>
       </c>
       <c r="M10">
-        <v>0.94674100000000005</v>
+        <v>0.88500400000000001</v>
       </c>
       <c r="N10">
-        <v>0.95375399999999999</v>
+        <v>0.882606</v>
       </c>
       <c r="O10">
-        <v>0.96691400000000005</v>
+        <v>0.87930699999999995</v>
       </c>
       <c r="P10">
-        <v>0.967893</v>
+        <v>0.87525299999999995</v>
       </c>
       <c r="Q10">
-        <v>0.98492400000000002</v>
+        <v>0.90305800000000003</v>
       </c>
       <c r="R10">
-        <v>1.0083869999999999</v>
+        <v>0.89626600000000001</v>
       </c>
       <c r="S10">
-        <v>1.002704</v>
+        <v>0.912385</v>
       </c>
       <c r="T10">
-        <v>0.99166900000000002</v>
+        <v>0.87752300000000005</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A11">
-        <v>0.89600400000000002</v>
+        <v>0.84440999999999999</v>
       </c>
       <c r="B11">
-        <v>0.89738600000000002</v>
+        <v>0.84820600000000002</v>
       </c>
       <c r="C11">
-        <v>0.909246</v>
+        <v>0.85270800000000002</v>
       </c>
       <c r="D11">
-        <v>0.91040900000000002</v>
+        <v>0.85360999999999998</v>
       </c>
       <c r="E11">
-        <v>0.91965200000000003</v>
+        <v>0.86824299999999999</v>
       </c>
       <c r="F11">
-        <v>0.92225400000000002</v>
+        <v>0.86826400000000004</v>
       </c>
       <c r="G11">
-        <v>0.92852000000000001</v>
+        <v>0.87052099999999999</v>
       </c>
       <c r="H11">
-        <v>0.92930500000000005</v>
+        <v>0.871861</v>
       </c>
       <c r="I11">
-        <v>0.93771300000000002</v>
+        <v>0.87561</v>
       </c>
       <c r="J11">
-        <v>0.93421500000000002</v>
+        <v>0.87379700000000005</v>
       </c>
       <c r="K11">
-        <v>0.94446099999999999</v>
+        <v>0.89164900000000002</v>
       </c>
       <c r="L11">
-        <v>0.94551499999999999</v>
+        <v>0.89731399999999994</v>
       </c>
       <c r="M11">
-        <v>0.956762</v>
+        <v>0.90379699999999996</v>
       </c>
       <c r="N11">
-        <v>0.96202500000000002</v>
+        <v>0.903115</v>
       </c>
       <c r="O11">
-        <v>0.978298</v>
+        <v>0.89744199999999996</v>
       </c>
       <c r="P11">
-        <v>0.97944500000000001</v>
+        <v>0.89410000000000001</v>
       </c>
       <c r="Q11">
-        <v>0.99430099999999999</v>
+        <v>0.92767900000000003</v>
       </c>
       <c r="R11">
-        <v>1.0152460000000001</v>
+        <v>0.92099500000000001</v>
       </c>
       <c r="S11">
-        <v>1.014966</v>
+        <v>0.94401900000000005</v>
       </c>
       <c r="T11">
-        <v>1.002837</v>
+        <v>0.920817</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A12">
-        <v>0.89802199999999999</v>
+        <v>0.84825899999999999</v>
       </c>
       <c r="B12">
-        <v>0.89848300000000003</v>
+        <v>0.84947499999999998</v>
       </c>
       <c r="C12">
-        <v>0.90535699999999997</v>
+        <v>0.85473500000000002</v>
       </c>
       <c r="D12">
-        <v>0.90681800000000001</v>
+        <v>0.85464499999999999</v>
       </c>
       <c r="E12">
-        <v>0.91723500000000002</v>
+        <v>0.87084700000000004</v>
       </c>
       <c r="F12">
-        <v>0.92083300000000001</v>
+        <v>0.872251</v>
       </c>
       <c r="G12">
-        <v>0.92874199999999996</v>
+        <v>0.875224</v>
       </c>
       <c r="H12">
-        <v>0.92832800000000004</v>
+        <v>0.877494</v>
       </c>
       <c r="I12">
-        <v>0.93847800000000003</v>
+        <v>0.87993500000000002</v>
       </c>
       <c r="J12">
-        <v>0.93629200000000001</v>
+        <v>0.87895500000000004</v>
       </c>
       <c r="K12">
-        <v>0.94459400000000004</v>
+        <v>0.89728799999999997</v>
       </c>
       <c r="L12">
-        <v>0.94482600000000005</v>
+        <v>0.90217400000000003</v>
       </c>
       <c r="M12">
-        <v>0.95817799999999997</v>
+        <v>0.91003900000000004</v>
       </c>
       <c r="N12">
-        <v>0.96566200000000002</v>
+        <v>0.90946300000000002</v>
       </c>
       <c r="O12">
-        <v>0.97760499999999995</v>
+        <v>0.89953899999999998</v>
       </c>
       <c r="P12">
-        <v>0.98174600000000001</v>
+        <v>0.89591200000000004</v>
       </c>
       <c r="Q12">
-        <v>0.99294400000000005</v>
+        <v>0.91916399999999998</v>
       </c>
       <c r="R12">
-        <v>1.0019610000000001</v>
+        <v>0.91052299999999997</v>
       </c>
       <c r="S12">
-        <v>1.0036560000000001</v>
+        <v>0.933307</v>
       </c>
       <c r="T12">
-        <v>0.99613600000000002</v>
+        <v>0.91233699999999995</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A13">
-        <v>0.91249899999999995</v>
+        <v>0.85226299999999999</v>
       </c>
       <c r="B13">
-        <v>0.91220199999999996</v>
+        <v>0.85223199999999999</v>
       </c>
       <c r="C13">
-        <v>0.91880600000000001</v>
+        <v>0.85645499999999997</v>
       </c>
       <c r="D13">
-        <v>0.91963899999999998</v>
+        <v>0.85685699999999998</v>
       </c>
       <c r="E13">
-        <v>0.92803899999999995</v>
+        <v>0.87597400000000003</v>
       </c>
       <c r="F13">
-        <v>0.93123199999999995</v>
+        <v>0.87814099999999995</v>
       </c>
       <c r="G13">
-        <v>0.94127899999999998</v>
+        <v>0.88066100000000003</v>
       </c>
       <c r="H13">
-        <v>0.939608</v>
+        <v>0.88193600000000005</v>
       </c>
       <c r="I13">
-        <v>0.95293300000000003</v>
+        <v>0.883795</v>
       </c>
       <c r="J13">
-        <v>0.95280500000000001</v>
+        <v>0.88178999999999996</v>
       </c>
       <c r="K13">
-        <v>0.96042000000000005</v>
+        <v>0.90192399999999995</v>
       </c>
       <c r="L13">
-        <v>0.95532300000000003</v>
+        <v>0.90798400000000001</v>
       </c>
       <c r="M13">
-        <v>0.96938400000000002</v>
+        <v>0.91570300000000004</v>
       </c>
       <c r="N13">
-        <v>0.97806300000000002</v>
+        <v>0.91178300000000001</v>
       </c>
       <c r="O13">
-        <v>0.98905100000000001</v>
+        <v>0.90456700000000001</v>
       </c>
       <c r="P13">
-        <v>0.99701499999999998</v>
+        <v>0.90323600000000004</v>
       </c>
       <c r="Q13">
-        <v>1.0151269999999999</v>
+        <v>0.92628900000000003</v>
       </c>
       <c r="R13">
-        <v>1.0146869999999999</v>
+        <v>0.92229499999999998</v>
       </c>
       <c r="S13">
-        <v>1.0117480000000001</v>
+        <v>0.94861499999999999</v>
       </c>
       <c r="T13">
-        <v>0.998695</v>
+        <v>0.927624</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A14">
-        <v>0.93017000000000005</v>
+        <v>0.87867300000000004</v>
       </c>
       <c r="B14">
-        <v>0.930867</v>
+        <v>0.87809499999999996</v>
       </c>
       <c r="C14">
-        <v>0.93986899999999995</v>
+        <v>0.87967399999999996</v>
       </c>
       <c r="D14">
-        <v>0.94231799999999999</v>
+        <v>0.87880000000000003</v>
       </c>
       <c r="E14">
-        <v>0.95281499999999997</v>
+        <v>0.90046599999999999</v>
       </c>
       <c r="F14">
-        <v>0.95562999999999998</v>
+        <v>0.90443399999999996</v>
       </c>
       <c r="G14">
-        <v>0.96466300000000005</v>
+        <v>0.90861700000000001</v>
       </c>
       <c r="H14">
-        <v>0.96385399999999999</v>
+        <v>0.91227400000000003</v>
       </c>
       <c r="I14">
-        <v>0.97419</v>
+        <v>0.916157</v>
       </c>
       <c r="J14">
-        <v>0.97102599999999994</v>
+        <v>0.91102300000000003</v>
       </c>
       <c r="K14">
-        <v>0.98153100000000004</v>
+        <v>0.93653799999999998</v>
       </c>
       <c r="L14">
-        <v>0.97835799999999995</v>
+        <v>0.94143699999999997</v>
       </c>
       <c r="M14">
-        <v>0.99266600000000005</v>
+        <v>0.95419200000000004</v>
       </c>
       <c r="N14">
-        <v>1.0006619999999999</v>
+        <v>0.95337700000000003</v>
       </c>
       <c r="O14">
-        <v>1.01701</v>
+        <v>0.94948299999999997</v>
       </c>
       <c r="P14">
-        <v>1.024124</v>
+        <v>0.95552199999999998</v>
       </c>
       <c r="Q14">
-        <v>1.0500210000000001</v>
+        <v>0.97354600000000002</v>
       </c>
       <c r="R14">
-        <v>1.0589770000000001</v>
+        <v>0.96450899999999995</v>
       </c>
       <c r="S14">
-        <v>1.0581389999999999</v>
+        <v>0.99079300000000003</v>
       </c>
       <c r="T14">
-        <v>1.0602400000000001</v>
+        <v>0.95690699999999995</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A15">
-        <v>0.95564899999999997</v>
+        <v>0.90976599999999996</v>
       </c>
       <c r="B15">
-        <v>0.95526299999999997</v>
+        <v>0.90948700000000005</v>
       </c>
       <c r="C15">
-        <v>0.96037899999999998</v>
+        <v>0.91308800000000001</v>
       </c>
       <c r="D15">
-        <v>0.96499800000000002</v>
+        <v>0.914188</v>
       </c>
       <c r="E15">
-        <v>0.97921199999999997</v>
+        <v>0.940388</v>
       </c>
       <c r="F15">
-        <v>0.98386300000000004</v>
+        <v>0.94743900000000003</v>
       </c>
       <c r="G15">
-        <v>0.98964799999999997</v>
+        <v>0.94728400000000001</v>
       </c>
       <c r="H15">
-        <v>0.99085500000000004</v>
+        <v>0.95322700000000005</v>
       </c>
       <c r="I15">
-        <v>0.99987999999999999</v>
+        <v>0.96012799999999998</v>
       </c>
       <c r="J15">
-        <v>0.99993699999999996</v>
+        <v>0.956376</v>
       </c>
       <c r="K15">
-        <v>1.0089669999999999</v>
+        <v>0.98864399999999997</v>
       </c>
       <c r="L15">
-        <v>1.0011270000000001</v>
+        <v>0.99879700000000005</v>
       </c>
       <c r="M15">
-        <v>1.017485</v>
+        <v>1.010232</v>
       </c>
       <c r="N15">
-        <v>1.0306519999999999</v>
+        <v>1.0110239999999999</v>
       </c>
       <c r="O15">
-        <v>1.044387</v>
+        <v>1.006975</v>
       </c>
       <c r="P15">
-        <v>1.05358</v>
+        <v>1.0028980000000001</v>
       </c>
       <c r="Q15">
-        <v>1.0743689999999999</v>
+        <v>1.030356</v>
       </c>
       <c r="R15">
-        <v>1.093853</v>
+        <v>1.018456</v>
       </c>
       <c r="S15">
-        <v>1.0889489999999999</v>
+        <v>1.042322</v>
       </c>
       <c r="T15">
-        <v>1.103043</v>
+        <v>1.0061370000000001</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A16">
-        <v>0.92101100000000002</v>
+        <v>0.87212000000000001</v>
       </c>
       <c r="B16">
-        <v>0.92175099999999999</v>
+        <v>0.86969399999999997</v>
       </c>
       <c r="C16">
-        <v>0.92279199999999995</v>
+        <v>0.87356299999999998</v>
       </c>
       <c r="D16">
-        <v>0.92968600000000001</v>
+        <v>0.87533099999999997</v>
       </c>
       <c r="E16">
-        <v>0.94566600000000001</v>
+        <v>0.90063300000000002</v>
       </c>
       <c r="F16">
-        <v>0.951905</v>
+        <v>0.90530100000000002</v>
       </c>
       <c r="G16">
-        <v>0.95869300000000002</v>
+        <v>0.90193500000000004</v>
       </c>
       <c r="H16">
-        <v>0.95775299999999997</v>
+        <v>0.90876800000000002</v>
       </c>
       <c r="I16">
-        <v>0.96606400000000003</v>
+        <v>0.91667200000000004</v>
       </c>
       <c r="J16">
-        <v>0.96862400000000004</v>
+        <v>0.91455600000000004</v>
       </c>
       <c r="K16">
-        <v>0.98144799999999999</v>
+        <v>0.94758900000000001</v>
       </c>
       <c r="L16">
-        <v>0.97640000000000005</v>
+        <v>0.95953900000000003</v>
       </c>
       <c r="M16">
-        <v>0.99307199999999995</v>
+        <v>0.96809000000000001</v>
       </c>
       <c r="N16">
-        <v>1.0118720000000001</v>
+        <v>0.97114900000000004</v>
       </c>
       <c r="O16">
-        <v>1.0295049999999999</v>
+        <v>0.96846900000000002</v>
       </c>
       <c r="P16">
-        <v>1.0457289999999999</v>
+        <v>0.96712299999999995</v>
       </c>
       <c r="Q16">
-        <v>1.063469</v>
+        <v>1.0028699999999999</v>
       </c>
       <c r="R16">
-        <v>1.078244</v>
+        <v>0.99297599999999997</v>
       </c>
       <c r="S16">
-        <v>1.0764819999999999</v>
+        <v>1.014624</v>
       </c>
       <c r="T16">
-        <v>1.088203</v>
+        <v>0.97799700000000001</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A17">
-        <v>0.93583300000000003</v>
+        <v>0.86466699999999996</v>
       </c>
       <c r="B17">
-        <v>0.93914699999999995</v>
+        <v>0.86225700000000005</v>
       </c>
       <c r="C17">
-        <v>0.93951499999999999</v>
+        <v>0.86963299999999999</v>
       </c>
       <c r="D17">
-        <v>0.94795799999999997</v>
+        <v>0.873108</v>
       </c>
       <c r="E17">
-        <v>0.96257000000000004</v>
+        <v>0.89815199999999995</v>
       </c>
       <c r="F17">
-        <v>0.96819</v>
+        <v>0.90146099999999996</v>
       </c>
       <c r="G17">
-        <v>0.98000299999999996</v>
+        <v>0.89947600000000005</v>
       </c>
       <c r="H17">
-        <v>0.97679300000000002</v>
+        <v>0.91159999999999997</v>
       </c>
       <c r="I17">
-        <v>0.97734100000000002</v>
+        <v>0.92398400000000003</v>
       </c>
       <c r="J17">
-        <v>0.98449900000000001</v>
+        <v>0.91958499999999999</v>
       </c>
       <c r="K17">
-        <v>1.000556</v>
+        <v>0.96086700000000003</v>
       </c>
       <c r="L17">
-        <v>0.991645</v>
+        <v>0.97451600000000005</v>
       </c>
       <c r="M17">
-        <v>1.0074149999999999</v>
+        <v>0.983371</v>
       </c>
       <c r="N17">
-        <v>1.0334540000000001</v>
+        <v>0.98627500000000001</v>
       </c>
       <c r="O17">
-        <v>1.051849</v>
+        <v>0.98902299999999999</v>
       </c>
       <c r="P17">
-        <v>1.0693520000000001</v>
+        <v>0.99947200000000003</v>
       </c>
       <c r="Q17">
-        <v>1.0830169999999999</v>
+        <v>1.0568869999999999</v>
       </c>
       <c r="R17">
-        <v>1.1121110000000001</v>
+        <v>1.0502689999999999</v>
       </c>
       <c r="S17">
-        <v>1.1163460000000001</v>
+        <v>1.0768120000000001</v>
       </c>
       <c r="T17">
-        <v>1.116447</v>
+        <v>1.0054289999999999</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A18">
-        <v>0.90221300000000004</v>
+        <v>0.85006999999999999</v>
       </c>
       <c r="B18">
-        <v>0.90901900000000002</v>
+        <v>0.848634</v>
       </c>
       <c r="C18">
-        <v>0.91045100000000001</v>
+        <v>0.86122399999999999</v>
       </c>
       <c r="D18">
-        <v>0.91731700000000005</v>
+        <v>0.86388600000000004</v>
       </c>
       <c r="E18">
-        <v>0.932284</v>
+        <v>0.89090400000000003</v>
       </c>
       <c r="F18">
-        <v>0.92943699999999996</v>
+        <v>0.89223600000000003</v>
       </c>
       <c r="G18">
-        <v>0.94733000000000001</v>
+        <v>0.88650799999999996</v>
       </c>
       <c r="H18">
-        <v>0.94618599999999997</v>
+        <v>0.89977700000000005</v>
       </c>
       <c r="I18">
-        <v>0.95067800000000002</v>
+        <v>0.92132400000000003</v>
       </c>
       <c r="J18">
-        <v>0.95774199999999998</v>
+        <v>0.921014</v>
       </c>
       <c r="K18">
-        <v>0.97850999999999999</v>
+        <v>0.96994000000000002</v>
       </c>
       <c r="L18">
-        <v>0.97117399999999998</v>
+        <v>0.98912699999999998</v>
       </c>
       <c r="M18">
-        <v>0.98229100000000003</v>
+        <v>0.98861699999999997</v>
       </c>
       <c r="N18">
-        <v>1.008148</v>
+        <v>0.99015299999999995</v>
       </c>
       <c r="O18">
-        <v>1.031425</v>
+        <v>0.99453599999999998</v>
       </c>
       <c r="P18">
-        <v>1.054443</v>
+        <v>0.99120600000000003</v>
       </c>
       <c r="Q18">
-        <v>1.0734399999999999</v>
+        <v>1.0512349999999999</v>
       </c>
       <c r="R18">
-        <v>1.090724</v>
+        <v>1.046268</v>
       </c>
       <c r="S18">
-        <v>1.096714</v>
+        <v>1.0711949999999999</v>
       </c>
       <c r="T18">
-        <v>1.1179250000000001</v>
+        <v>1.018195</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A19">
-        <v>0.925813</v>
+        <v>0.83448999999999995</v>
       </c>
       <c r="B19">
-        <v>0.92349499999999995</v>
+        <v>0.83304699999999998</v>
       </c>
       <c r="C19">
-        <v>0.92117499999999997</v>
+        <v>0.84945199999999998</v>
       </c>
       <c r="D19">
-        <v>0.91792700000000005</v>
+        <v>0.84699599999999997</v>
       </c>
       <c r="E19">
-        <v>0.93702600000000003</v>
+        <v>0.88851400000000003</v>
       </c>
       <c r="F19">
-        <v>0.93560600000000005</v>
+        <v>0.89595100000000005</v>
       </c>
       <c r="G19">
-        <v>0.95268200000000003</v>
+        <v>0.89075499999999996</v>
       </c>
       <c r="H19">
-        <v>0.95783300000000005</v>
+        <v>0.92346200000000001</v>
       </c>
       <c r="I19">
-        <v>0.96376600000000001</v>
+        <v>0.93052900000000005</v>
       </c>
       <c r="J19">
-        <v>0.97101800000000005</v>
+        <v>0.93807499999999999</v>
       </c>
       <c r="K19">
-        <v>1.0043949999999999</v>
+        <v>0.98027900000000001</v>
       </c>
       <c r="L19">
-        <v>0.99819100000000005</v>
+        <v>0.99108399999999996</v>
       </c>
       <c r="M19">
-        <v>1.019722</v>
+        <v>0.98167199999999999</v>
       </c>
       <c r="N19">
-        <v>1.054243</v>
+        <v>0.98353100000000004</v>
       </c>
       <c r="O19">
-        <v>1.0776939999999999</v>
+        <v>0.98774799999999996</v>
       </c>
       <c r="P19">
-        <v>1.1026</v>
+        <v>1.003347</v>
       </c>
       <c r="Q19">
-        <v>1.145778</v>
+        <v>1.052567</v>
       </c>
       <c r="R19">
-        <v>1.169071</v>
+        <v>1.0754429999999999</v>
       </c>
       <c r="S19">
-        <v>1.253717</v>
+        <v>1.1285069999999999</v>
       </c>
       <c r="T19">
-        <v>1.2395830000000001</v>
+        <v>1.0999479999999999</v>
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A20">
-        <v>0.81850599999999996</v>
+        <v>0.73716800000000005</v>
       </c>
       <c r="B20">
-        <v>0.81609399999999999</v>
+        <v>0.73618899999999998</v>
       </c>
       <c r="C20">
-        <v>0.81367900000000004</v>
+        <v>0.73423099999999997</v>
       </c>
       <c r="D20">
-        <v>0.81206900000000004</v>
+        <v>0.73227100000000001</v>
       </c>
       <c r="E20">
-        <v>0.80965200000000004</v>
+        <v>0.77449299999999999</v>
       </c>
       <c r="F20">
-        <v>0.80884599999999995</v>
+        <v>0.77244999999999997</v>
       </c>
       <c r="G20">
-        <v>0.86837699999999995</v>
+        <v>0.76835900000000001</v>
       </c>
       <c r="H20">
-        <v>0.86666799999999999</v>
+        <v>0.81570299999999996</v>
       </c>
       <c r="I20">
-        <v>0.86238999999999999</v>
+        <v>0.81248900000000002</v>
       </c>
       <c r="J20">
-        <v>0.89637100000000003</v>
+        <v>0.80604900000000002</v>
       </c>
       <c r="K20">
-        <v>0.93660399999999999</v>
+        <v>0.94368799999999997</v>
       </c>
       <c r="L20">
-        <v>0.93203199999999997</v>
+        <v>0.94013800000000003</v>
       </c>
       <c r="M20">
-        <v>0.92562</v>
+        <v>0.93064000000000002</v>
       </c>
       <c r="N20">
-        <v>1.0251699999999999</v>
+        <v>0.91511299999999995</v>
       </c>
       <c r="O20">
-        <v>1.014303</v>
+        <v>0.90188299999999999</v>
       </c>
       <c r="P20">
-        <v>1.0043839999999999</v>
+        <v>0.88004700000000002</v>
       </c>
       <c r="Q20">
-        <v>0.98943400000000004</v>
+        <v>0.85797400000000001</v>
       </c>
       <c r="R20">
-        <v>0.96734799999999999</v>
+        <v>0.839395</v>
       </c>
       <c r="S20">
-        <v>1.2121630000000001</v>
+        <v>1.0483439999999999</v>
       </c>
       <c r="T20">
-        <v>1.150015</v>
+        <v>1.2424109999999999</v>
       </c>
     </row>
   </sheetData>

--- a/TMVA/FOM_small.xlsx
+++ b/TMVA/FOM_small.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\purol\OneDrive\바탕 화면\github\Belle2_script\TMVA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F94B995-4F38-41F4-8178-E275611BCD24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{613EC611-0383-434B-81B1-E0A464855040}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/TMVA/FOM_small.xlsx
+++ b/TMVA/FOM_small.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\purol\OneDrive\바탕 화면\github\Belle2_script\TMVA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{613EC611-0383-434B-81B1-E0A464855040}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB69E62E-C32D-4152-880A-DEFF3A4A25DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,9 +24,13 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -40,6 +44,13 @@
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
     </font>
   </fonts>
   <fills count="2">
@@ -62,8 +73,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -348,1243 +360,1243 @@
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.45">
-      <c r="A1">
-        <v>0.76303100000000001</v>
+      <c r="A1" s="1">
+        <v>0.669346</v>
       </c>
       <c r="B1">
-        <v>0.76717900000000006</v>
+        <v>0.66735999999999995</v>
       </c>
       <c r="C1">
-        <v>0.77315599999999995</v>
+        <v>0.667624</v>
       </c>
       <c r="D1">
-        <v>0.77193699999999998</v>
+        <v>0.66664500000000004</v>
       </c>
       <c r="E1">
-        <v>0.77916399999999997</v>
+        <v>0.66824899999999998</v>
       </c>
       <c r="F1">
-        <v>0.777721</v>
+        <v>0.66706600000000005</v>
       </c>
       <c r="G1">
-        <v>0.78299799999999997</v>
+        <v>0.67020299999999999</v>
       </c>
       <c r="H1">
-        <v>0.78242599999999995</v>
+        <v>0.67311900000000002</v>
       </c>
       <c r="I1">
-        <v>0.78178899999999996</v>
+        <v>0.67248600000000003</v>
       </c>
       <c r="J1">
-        <v>0.78102800000000006</v>
+        <v>0.66652100000000003</v>
       </c>
       <c r="K1">
-        <v>0.79250399999999999</v>
+        <v>0.66783700000000001</v>
       </c>
       <c r="L1">
-        <v>0.79783099999999996</v>
+        <v>0.67524099999999998</v>
       </c>
       <c r="M1">
-        <v>0.79895899999999997</v>
+        <v>0.67705599999999999</v>
       </c>
       <c r="N1">
-        <v>0.796574</v>
+        <v>0.67364400000000002</v>
       </c>
       <c r="O1">
-        <v>0.79680499999999999</v>
+        <v>0.66529499999999997</v>
       </c>
       <c r="P1">
-        <v>0.79417199999999999</v>
+        <v>0.67052900000000004</v>
       </c>
       <c r="Q1">
-        <v>0.80876800000000004</v>
+        <v>0.66559199999999996</v>
       </c>
       <c r="R1">
-        <v>0.80239899999999997</v>
+        <v>0.64706699999999995</v>
       </c>
       <c r="S1">
-        <v>0.81112700000000004</v>
+        <v>0.63636999999999999</v>
       </c>
       <c r="T1">
-        <v>0.76530600000000004</v>
+        <v>0.60753800000000002</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A2">
-        <v>0.76319099999999995</v>
+        <v>0.683195</v>
       </c>
       <c r="B2">
-        <v>0.76688699999999999</v>
+        <v>0.68174400000000002</v>
       </c>
       <c r="C2">
-        <v>0.77227500000000004</v>
+        <v>0.68253799999999998</v>
       </c>
       <c r="D2">
-        <v>0.77059100000000003</v>
+        <v>0.68187900000000001</v>
       </c>
       <c r="E2">
-        <v>0.77803</v>
+        <v>0.68421299999999996</v>
       </c>
       <c r="F2">
-        <v>0.77711300000000005</v>
+        <v>0.68351300000000004</v>
       </c>
       <c r="G2">
-        <v>0.78183999999999998</v>
+        <v>0.68252500000000005</v>
       </c>
       <c r="H2">
-        <v>0.78199399999999997</v>
+        <v>0.68672999999999995</v>
       </c>
       <c r="I2">
-        <v>0.78066599999999997</v>
+        <v>0.685446</v>
       </c>
       <c r="J2">
-        <v>0.77902499999999997</v>
+        <v>0.67818699999999998</v>
       </c>
       <c r="K2">
-        <v>0.79094299999999995</v>
+        <v>0.68060399999999999</v>
       </c>
       <c r="L2">
-        <v>0.79646499999999998</v>
+        <v>0.687531</v>
       </c>
       <c r="M2">
-        <v>0.79790799999999995</v>
+        <v>0.69020800000000004</v>
       </c>
       <c r="N2">
-        <v>0.79695099999999996</v>
+        <v>0.68626100000000001</v>
       </c>
       <c r="O2">
-        <v>0.79877699999999996</v>
+        <v>0.67827400000000004</v>
       </c>
       <c r="P2">
-        <v>0.79669699999999999</v>
+        <v>0.68354899999999996</v>
       </c>
       <c r="Q2">
-        <v>0.81138399999999999</v>
+        <v>0.68027300000000002</v>
       </c>
       <c r="R2">
-        <v>0.80667100000000003</v>
+        <v>0.66257999999999995</v>
       </c>
       <c r="S2">
-        <v>0.81292699999999996</v>
+        <v>0.65502899999999997</v>
       </c>
       <c r="T2">
-        <v>0.76719199999999999</v>
+        <v>0.62368599999999996</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A3">
-        <v>0.76848300000000003</v>
+        <v>0.68518900000000005</v>
       </c>
       <c r="B3">
-        <v>0.77278199999999997</v>
+        <v>0.68400099999999997</v>
       </c>
       <c r="C3">
-        <v>0.77874299999999996</v>
+        <v>0.68379599999999996</v>
       </c>
       <c r="D3">
-        <v>0.77732699999999999</v>
+        <v>0.68326299999999995</v>
       </c>
       <c r="E3">
-        <v>0.78492600000000001</v>
+        <v>0.68583099999999997</v>
       </c>
       <c r="F3">
-        <v>0.78452</v>
+        <v>0.68524600000000002</v>
       </c>
       <c r="G3">
-        <v>0.79018999999999995</v>
+        <v>0.68503800000000004</v>
       </c>
       <c r="H3">
-        <v>0.79064999999999996</v>
+        <v>0.68852100000000005</v>
       </c>
       <c r="I3">
-        <v>0.78991500000000003</v>
+        <v>0.68783099999999997</v>
       </c>
       <c r="J3">
-        <v>0.78878300000000001</v>
+        <v>0.68071300000000001</v>
       </c>
       <c r="K3">
-        <v>0.79983599999999999</v>
+        <v>0.68165699999999996</v>
       </c>
       <c r="L3">
-        <v>0.80628100000000003</v>
+        <v>0.68898300000000001</v>
       </c>
       <c r="M3">
-        <v>0.80883700000000003</v>
+        <v>0.692747</v>
       </c>
       <c r="N3">
-        <v>0.809531</v>
+        <v>0.69018800000000002</v>
       </c>
       <c r="O3">
-        <v>0.80988199999999999</v>
+        <v>0.68355600000000005</v>
       </c>
       <c r="P3">
-        <v>0.80793599999999999</v>
+        <v>0.69005700000000003</v>
       </c>
       <c r="Q3">
-        <v>0.82203800000000005</v>
+        <v>0.686581</v>
       </c>
       <c r="R3">
-        <v>0.81820400000000004</v>
+        <v>0.66771000000000003</v>
       </c>
       <c r="S3">
-        <v>0.82355999999999996</v>
+        <v>0.66234800000000005</v>
       </c>
       <c r="T3">
-        <v>0.78308199999999994</v>
+        <v>0.62651199999999996</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A4">
-        <v>0.77410000000000001</v>
+        <v>0.69467599999999996</v>
       </c>
       <c r="B4">
-        <v>0.77617499999999995</v>
+        <v>0.69406000000000001</v>
       </c>
       <c r="C4">
-        <v>0.78073300000000001</v>
+        <v>0.69307399999999997</v>
       </c>
       <c r="D4">
-        <v>0.77954800000000002</v>
+        <v>0.69304699999999997</v>
       </c>
       <c r="E4">
-        <v>0.78691999999999995</v>
+        <v>0.69371899999999997</v>
       </c>
       <c r="F4">
-        <v>0.78696100000000002</v>
+        <v>0.69378099999999998</v>
       </c>
       <c r="G4">
-        <v>0.79294100000000001</v>
+        <v>0.69415000000000004</v>
       </c>
       <c r="H4">
-        <v>0.79393100000000005</v>
+        <v>0.69730000000000003</v>
       </c>
       <c r="I4">
-        <v>0.79438399999999998</v>
+        <v>0.69660100000000003</v>
       </c>
       <c r="J4">
-        <v>0.79400199999999999</v>
+        <v>0.68942000000000003</v>
       </c>
       <c r="K4">
-        <v>0.80581199999999997</v>
+        <v>0.68944700000000003</v>
       </c>
       <c r="L4">
-        <v>0.81063200000000002</v>
+        <v>0.69806699999999999</v>
       </c>
       <c r="M4">
-        <v>0.81374899999999994</v>
+        <v>0.70369700000000002</v>
       </c>
       <c r="N4">
-        <v>0.81377900000000003</v>
+        <v>0.70199</v>
       </c>
       <c r="O4">
-        <v>0.81520599999999999</v>
+        <v>0.69584100000000004</v>
       </c>
       <c r="P4">
-        <v>0.81277100000000002</v>
+        <v>0.69836699999999996</v>
       </c>
       <c r="Q4">
-        <v>0.82717399999999996</v>
+        <v>0.69449399999999994</v>
       </c>
       <c r="R4">
-        <v>0.823214</v>
+        <v>0.67466800000000005</v>
       </c>
       <c r="S4">
-        <v>0.82879700000000001</v>
+        <v>0.66903999999999997</v>
       </c>
       <c r="T4">
-        <v>0.78959299999999999</v>
+        <v>0.63780099999999995</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A5">
-        <v>0.78969500000000004</v>
+        <v>0.69684999999999997</v>
       </c>
       <c r="B5">
-        <v>0.792381</v>
+        <v>0.69634200000000002</v>
       </c>
       <c r="C5">
-        <v>0.79723100000000002</v>
+        <v>0.69606999999999997</v>
       </c>
       <c r="D5">
-        <v>0.79647999999999997</v>
+        <v>0.69378899999999999</v>
       </c>
       <c r="E5">
-        <v>0.80440500000000004</v>
+        <v>0.695245</v>
       </c>
       <c r="F5">
-        <v>0.80386800000000003</v>
+        <v>0.69565600000000005</v>
       </c>
       <c r="G5">
-        <v>0.81095600000000001</v>
+        <v>0.69502900000000001</v>
       </c>
       <c r="H5">
-        <v>0.81183499999999997</v>
+        <v>0.69721</v>
       </c>
       <c r="I5">
-        <v>0.81208199999999997</v>
+        <v>0.696855</v>
       </c>
       <c r="J5">
-        <v>0.812384</v>
+        <v>0.689832</v>
       </c>
       <c r="K5">
-        <v>0.826515</v>
+        <v>0.68998599999999999</v>
       </c>
       <c r="L5">
-        <v>0.83024100000000001</v>
+        <v>0.69976300000000002</v>
       </c>
       <c r="M5">
-        <v>0.83331</v>
+        <v>0.70711299999999999</v>
       </c>
       <c r="N5">
-        <v>0.83246900000000001</v>
+        <v>0.70485799999999998</v>
       </c>
       <c r="O5">
-        <v>0.83157499999999995</v>
+        <v>0.69798400000000005</v>
       </c>
       <c r="P5">
-        <v>0.82969899999999996</v>
+        <v>0.70160199999999995</v>
       </c>
       <c r="Q5">
-        <v>0.84552300000000002</v>
+        <v>0.69879899999999995</v>
       </c>
       <c r="R5">
-        <v>0.83451600000000004</v>
+        <v>0.67953300000000005</v>
       </c>
       <c r="S5">
-        <v>0.83774000000000004</v>
+        <v>0.67749599999999999</v>
       </c>
       <c r="T5">
-        <v>0.803041</v>
+        <v>0.64928699999999995</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A6">
-        <v>0.79650900000000002</v>
+        <v>0.70022700000000004</v>
       </c>
       <c r="B6">
-        <v>0.79988300000000001</v>
+        <v>0.69984900000000005</v>
       </c>
       <c r="C6">
-        <v>0.80443699999999996</v>
+        <v>0.70013000000000003</v>
       </c>
       <c r="D6">
-        <v>0.80422800000000005</v>
+        <v>0.69656799999999996</v>
       </c>
       <c r="E6">
-        <v>0.81328900000000004</v>
+        <v>0.69846900000000001</v>
       </c>
       <c r="F6">
-        <v>0.81356300000000004</v>
+        <v>0.69928400000000002</v>
       </c>
       <c r="G6">
-        <v>0.81952700000000001</v>
+        <v>0.69760999999999995</v>
       </c>
       <c r="H6">
-        <v>0.81937000000000004</v>
+        <v>0.69923999999999997</v>
       </c>
       <c r="I6">
-        <v>0.82031799999999999</v>
+        <v>0.69795099999999999</v>
       </c>
       <c r="J6">
-        <v>0.82006500000000004</v>
+        <v>0.69087500000000002</v>
       </c>
       <c r="K6">
-        <v>0.83673200000000003</v>
+        <v>0.69139799999999996</v>
       </c>
       <c r="L6">
-        <v>0.84148400000000001</v>
+        <v>0.69853600000000005</v>
       </c>
       <c r="M6">
-        <v>0.84578299999999995</v>
+        <v>0.70695399999999997</v>
       </c>
       <c r="N6">
-        <v>0.84350899999999995</v>
+        <v>0.70511500000000005</v>
       </c>
       <c r="O6">
-        <v>0.84414</v>
+        <v>0.69859499999999997</v>
       </c>
       <c r="P6">
-        <v>0.84304400000000002</v>
+        <v>0.70138999999999996</v>
       </c>
       <c r="Q6">
-        <v>0.86116599999999999</v>
+        <v>0.69821999999999995</v>
       </c>
       <c r="R6">
-        <v>0.84917200000000004</v>
+        <v>0.67742100000000005</v>
       </c>
       <c r="S6">
-        <v>0.85472000000000004</v>
+        <v>0.67311500000000002</v>
       </c>
       <c r="T6">
-        <v>0.824214</v>
+        <v>0.64365000000000006</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A7">
-        <v>0.80183199999999999</v>
+        <v>0.69672900000000004</v>
       </c>
       <c r="B7">
-        <v>0.80593000000000004</v>
+        <v>0.69704500000000003</v>
       </c>
       <c r="C7">
-        <v>0.81152000000000002</v>
+        <v>0.69762500000000005</v>
       </c>
       <c r="D7">
-        <v>0.812249</v>
+        <v>0.69427499999999998</v>
       </c>
       <c r="E7">
-        <v>0.82123699999999999</v>
+        <v>0.69656499999999999</v>
       </c>
       <c r="F7">
-        <v>0.82101500000000005</v>
+        <v>0.69752199999999998</v>
       </c>
       <c r="G7">
-        <v>0.82556799999999997</v>
+        <v>0.69594900000000004</v>
       </c>
       <c r="H7">
-        <v>0.82643</v>
+        <v>0.69487500000000002</v>
       </c>
       <c r="I7">
-        <v>0.82722499999999999</v>
+        <v>0.69386999999999999</v>
       </c>
       <c r="J7">
-        <v>0.82591499999999995</v>
+        <v>0.68693899999999997</v>
       </c>
       <c r="K7">
-        <v>0.84109999999999996</v>
+        <v>0.68801999999999996</v>
       </c>
       <c r="L7">
-        <v>0.84538999999999997</v>
+        <v>0.69272999999999996</v>
       </c>
       <c r="M7">
-        <v>0.84775199999999995</v>
+        <v>0.70138100000000003</v>
       </c>
       <c r="N7">
-        <v>0.846221</v>
+        <v>0.70010399999999995</v>
       </c>
       <c r="O7">
-        <v>0.84484199999999998</v>
+        <v>0.69059800000000005</v>
       </c>
       <c r="P7">
-        <v>0.84445400000000004</v>
+        <v>0.69223800000000002</v>
       </c>
       <c r="Q7">
-        <v>0.86527299999999996</v>
+        <v>0.69021999999999994</v>
       </c>
       <c r="R7">
-        <v>0.85533899999999996</v>
+        <v>0.66925299999999999</v>
       </c>
       <c r="S7">
-        <v>0.86013799999999996</v>
+        <v>0.66496999999999995</v>
       </c>
       <c r="T7">
-        <v>0.83543599999999996</v>
+        <v>0.63624599999999998</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A8">
-        <v>0.80659000000000003</v>
+        <v>0.70410899999999998</v>
       </c>
       <c r="B8">
-        <v>0.81147800000000003</v>
+        <v>0.70491499999999996</v>
       </c>
       <c r="C8">
-        <v>0.81650500000000004</v>
+        <v>0.70447599999999999</v>
       </c>
       <c r="D8">
-        <v>0.81786700000000001</v>
+        <v>0.70187100000000002</v>
       </c>
       <c r="E8">
-        <v>0.82808999999999999</v>
+        <v>0.70464899999999997</v>
       </c>
       <c r="F8">
-        <v>0.82744499999999999</v>
+        <v>0.70600399999999996</v>
       </c>
       <c r="G8">
-        <v>0.83127799999999996</v>
+        <v>0.70544499999999999</v>
       </c>
       <c r="H8">
-        <v>0.83173699999999995</v>
+        <v>0.70497799999999999</v>
       </c>
       <c r="I8">
-        <v>0.833457</v>
+        <v>0.70484199999999997</v>
       </c>
       <c r="J8">
-        <v>0.83309599999999995</v>
+        <v>0.69529300000000005</v>
       </c>
       <c r="K8">
-        <v>0.85052799999999995</v>
+        <v>0.69703599999999999</v>
       </c>
       <c r="L8">
-        <v>0.85741599999999996</v>
+        <v>0.70330700000000002</v>
       </c>
       <c r="M8">
-        <v>0.86128000000000005</v>
+        <v>0.71301700000000001</v>
       </c>
       <c r="N8">
-        <v>0.85800699999999996</v>
+        <v>0.70934200000000003</v>
       </c>
       <c r="O8">
-        <v>0.85480699999999998</v>
+        <v>0.70053299999999996</v>
       </c>
       <c r="P8">
-        <v>0.85337300000000005</v>
+        <v>0.69975299999999996</v>
       </c>
       <c r="Q8">
-        <v>0.87690900000000005</v>
+        <v>0.69497200000000003</v>
       </c>
       <c r="R8">
-        <v>0.86629999999999996</v>
+        <v>0.675929</v>
       </c>
       <c r="S8">
-        <v>0.87399499999999997</v>
+        <v>0.67179100000000003</v>
       </c>
       <c r="T8">
-        <v>0.855904</v>
+        <v>0.64155899999999999</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A9">
-        <v>0.82120400000000005</v>
+        <v>0.70882400000000001</v>
       </c>
       <c r="B9">
-        <v>0.82729699999999995</v>
+        <v>0.71014100000000002</v>
       </c>
       <c r="C9">
-        <v>0.83237499999999998</v>
+        <v>0.70989199999999997</v>
       </c>
       <c r="D9">
-        <v>0.83204</v>
+        <v>0.70786199999999999</v>
       </c>
       <c r="E9">
-        <v>0.84277400000000002</v>
+        <v>0.71141600000000005</v>
       </c>
       <c r="F9">
-        <v>0.84290699999999996</v>
+        <v>0.71392</v>
       </c>
       <c r="G9">
-        <v>0.84511800000000004</v>
+        <v>0.71243199999999995</v>
       </c>
       <c r="H9">
-        <v>0.84668900000000002</v>
+        <v>0.71194199999999996</v>
       </c>
       <c r="I9">
-        <v>0.84931199999999996</v>
+        <v>0.71269400000000005</v>
       </c>
       <c r="J9">
-        <v>0.84875</v>
+        <v>0.70306599999999997</v>
       </c>
       <c r="K9">
-        <v>0.86773</v>
+        <v>0.70579499999999995</v>
       </c>
       <c r="L9">
-        <v>0.87555400000000005</v>
+        <v>0.713063</v>
       </c>
       <c r="M9">
-        <v>0.87747600000000003</v>
+        <v>0.71915700000000005</v>
       </c>
       <c r="N9">
-        <v>0.87362099999999998</v>
+        <v>0.71417900000000001</v>
       </c>
       <c r="O9">
-        <v>0.87304800000000005</v>
+        <v>0.70206400000000002</v>
       </c>
       <c r="P9">
-        <v>0.86774600000000002</v>
+        <v>0.70089500000000005</v>
       </c>
       <c r="Q9">
-        <v>0.892818</v>
+        <v>0.69545999999999997</v>
       </c>
       <c r="R9">
-        <v>0.88549699999999998</v>
+        <v>0.67769699999999999</v>
       </c>
       <c r="S9">
-        <v>0.90316600000000002</v>
+        <v>0.67643900000000001</v>
       </c>
       <c r="T9">
-        <v>0.86868000000000001</v>
+        <v>0.65065499999999998</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A10">
-        <v>0.82703099999999996</v>
+        <v>0.70643699999999998</v>
       </c>
       <c r="B10">
-        <v>0.83124799999999999</v>
+        <v>0.70819699999999997</v>
       </c>
       <c r="C10">
-        <v>0.836059</v>
+        <v>0.70657400000000004</v>
       </c>
       <c r="D10">
-        <v>0.83609699999999998</v>
+        <v>0.70484199999999997</v>
       </c>
       <c r="E10">
-        <v>0.84836100000000003</v>
+        <v>0.70788399999999996</v>
       </c>
       <c r="F10">
-        <v>0.84767199999999998</v>
+        <v>0.70903300000000002</v>
       </c>
       <c r="G10">
-        <v>0.85047799999999996</v>
+        <v>0.70812200000000003</v>
       </c>
       <c r="H10">
-        <v>0.85107500000000003</v>
+        <v>0.70632899999999998</v>
       </c>
       <c r="I10">
-        <v>0.85275800000000002</v>
+        <v>0.707978</v>
       </c>
       <c r="J10">
-        <v>0.85131900000000005</v>
+        <v>0.698627</v>
       </c>
       <c r="K10">
-        <v>0.87273000000000001</v>
+        <v>0.70007900000000001</v>
       </c>
       <c r="L10">
-        <v>0.88175000000000003</v>
+        <v>0.70662400000000003</v>
       </c>
       <c r="M10">
-        <v>0.88500400000000001</v>
+        <v>0.71157800000000004</v>
       </c>
       <c r="N10">
-        <v>0.882606</v>
+        <v>0.70510499999999998</v>
       </c>
       <c r="O10">
-        <v>0.87930699999999995</v>
+        <v>0.69056899999999999</v>
       </c>
       <c r="P10">
-        <v>0.87525299999999995</v>
+        <v>0.69171899999999997</v>
       </c>
       <c r="Q10">
-        <v>0.90305800000000003</v>
+        <v>0.68646099999999999</v>
       </c>
       <c r="R10">
-        <v>0.89626600000000001</v>
+        <v>0.66992300000000005</v>
       </c>
       <c r="S10">
-        <v>0.912385</v>
+        <v>0.67069599999999996</v>
       </c>
       <c r="T10">
-        <v>0.87752300000000005</v>
+        <v>0.654053</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A11">
-        <v>0.84440999999999999</v>
+        <v>0.710341</v>
       </c>
       <c r="B11">
-        <v>0.84820600000000002</v>
+        <v>0.713476</v>
       </c>
       <c r="C11">
-        <v>0.85270800000000002</v>
+        <v>0.712453</v>
       </c>
       <c r="D11">
-        <v>0.85360999999999998</v>
+        <v>0.70974700000000002</v>
       </c>
       <c r="E11">
-        <v>0.86824299999999999</v>
+        <v>0.71361699999999995</v>
       </c>
       <c r="F11">
-        <v>0.86826400000000004</v>
+        <v>0.71343900000000005</v>
       </c>
       <c r="G11">
-        <v>0.87052099999999999</v>
+        <v>0.713866</v>
       </c>
       <c r="H11">
-        <v>0.871861</v>
+        <v>0.712808</v>
       </c>
       <c r="I11">
-        <v>0.87561</v>
+        <v>0.71608499999999997</v>
       </c>
       <c r="J11">
-        <v>0.87379700000000005</v>
+        <v>0.70686499999999997</v>
       </c>
       <c r="K11">
-        <v>0.89164900000000002</v>
+        <v>0.70910600000000001</v>
       </c>
       <c r="L11">
-        <v>0.89731399999999994</v>
+        <v>0.71451299999999995</v>
       </c>
       <c r="M11">
-        <v>0.90379699999999996</v>
+        <v>0.72124699999999997</v>
       </c>
       <c r="N11">
-        <v>0.903115</v>
+        <v>0.71589199999999997</v>
       </c>
       <c r="O11">
-        <v>0.89744199999999996</v>
+        <v>0.70212699999999995</v>
       </c>
       <c r="P11">
-        <v>0.89410000000000001</v>
+        <v>0.70759300000000003</v>
       </c>
       <c r="Q11">
-        <v>0.92767900000000003</v>
+        <v>0.69906800000000002</v>
       </c>
       <c r="R11">
-        <v>0.92099500000000001</v>
+        <v>0.682338</v>
       </c>
       <c r="S11">
-        <v>0.94401900000000005</v>
+        <v>0.68105199999999999</v>
       </c>
       <c r="T11">
-        <v>0.920817</v>
+        <v>0.66129599999999999</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A12">
-        <v>0.84825899999999999</v>
+        <v>0.71605600000000003</v>
       </c>
       <c r="B12">
-        <v>0.84947499999999998</v>
+        <v>0.72062700000000002</v>
       </c>
       <c r="C12">
-        <v>0.85473500000000002</v>
+        <v>0.72032799999999997</v>
       </c>
       <c r="D12">
-        <v>0.85464499999999999</v>
+        <v>0.71852199999999999</v>
       </c>
       <c r="E12">
-        <v>0.87084700000000004</v>
+        <v>0.72190200000000004</v>
       </c>
       <c r="F12">
-        <v>0.872251</v>
+        <v>0.722939</v>
       </c>
       <c r="G12">
-        <v>0.875224</v>
+        <v>0.72070599999999996</v>
       </c>
       <c r="H12">
-        <v>0.877494</v>
+        <v>0.718476</v>
       </c>
       <c r="I12">
-        <v>0.87993500000000002</v>
+        <v>0.72284499999999996</v>
       </c>
       <c r="J12">
-        <v>0.87895500000000004</v>
+        <v>0.71371700000000005</v>
       </c>
       <c r="K12">
-        <v>0.89728799999999997</v>
+        <v>0.71773200000000004</v>
       </c>
       <c r="L12">
-        <v>0.90217400000000003</v>
+        <v>0.72034799999999999</v>
       </c>
       <c r="M12">
-        <v>0.91003900000000004</v>
+        <v>0.72884199999999999</v>
       </c>
       <c r="N12">
-        <v>0.90946300000000002</v>
+        <v>0.72532799999999997</v>
       </c>
       <c r="O12">
-        <v>0.89953899999999998</v>
+        <v>0.70772999999999997</v>
       </c>
       <c r="P12">
-        <v>0.89591200000000004</v>
+        <v>0.71315799999999996</v>
       </c>
       <c r="Q12">
-        <v>0.91916399999999998</v>
+        <v>0.70629799999999998</v>
       </c>
       <c r="R12">
-        <v>0.91052299999999997</v>
+        <v>0.68691899999999995</v>
       </c>
       <c r="S12">
-        <v>0.933307</v>
+        <v>0.68765299999999996</v>
       </c>
       <c r="T12">
-        <v>0.91233699999999995</v>
+        <v>0.68007099999999998</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A13">
-        <v>0.85226299999999999</v>
+        <v>0.71741900000000003</v>
       </c>
       <c r="B13">
-        <v>0.85223199999999999</v>
+        <v>0.72153500000000004</v>
       </c>
       <c r="C13">
-        <v>0.85645499999999997</v>
+        <v>0.72150300000000001</v>
       </c>
       <c r="D13">
-        <v>0.85685699999999998</v>
+        <v>0.72069399999999995</v>
       </c>
       <c r="E13">
-        <v>0.87597400000000003</v>
+        <v>0.72544900000000001</v>
       </c>
       <c r="F13">
-        <v>0.87814099999999995</v>
+        <v>0.72531299999999999</v>
       </c>
       <c r="G13">
-        <v>0.88066100000000003</v>
+        <v>0.72207500000000002</v>
       </c>
       <c r="H13">
-        <v>0.88193600000000005</v>
+        <v>0.72057700000000002</v>
       </c>
       <c r="I13">
-        <v>0.883795</v>
+        <v>0.72742200000000001</v>
       </c>
       <c r="J13">
-        <v>0.88178999999999996</v>
+        <v>0.71805099999999999</v>
       </c>
       <c r="K13">
-        <v>0.90192399999999995</v>
+        <v>0.72331000000000001</v>
       </c>
       <c r="L13">
-        <v>0.90798400000000001</v>
+        <v>0.72804000000000002</v>
       </c>
       <c r="M13">
-        <v>0.91570300000000004</v>
+        <v>0.73980299999999999</v>
       </c>
       <c r="N13">
-        <v>0.91178300000000001</v>
+        <v>0.73631100000000005</v>
       </c>
       <c r="O13">
-        <v>0.90456700000000001</v>
+        <v>0.72006499999999996</v>
       </c>
       <c r="P13">
-        <v>0.90323600000000004</v>
+        <v>0.72744799999999998</v>
       </c>
       <c r="Q13">
-        <v>0.92628900000000003</v>
+        <v>0.72459499999999999</v>
       </c>
       <c r="R13">
-        <v>0.92229499999999998</v>
+        <v>0.706959</v>
       </c>
       <c r="S13">
-        <v>0.94861499999999999</v>
+        <v>0.69620000000000004</v>
       </c>
       <c r="T13">
-        <v>0.927624</v>
+        <v>0.68921699999999997</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A14">
-        <v>0.87867300000000004</v>
+        <v>0.72202999999999995</v>
       </c>
       <c r="B14">
-        <v>0.87809499999999996</v>
+        <v>0.72760000000000002</v>
       </c>
       <c r="C14">
-        <v>0.87967399999999996</v>
+        <v>0.72856799999999999</v>
       </c>
       <c r="D14">
-        <v>0.87880000000000003</v>
+        <v>0.72872899999999996</v>
       </c>
       <c r="E14">
-        <v>0.90046599999999999</v>
+        <v>0.73537300000000005</v>
       </c>
       <c r="F14">
-        <v>0.90443399999999996</v>
+        <v>0.73304400000000003</v>
       </c>
       <c r="G14">
-        <v>0.90861700000000001</v>
+        <v>0.73041100000000003</v>
       </c>
       <c r="H14">
-        <v>0.91227400000000003</v>
+        <v>0.73019800000000001</v>
       </c>
       <c r="I14">
-        <v>0.916157</v>
+        <v>0.73254600000000003</v>
       </c>
       <c r="J14">
-        <v>0.91102300000000003</v>
+        <v>0.72437700000000005</v>
       </c>
       <c r="K14">
-        <v>0.93653799999999998</v>
+        <v>0.73156699999999997</v>
       </c>
       <c r="L14">
-        <v>0.94143699999999997</v>
+        <v>0.73800900000000003</v>
       </c>
       <c r="M14">
-        <v>0.95419200000000004</v>
+        <v>0.75005900000000003</v>
       </c>
       <c r="N14">
-        <v>0.95337700000000003</v>
+        <v>0.74793600000000005</v>
       </c>
       <c r="O14">
-        <v>0.94948299999999997</v>
+        <v>0.732491</v>
       </c>
       <c r="P14">
-        <v>0.95552199999999998</v>
+        <v>0.74269600000000002</v>
       </c>
       <c r="Q14">
-        <v>0.97354600000000002</v>
+        <v>0.74166799999999999</v>
       </c>
       <c r="R14">
-        <v>0.96450899999999995</v>
+        <v>0.72856500000000002</v>
       </c>
       <c r="S14">
-        <v>0.99079300000000003</v>
+        <v>0.72197699999999998</v>
       </c>
       <c r="T14">
-        <v>0.95690699999999995</v>
+        <v>0.70225599999999999</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A15">
-        <v>0.90976599999999996</v>
+        <v>0.75023099999999998</v>
       </c>
       <c r="B15">
-        <v>0.90948700000000005</v>
+        <v>0.75834699999999999</v>
       </c>
       <c r="C15">
-        <v>0.91308800000000001</v>
+        <v>0.75783299999999998</v>
       </c>
       <c r="D15">
-        <v>0.914188</v>
+        <v>0.75668999999999997</v>
       </c>
       <c r="E15">
-        <v>0.940388</v>
+        <v>0.75897599999999998</v>
       </c>
       <c r="F15">
-        <v>0.94743900000000003</v>
+        <v>0.754104</v>
       </c>
       <c r="G15">
-        <v>0.94728400000000001</v>
+        <v>0.75265899999999997</v>
       </c>
       <c r="H15">
-        <v>0.95322700000000005</v>
+        <v>0.75473299999999999</v>
       </c>
       <c r="I15">
-        <v>0.96012799999999998</v>
+        <v>0.75233799999999995</v>
       </c>
       <c r="J15">
-        <v>0.956376</v>
+        <v>0.74437699999999996</v>
       </c>
       <c r="K15">
-        <v>0.98864399999999997</v>
+        <v>0.75085999999999997</v>
       </c>
       <c r="L15">
-        <v>0.99879700000000005</v>
+        <v>0.76165499999999997</v>
       </c>
       <c r="M15">
-        <v>1.010232</v>
+        <v>0.77762900000000001</v>
       </c>
       <c r="N15">
-        <v>1.0110239999999999</v>
+        <v>0.77456899999999995</v>
       </c>
       <c r="O15">
-        <v>1.006975</v>
+        <v>0.75907599999999997</v>
       </c>
       <c r="P15">
-        <v>1.0028980000000001</v>
+        <v>0.75814499999999996</v>
       </c>
       <c r="Q15">
-        <v>1.030356</v>
+        <v>0.76327599999999995</v>
       </c>
       <c r="R15">
-        <v>1.018456</v>
+        <v>0.75057700000000005</v>
       </c>
       <c r="S15">
-        <v>1.042322</v>
+        <v>0.74193699999999996</v>
       </c>
       <c r="T15">
-        <v>1.0061370000000001</v>
+        <v>0.70867000000000002</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A16">
-        <v>0.87212000000000001</v>
+        <v>0.74201399999999995</v>
       </c>
       <c r="B16">
-        <v>0.86969399999999997</v>
+        <v>0.75212100000000004</v>
       </c>
       <c r="C16">
-        <v>0.87356299999999998</v>
+        <v>0.74831099999999995</v>
       </c>
       <c r="D16">
-        <v>0.87533099999999997</v>
+        <v>0.747722</v>
       </c>
       <c r="E16">
-        <v>0.90063300000000002</v>
+        <v>0.75118600000000002</v>
       </c>
       <c r="F16">
-        <v>0.90530100000000002</v>
+        <v>0.74695699999999998</v>
       </c>
       <c r="G16">
-        <v>0.90193500000000004</v>
+        <v>0.74714199999999997</v>
       </c>
       <c r="H16">
-        <v>0.90876800000000002</v>
+        <v>0.75083599999999995</v>
       </c>
       <c r="I16">
-        <v>0.91667200000000004</v>
+        <v>0.750417</v>
       </c>
       <c r="J16">
-        <v>0.91455600000000004</v>
+        <v>0.74283299999999997</v>
       </c>
       <c r="K16">
-        <v>0.94758900000000001</v>
+        <v>0.75189399999999995</v>
       </c>
       <c r="L16">
-        <v>0.95953900000000003</v>
+        <v>0.76086600000000004</v>
       </c>
       <c r="M16">
-        <v>0.96809000000000001</v>
+        <v>0.778447</v>
       </c>
       <c r="N16">
-        <v>0.97114900000000004</v>
+        <v>0.77241199999999999</v>
       </c>
       <c r="O16">
-        <v>0.96846900000000002</v>
+        <v>0.75756999999999997</v>
       </c>
       <c r="P16">
-        <v>0.96712299999999995</v>
+        <v>0.75503900000000002</v>
       </c>
       <c r="Q16">
-        <v>1.0028699999999999</v>
+        <v>0.75894399999999995</v>
       </c>
       <c r="R16">
-        <v>0.99297599999999997</v>
+        <v>0.75446999999999997</v>
       </c>
       <c r="S16">
-        <v>1.014624</v>
+        <v>0.75149500000000002</v>
       </c>
       <c r="T16">
-        <v>0.97799700000000001</v>
+        <v>0.70629299999999995</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A17">
-        <v>0.86466699999999996</v>
+        <v>0.74586399999999997</v>
       </c>
       <c r="B17">
-        <v>0.86225700000000005</v>
+        <v>0.75412400000000002</v>
       </c>
       <c r="C17">
-        <v>0.86963299999999999</v>
+        <v>0.74978900000000004</v>
       </c>
       <c r="D17">
-        <v>0.873108</v>
+        <v>0.75106899999999999</v>
       </c>
       <c r="E17">
-        <v>0.89815199999999995</v>
+        <v>0.75866699999999998</v>
       </c>
       <c r="F17">
-        <v>0.90146099999999996</v>
+        <v>0.754637</v>
       </c>
       <c r="G17">
-        <v>0.89947600000000005</v>
+        <v>0.75100900000000004</v>
       </c>
       <c r="H17">
-        <v>0.91159999999999997</v>
+        <v>0.75811399999999995</v>
       </c>
       <c r="I17">
-        <v>0.92398400000000003</v>
+        <v>0.75894399999999995</v>
       </c>
       <c r="J17">
-        <v>0.91958499999999999</v>
+        <v>0.75234000000000001</v>
       </c>
       <c r="K17">
-        <v>0.96086700000000003</v>
+        <v>0.76736899999999997</v>
       </c>
       <c r="L17">
-        <v>0.97451600000000005</v>
+        <v>0.78331799999999996</v>
       </c>
       <c r="M17">
-        <v>0.983371</v>
+        <v>0.79724099999999998</v>
       </c>
       <c r="N17">
-        <v>0.98627500000000001</v>
+        <v>0.78745399999999999</v>
       </c>
       <c r="O17">
-        <v>0.98902299999999999</v>
+        <v>0.77364100000000002</v>
       </c>
       <c r="P17">
-        <v>0.99947200000000003</v>
+        <v>0.77683100000000005</v>
       </c>
       <c r="Q17">
-        <v>1.0568869999999999</v>
+        <v>0.77669900000000003</v>
       </c>
       <c r="R17">
-        <v>1.0502689999999999</v>
+        <v>0.76816300000000004</v>
       </c>
       <c r="S17">
-        <v>1.0768120000000001</v>
+        <v>0.76185999999999998</v>
       </c>
       <c r="T17">
-        <v>1.0054289999999999</v>
+        <v>0.71723499999999996</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A18">
-        <v>0.85006999999999999</v>
+        <v>0.73245000000000005</v>
       </c>
       <c r="B18">
-        <v>0.848634</v>
+        <v>0.73768699999999998</v>
       </c>
       <c r="C18">
-        <v>0.86122399999999999</v>
+        <v>0.73482400000000003</v>
       </c>
       <c r="D18">
-        <v>0.86388600000000004</v>
+        <v>0.73880100000000004</v>
       </c>
       <c r="E18">
-        <v>0.89090400000000003</v>
+        <v>0.75278199999999995</v>
       </c>
       <c r="F18">
-        <v>0.89223600000000003</v>
+        <v>0.74883900000000003</v>
       </c>
       <c r="G18">
-        <v>0.88650799999999996</v>
+        <v>0.74587999999999999</v>
       </c>
       <c r="H18">
-        <v>0.89977700000000005</v>
+        <v>0.74094599999999999</v>
       </c>
       <c r="I18">
-        <v>0.92132400000000003</v>
+        <v>0.74548199999999998</v>
       </c>
       <c r="J18">
-        <v>0.921014</v>
+        <v>0.74148599999999998</v>
       </c>
       <c r="K18">
-        <v>0.96994000000000002</v>
+        <v>0.75681399999999999</v>
       </c>
       <c r="L18">
-        <v>0.98912699999999998</v>
+        <v>0.78372900000000001</v>
       </c>
       <c r="M18">
-        <v>0.98861699999999997</v>
+        <v>0.77525100000000002</v>
       </c>
       <c r="N18">
-        <v>0.99015299999999995</v>
+        <v>0.767822</v>
       </c>
       <c r="O18">
-        <v>0.99453599999999998</v>
+        <v>0.75506499999999999</v>
       </c>
       <c r="P18">
-        <v>0.99120600000000003</v>
+        <v>0.75406499999999999</v>
       </c>
       <c r="Q18">
-        <v>1.0512349999999999</v>
+        <v>0.76786600000000005</v>
       </c>
       <c r="R18">
-        <v>1.046268</v>
+        <v>0.75867799999999996</v>
       </c>
       <c r="S18">
-        <v>1.0711949999999999</v>
+        <v>0.73536400000000002</v>
       </c>
       <c r="T18">
-        <v>1.018195</v>
+        <v>0.68667800000000001</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A19">
-        <v>0.83448999999999995</v>
+        <v>0.75150399999999995</v>
       </c>
       <c r="B19">
-        <v>0.83304699999999998</v>
+        <v>0.76620699999999997</v>
       </c>
       <c r="C19">
-        <v>0.84945199999999998</v>
+        <v>0.76278100000000004</v>
       </c>
       <c r="D19">
-        <v>0.84699599999999997</v>
+        <v>0.76003799999999999</v>
       </c>
       <c r="E19">
-        <v>0.88851400000000003</v>
+        <v>0.77584399999999998</v>
       </c>
       <c r="F19">
-        <v>0.89595100000000005</v>
+        <v>0.77234000000000003</v>
       </c>
       <c r="G19">
-        <v>0.89075499999999996</v>
+        <v>0.77093800000000001</v>
       </c>
       <c r="H19">
-        <v>0.92346200000000001</v>
+        <v>0.76742900000000003</v>
       </c>
       <c r="I19">
-        <v>0.93052900000000005</v>
+        <v>0.78516200000000003</v>
       </c>
       <c r="J19">
-        <v>0.93807499999999999</v>
+        <v>0.78157299999999996</v>
       </c>
       <c r="K19">
-        <v>0.98027900000000001</v>
+        <v>0.80011100000000002</v>
       </c>
       <c r="L19">
-        <v>0.99108399999999996</v>
+        <v>0.82048100000000002</v>
       </c>
       <c r="M19">
-        <v>0.98167199999999999</v>
+        <v>0.81218900000000005</v>
       </c>
       <c r="N19">
-        <v>0.98353100000000004</v>
+        <v>0.80614799999999998</v>
       </c>
       <c r="O19">
-        <v>0.98774799999999996</v>
+        <v>0.797068</v>
       </c>
       <c r="P19">
-        <v>1.003347</v>
+        <v>0.78872600000000004</v>
       </c>
       <c r="Q19">
-        <v>1.052567</v>
+        <v>0.82653699999999997</v>
       </c>
       <c r="R19">
-        <v>1.0754429999999999</v>
+        <v>0.80965200000000004</v>
       </c>
       <c r="S19">
-        <v>1.1285069999999999</v>
+        <v>0.77970499999999998</v>
       </c>
       <c r="T19">
-        <v>1.0999479999999999</v>
+        <v>0.74179099999999998</v>
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A20">
-        <v>0.73716800000000005</v>
+        <v>0.56753299999999995</v>
       </c>
       <c r="B20">
-        <v>0.73618899999999998</v>
+        <v>0.56753299999999995</v>
       </c>
       <c r="C20">
-        <v>0.73423099999999997</v>
+        <v>0.56642899999999996</v>
       </c>
       <c r="D20">
-        <v>0.73227100000000001</v>
+        <v>0.56532400000000005</v>
       </c>
       <c r="E20">
-        <v>0.77449299999999999</v>
+        <v>0.56532400000000005</v>
       </c>
       <c r="F20">
-        <v>0.77244999999999997</v>
+        <v>0.56532400000000005</v>
       </c>
       <c r="G20">
-        <v>0.76835900000000001</v>
+        <v>0.56532400000000005</v>
       </c>
       <c r="H20">
-        <v>0.81570299999999996</v>
+        <v>0.56089999999999995</v>
       </c>
       <c r="I20">
-        <v>0.81248900000000002</v>
+        <v>0.55979299999999999</v>
       </c>
       <c r="J20">
-        <v>0.80604900000000002</v>
+        <v>0.55979299999999999</v>
       </c>
       <c r="K20">
-        <v>0.94368799999999997</v>
+        <v>0.59992000000000001</v>
       </c>
       <c r="L20">
-        <v>0.94013800000000003</v>
+        <v>0.59992000000000001</v>
       </c>
       <c r="M20">
-        <v>0.93064000000000002</v>
+        <v>0.59523999999999999</v>
       </c>
       <c r="N20">
-        <v>0.91511299999999995</v>
+        <v>0.591723</v>
       </c>
       <c r="O20">
-        <v>0.90188299999999999</v>
+        <v>0.58467599999999997</v>
       </c>
       <c r="P20">
-        <v>0.88004700000000002</v>
+        <v>0.58114399999999999</v>
       </c>
       <c r="Q20">
-        <v>0.85797400000000001</v>
+        <v>0.61815100000000001</v>
       </c>
       <c r="R20">
-        <v>0.839395</v>
+        <v>0.614371</v>
       </c>
       <c r="S20">
-        <v>1.0483439999999999</v>
+        <v>0.59664600000000001</v>
       </c>
       <c r="T20">
-        <v>1.2424109999999999</v>
+        <v>0.55298899999999995</v>
       </c>
     </row>
   </sheetData>

--- a/TMVA/FOM_small.xlsx
+++ b/TMVA/FOM_small.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24701"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24729"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\purol\OneDrive\바탕 화면\github\Belle2_script\TMVA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB69E62E-C32D-4152-880A-DEFF3A4A25DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18772F22-8C8F-48CE-B741-B3436F775359}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,10 +22,6 @@
     </ext>
   </extLst>
 </workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -361,1242 +357,1242 @@
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A1" s="1">
-        <v>0.669346</v>
+        <v>0.50592499999999996</v>
       </c>
       <c r="B1">
-        <v>0.66735999999999995</v>
+        <v>0.50761299999999998</v>
       </c>
       <c r="C1">
-        <v>0.667624</v>
+        <v>0.503772</v>
       </c>
       <c r="D1">
-        <v>0.66664500000000004</v>
+        <v>0.50446199999999997</v>
       </c>
       <c r="E1">
-        <v>0.66824899999999998</v>
+        <v>0.51208299999999995</v>
       </c>
       <c r="F1">
-        <v>0.66706600000000005</v>
+        <v>0.506772</v>
       </c>
       <c r="G1">
-        <v>0.67020299999999999</v>
+        <v>0.50120200000000004</v>
       </c>
       <c r="H1">
-        <v>0.67311900000000002</v>
+        <v>0.49375999999999998</v>
       </c>
       <c r="I1">
-        <v>0.67248600000000003</v>
+        <v>0.49417499999999998</v>
       </c>
       <c r="J1">
-        <v>0.66652100000000003</v>
+        <v>0.48901800000000001</v>
       </c>
       <c r="K1">
-        <v>0.66783700000000001</v>
+        <v>0.49048900000000001</v>
       </c>
       <c r="L1">
-        <v>0.67524099999999998</v>
+        <v>0.48291800000000001</v>
       </c>
       <c r="M1">
-        <v>0.67705599999999999</v>
+        <v>0.48261300000000001</v>
       </c>
       <c r="N1">
-        <v>0.67364400000000002</v>
+        <v>0.48232799999999998</v>
       </c>
       <c r="O1">
-        <v>0.66529499999999997</v>
+        <v>0.47475299999999998</v>
       </c>
       <c r="P1">
-        <v>0.67052900000000004</v>
+        <v>0.46905799999999997</v>
       </c>
       <c r="Q1">
-        <v>0.66559199999999996</v>
+        <v>0.45779900000000001</v>
       </c>
       <c r="R1">
-        <v>0.64706699999999995</v>
+        <v>0.46878799999999998</v>
       </c>
       <c r="S1">
-        <v>0.63636999999999999</v>
+        <v>0.46063199999999999</v>
       </c>
       <c r="T1">
-        <v>0.60753800000000002</v>
+        <v>0.45801399999999998</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A2">
-        <v>0.683195</v>
+        <v>0.50601099999999999</v>
       </c>
       <c r="B2">
-        <v>0.68174400000000002</v>
+        <v>0.50973299999999999</v>
       </c>
       <c r="C2">
-        <v>0.68253799999999998</v>
+        <v>0.50605599999999995</v>
       </c>
       <c r="D2">
-        <v>0.68187900000000001</v>
+        <v>0.50903600000000004</v>
       </c>
       <c r="E2">
-        <v>0.68421299999999996</v>
+        <v>0.51889099999999999</v>
       </c>
       <c r="F2">
-        <v>0.68351300000000004</v>
+        <v>0.51348000000000005</v>
       </c>
       <c r="G2">
-        <v>0.68252500000000005</v>
+        <v>0.50959299999999996</v>
       </c>
       <c r="H2">
-        <v>0.68672999999999995</v>
+        <v>0.50214099999999995</v>
       </c>
       <c r="I2">
-        <v>0.685446</v>
+        <v>0.50441400000000003</v>
       </c>
       <c r="J2">
-        <v>0.67818699999999998</v>
+        <v>0.50133000000000005</v>
       </c>
       <c r="K2">
-        <v>0.68060399999999999</v>
+        <v>0.50699700000000003</v>
       </c>
       <c r="L2">
-        <v>0.687531</v>
+        <v>0.50229199999999996</v>
       </c>
       <c r="M2">
-        <v>0.69020800000000004</v>
+        <v>0.50239400000000001</v>
       </c>
       <c r="N2">
-        <v>0.68626100000000001</v>
+        <v>0.49777100000000002</v>
       </c>
       <c r="O2">
-        <v>0.67827400000000004</v>
+        <v>0.48991499999999999</v>
       </c>
       <c r="P2">
-        <v>0.68354899999999996</v>
+        <v>0.48594799999999999</v>
       </c>
       <c r="Q2">
-        <v>0.68027300000000002</v>
+        <v>0.47431000000000001</v>
       </c>
       <c r="R2">
-        <v>0.66257999999999995</v>
+        <v>0.48974200000000001</v>
       </c>
       <c r="S2">
-        <v>0.65502899999999997</v>
+        <v>0.47890500000000003</v>
       </c>
       <c r="T2">
-        <v>0.62368599999999996</v>
+        <v>0.46513500000000002</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A3">
-        <v>0.68518900000000005</v>
+        <v>0.50470199999999998</v>
       </c>
       <c r="B3">
-        <v>0.68400099999999997</v>
+        <v>0.51049500000000003</v>
       </c>
       <c r="C3">
-        <v>0.68379599999999996</v>
+        <v>0.50817599999999996</v>
       </c>
       <c r="D3">
-        <v>0.68326299999999995</v>
+        <v>0.51185999999999998</v>
       </c>
       <c r="E3">
-        <v>0.68583099999999997</v>
+        <v>0.52581199999999995</v>
       </c>
       <c r="F3">
-        <v>0.68524600000000002</v>
+        <v>0.52022500000000005</v>
       </c>
       <c r="G3">
-        <v>0.68503800000000004</v>
+        <v>0.51832</v>
       </c>
       <c r="H3">
-        <v>0.68852100000000005</v>
+        <v>0.511965</v>
       </c>
       <c r="I3">
-        <v>0.68783099999999997</v>
+        <v>0.51757699999999995</v>
       </c>
       <c r="J3">
-        <v>0.68071300000000001</v>
+        <v>0.51321399999999995</v>
       </c>
       <c r="K3">
-        <v>0.68165699999999996</v>
+        <v>0.51856400000000002</v>
       </c>
       <c r="L3">
-        <v>0.68898300000000001</v>
+        <v>0.51207199999999997</v>
       </c>
       <c r="M3">
-        <v>0.692747</v>
+        <v>0.51323200000000002</v>
       </c>
       <c r="N3">
-        <v>0.69018800000000002</v>
+        <v>0.51157300000000006</v>
       </c>
       <c r="O3">
-        <v>0.68355600000000005</v>
+        <v>0.50326499999999996</v>
       </c>
       <c r="P3">
-        <v>0.69005700000000003</v>
+        <v>0.50486900000000001</v>
       </c>
       <c r="Q3">
-        <v>0.686581</v>
+        <v>0.49760100000000002</v>
       </c>
       <c r="R3">
-        <v>0.66771000000000003</v>
+        <v>0.510934</v>
       </c>
       <c r="S3">
-        <v>0.66234800000000005</v>
+        <v>0.485072</v>
       </c>
       <c r="T3">
-        <v>0.62651199999999996</v>
+        <v>0.46980699999999997</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A4">
-        <v>0.69467599999999996</v>
+        <v>0.51188999999999996</v>
       </c>
       <c r="B4">
-        <v>0.69406000000000001</v>
+        <v>0.51800100000000004</v>
       </c>
       <c r="C4">
-        <v>0.69307399999999997</v>
+        <v>0.51555399999999996</v>
       </c>
       <c r="D4">
-        <v>0.69304699999999997</v>
+        <v>0.52208500000000002</v>
       </c>
       <c r="E4">
-        <v>0.69371899999999997</v>
+        <v>0.53731099999999998</v>
       </c>
       <c r="F4">
-        <v>0.69378099999999998</v>
+        <v>0.53298800000000002</v>
       </c>
       <c r="G4">
-        <v>0.69415000000000004</v>
+        <v>0.53410100000000005</v>
       </c>
       <c r="H4">
-        <v>0.69730000000000003</v>
+        <v>0.52504600000000001</v>
       </c>
       <c r="I4">
-        <v>0.69660100000000003</v>
+        <v>0.53573000000000004</v>
       </c>
       <c r="J4">
-        <v>0.68942000000000003</v>
+        <v>0.53165099999999998</v>
       </c>
       <c r="K4">
-        <v>0.68944700000000003</v>
+        <v>0.53718200000000005</v>
       </c>
       <c r="L4">
-        <v>0.69806699999999999</v>
+        <v>0.53301100000000001</v>
       </c>
       <c r="M4">
-        <v>0.70369700000000002</v>
+        <v>0.53995499999999996</v>
       </c>
       <c r="N4">
-        <v>0.70199</v>
+        <v>0.53967900000000002</v>
       </c>
       <c r="O4">
-        <v>0.69584100000000004</v>
+        <v>0.53137699999999999</v>
       </c>
       <c r="P4">
-        <v>0.69836699999999996</v>
+        <v>0.52441400000000005</v>
       </c>
       <c r="Q4">
-        <v>0.69449399999999994</v>
+        <v>0.50474399999999997</v>
       </c>
       <c r="R4">
-        <v>0.67466800000000005</v>
+        <v>0.52348099999999997</v>
       </c>
       <c r="S4">
-        <v>0.66903999999999997</v>
+        <v>0.488398</v>
       </c>
       <c r="T4">
-        <v>0.63780099999999995</v>
+        <v>0.471057</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A5">
-        <v>0.69684999999999997</v>
+        <v>0.51228499999999999</v>
       </c>
       <c r="B5">
-        <v>0.69634200000000002</v>
+        <v>0.52090499999999995</v>
       </c>
       <c r="C5">
-        <v>0.69606999999999997</v>
+        <v>0.51583800000000002</v>
       </c>
       <c r="D5">
-        <v>0.69378899999999999</v>
+        <v>0.51950600000000002</v>
       </c>
       <c r="E5">
-        <v>0.695245</v>
+        <v>0.53621399999999997</v>
       </c>
       <c r="F5">
-        <v>0.69565600000000005</v>
+        <v>0.53339099999999995</v>
       </c>
       <c r="G5">
-        <v>0.69502900000000001</v>
+        <v>0.53434300000000001</v>
       </c>
       <c r="H5">
-        <v>0.69721</v>
+        <v>0.52662500000000001</v>
       </c>
       <c r="I5">
-        <v>0.696855</v>
+        <v>0.54164400000000001</v>
       </c>
       <c r="J5">
-        <v>0.689832</v>
+        <v>0.53742100000000004</v>
       </c>
       <c r="K5">
-        <v>0.68998599999999999</v>
+        <v>0.54058499999999998</v>
       </c>
       <c r="L5">
-        <v>0.69976300000000002</v>
+        <v>0.53877200000000003</v>
       </c>
       <c r="M5">
-        <v>0.70711299999999999</v>
+        <v>0.55140800000000001</v>
       </c>
       <c r="N5">
-        <v>0.70485799999999998</v>
+        <v>0.55553600000000003</v>
       </c>
       <c r="O5">
-        <v>0.69798400000000005</v>
+        <v>0.54602799999999996</v>
       </c>
       <c r="P5">
-        <v>0.70160199999999995</v>
+        <v>0.54372299999999996</v>
       </c>
       <c r="Q5">
-        <v>0.69879899999999995</v>
+        <v>0.52580400000000005</v>
       </c>
       <c r="R5">
-        <v>0.67953300000000005</v>
+        <v>0.54369800000000001</v>
       </c>
       <c r="S5">
-        <v>0.67749599999999999</v>
+        <v>0.50882099999999997</v>
       </c>
       <c r="T5">
-        <v>0.64928699999999995</v>
+        <v>0.493647</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A6">
-        <v>0.70022700000000004</v>
+        <v>0.50527500000000003</v>
       </c>
       <c r="B6">
-        <v>0.69984900000000005</v>
+        <v>0.5161</v>
       </c>
       <c r="C6">
-        <v>0.70013000000000003</v>
+        <v>0.511799</v>
       </c>
       <c r="D6">
-        <v>0.69656799999999996</v>
+        <v>0.51327599999999995</v>
       </c>
       <c r="E6">
-        <v>0.69846900000000001</v>
+        <v>0.53118200000000004</v>
       </c>
       <c r="F6">
-        <v>0.69928400000000002</v>
+        <v>0.52971400000000002</v>
       </c>
       <c r="G6">
-        <v>0.69760999999999995</v>
+        <v>0.532439</v>
       </c>
       <c r="H6">
-        <v>0.69923999999999997</v>
+        <v>0.525617</v>
       </c>
       <c r="I6">
-        <v>0.69795099999999999</v>
+        <v>0.53893800000000003</v>
       </c>
       <c r="J6">
-        <v>0.69087500000000002</v>
+        <v>0.53681400000000001</v>
       </c>
       <c r="K6">
-        <v>0.69139799999999996</v>
+        <v>0.54008299999999998</v>
       </c>
       <c r="L6">
-        <v>0.69853600000000005</v>
+        <v>0.53244899999999995</v>
       </c>
       <c r="M6">
-        <v>0.70695399999999997</v>
+        <v>0.54591699999999999</v>
       </c>
       <c r="N6">
-        <v>0.70511500000000005</v>
+        <v>0.55331699999999995</v>
       </c>
       <c r="O6">
-        <v>0.69859499999999997</v>
+        <v>0.54596599999999995</v>
       </c>
       <c r="P6">
-        <v>0.70138999999999996</v>
+        <v>0.54209600000000002</v>
       </c>
       <c r="Q6">
-        <v>0.69821999999999995</v>
+        <v>0.52664100000000003</v>
       </c>
       <c r="R6">
-        <v>0.67742100000000005</v>
+        <v>0.55154000000000003</v>
       </c>
       <c r="S6">
-        <v>0.67311500000000002</v>
+        <v>0.51694799999999996</v>
       </c>
       <c r="T6">
-        <v>0.64365000000000006</v>
+        <v>0.50457099999999999</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A7">
-        <v>0.69672900000000004</v>
+        <v>0.51550700000000005</v>
       </c>
       <c r="B7">
-        <v>0.69704500000000003</v>
+        <v>0.52627699999999999</v>
       </c>
       <c r="C7">
-        <v>0.69762500000000005</v>
+        <v>0.52037199999999995</v>
       </c>
       <c r="D7">
-        <v>0.69427499999999998</v>
+        <v>0.52527500000000005</v>
       </c>
       <c r="E7">
-        <v>0.69656499999999999</v>
+        <v>0.54182799999999998</v>
       </c>
       <c r="F7">
-        <v>0.69752199999999998</v>
+        <v>0.54316399999999998</v>
       </c>
       <c r="G7">
-        <v>0.69594900000000004</v>
+        <v>0.55083000000000004</v>
       </c>
       <c r="H7">
-        <v>0.69487500000000002</v>
+        <v>0.54570300000000005</v>
       </c>
       <c r="I7">
-        <v>0.69386999999999999</v>
+        <v>0.55862599999999996</v>
       </c>
       <c r="J7">
-        <v>0.68693899999999997</v>
+        <v>0.556454</v>
       </c>
       <c r="K7">
-        <v>0.68801999999999996</v>
+        <v>0.55567900000000003</v>
       </c>
       <c r="L7">
-        <v>0.69272999999999996</v>
+        <v>0.55028999999999995</v>
       </c>
       <c r="M7">
-        <v>0.70138100000000003</v>
+        <v>0.55671599999999999</v>
       </c>
       <c r="N7">
-        <v>0.70010399999999995</v>
+        <v>0.55863399999999996</v>
       </c>
       <c r="O7">
-        <v>0.69059800000000005</v>
+        <v>0.54818699999999998</v>
       </c>
       <c r="P7">
-        <v>0.69223800000000002</v>
+        <v>0.547925</v>
       </c>
       <c r="Q7">
-        <v>0.69021999999999994</v>
+        <v>0.53527999999999998</v>
       </c>
       <c r="R7">
-        <v>0.66925299999999999</v>
+        <v>0.554979</v>
       </c>
       <c r="S7">
-        <v>0.66496999999999995</v>
+        <v>0.52086299999999996</v>
       </c>
       <c r="T7">
-        <v>0.63624599999999998</v>
+        <v>0.51136599999999999</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A8">
-        <v>0.70410899999999998</v>
+        <v>0.50436300000000001</v>
       </c>
       <c r="B8">
-        <v>0.70491499999999996</v>
+        <v>0.51432199999999995</v>
       </c>
       <c r="C8">
-        <v>0.70447599999999999</v>
+        <v>0.50629199999999996</v>
       </c>
       <c r="D8">
-        <v>0.70187100000000002</v>
+        <v>0.51008600000000004</v>
       </c>
       <c r="E8">
-        <v>0.70464899999999997</v>
+        <v>0.52237599999999995</v>
       </c>
       <c r="F8">
-        <v>0.70600399999999996</v>
+        <v>0.52571999999999997</v>
       </c>
       <c r="G8">
-        <v>0.70544499999999999</v>
+        <v>0.53487200000000001</v>
       </c>
       <c r="H8">
-        <v>0.70497799999999999</v>
+        <v>0.53131600000000001</v>
       </c>
       <c r="I8">
-        <v>0.70484199999999997</v>
+        <v>0.54296900000000003</v>
       </c>
       <c r="J8">
-        <v>0.69529300000000005</v>
+        <v>0.54269699999999998</v>
       </c>
       <c r="K8">
-        <v>0.69703599999999999</v>
+        <v>0.53957900000000003</v>
       </c>
       <c r="L8">
-        <v>0.70330700000000002</v>
+        <v>0.53044100000000005</v>
       </c>
       <c r="M8">
-        <v>0.71301700000000001</v>
+        <v>0.52840399999999998</v>
       </c>
       <c r="N8">
-        <v>0.70934200000000003</v>
+        <v>0.53165200000000001</v>
       </c>
       <c r="O8">
-        <v>0.70053299999999996</v>
+        <v>0.523316</v>
       </c>
       <c r="P8">
-        <v>0.69975299999999996</v>
+        <v>0.52510699999999999</v>
       </c>
       <c r="Q8">
-        <v>0.69497200000000003</v>
+        <v>0.51411200000000001</v>
       </c>
       <c r="R8">
-        <v>0.675929</v>
+        <v>0.53496100000000002</v>
       </c>
       <c r="S8">
-        <v>0.67179100000000003</v>
+        <v>0.50246900000000005</v>
       </c>
       <c r="T8">
-        <v>0.64155899999999999</v>
+        <v>0.49483899999999997</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A9">
-        <v>0.70882400000000001</v>
+        <v>0.51416200000000001</v>
       </c>
       <c r="B9">
-        <v>0.71014100000000002</v>
+        <v>0.52125999999999995</v>
       </c>
       <c r="C9">
-        <v>0.70989199999999997</v>
+        <v>0.51365000000000005</v>
       </c>
       <c r="D9">
-        <v>0.70786199999999999</v>
+        <v>0.51697499999999996</v>
       </c>
       <c r="E9">
-        <v>0.71141600000000005</v>
+        <v>0.522818</v>
       </c>
       <c r="F9">
-        <v>0.71392</v>
+        <v>0.525393</v>
       </c>
       <c r="G9">
-        <v>0.71243199999999995</v>
+        <v>0.53937500000000005</v>
       </c>
       <c r="H9">
-        <v>0.71194199999999996</v>
+        <v>0.53278800000000004</v>
       </c>
       <c r="I9">
-        <v>0.71269400000000005</v>
+        <v>0.54553200000000002</v>
       </c>
       <c r="J9">
-        <v>0.70306599999999997</v>
+        <v>0.54325400000000001</v>
       </c>
       <c r="K9">
-        <v>0.70579499999999995</v>
+        <v>0.53650799999999998</v>
       </c>
       <c r="L9">
-        <v>0.713063</v>
+        <v>0.52324400000000004</v>
       </c>
       <c r="M9">
-        <v>0.71915700000000005</v>
+        <v>0.51786699999999997</v>
       </c>
       <c r="N9">
-        <v>0.71417900000000001</v>
+        <v>0.52452699999999997</v>
       </c>
       <c r="O9">
-        <v>0.70206400000000002</v>
+        <v>0.51931300000000002</v>
       </c>
       <c r="P9">
-        <v>0.70089500000000005</v>
+        <v>0.51765600000000001</v>
       </c>
       <c r="Q9">
-        <v>0.69545999999999997</v>
+        <v>0.50187599999999999</v>
       </c>
       <c r="R9">
-        <v>0.67769699999999999</v>
+        <v>0.51749500000000004</v>
       </c>
       <c r="S9">
-        <v>0.67643900000000001</v>
+        <v>0.48666799999999999</v>
       </c>
       <c r="T9">
-        <v>0.65065499999999998</v>
+        <v>0.48220200000000002</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A10">
-        <v>0.70643699999999998</v>
+        <v>0.510988</v>
       </c>
       <c r="B10">
-        <v>0.70819699999999997</v>
+        <v>0.51701900000000001</v>
       </c>
       <c r="C10">
-        <v>0.70657400000000004</v>
+        <v>0.50956599999999996</v>
       </c>
       <c r="D10">
-        <v>0.70484199999999997</v>
+        <v>0.51101200000000002</v>
       </c>
       <c r="E10">
-        <v>0.70788399999999996</v>
+        <v>0.515324</v>
       </c>
       <c r="F10">
-        <v>0.70903300000000002</v>
+        <v>0.51575199999999999</v>
       </c>
       <c r="G10">
-        <v>0.70812200000000003</v>
+        <v>0.52884100000000001</v>
       </c>
       <c r="H10">
-        <v>0.70632899999999998</v>
+        <v>0.52357399999999998</v>
       </c>
       <c r="I10">
-        <v>0.707978</v>
+        <v>0.52850699999999995</v>
       </c>
       <c r="J10">
-        <v>0.698627</v>
+        <v>0.52216600000000002</v>
       </c>
       <c r="K10">
-        <v>0.70007900000000001</v>
+        <v>0.51720999999999995</v>
       </c>
       <c r="L10">
-        <v>0.70662400000000003</v>
+        <v>0.50488599999999995</v>
       </c>
       <c r="M10">
-        <v>0.71157800000000004</v>
+        <v>0.50075999999999998</v>
       </c>
       <c r="N10">
-        <v>0.70510499999999998</v>
+        <v>0.50341100000000005</v>
       </c>
       <c r="O10">
-        <v>0.69056899999999999</v>
+        <v>0.501448</v>
       </c>
       <c r="P10">
-        <v>0.69171899999999997</v>
+        <v>0.50271600000000005</v>
       </c>
       <c r="Q10">
-        <v>0.68646099999999999</v>
+        <v>0.48965500000000001</v>
       </c>
       <c r="R10">
-        <v>0.66992300000000005</v>
+        <v>0.50155400000000006</v>
       </c>
       <c r="S10">
-        <v>0.67069599999999996</v>
+        <v>0.47289199999999998</v>
       </c>
       <c r="T10">
-        <v>0.654053</v>
+        <v>0.46136500000000003</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A11">
-        <v>0.710341</v>
+        <v>0.48989100000000002</v>
       </c>
       <c r="B11">
-        <v>0.713476</v>
+        <v>0.49783300000000003</v>
       </c>
       <c r="C11">
-        <v>0.712453</v>
+        <v>0.49122700000000002</v>
       </c>
       <c r="D11">
-        <v>0.70974700000000002</v>
+        <v>0.49401499999999998</v>
       </c>
       <c r="E11">
-        <v>0.71361699999999995</v>
+        <v>0.49562699999999998</v>
       </c>
       <c r="F11">
-        <v>0.71343900000000005</v>
+        <v>0.497948</v>
       </c>
       <c r="G11">
-        <v>0.713866</v>
+        <v>0.51552900000000002</v>
       </c>
       <c r="H11">
-        <v>0.712808</v>
+        <v>0.51197300000000001</v>
       </c>
       <c r="I11">
-        <v>0.71608499999999997</v>
+        <v>0.514208</v>
       </c>
       <c r="J11">
-        <v>0.70686499999999997</v>
+        <v>0.51004499999999997</v>
       </c>
       <c r="K11">
-        <v>0.70910600000000001</v>
+        <v>0.50625200000000004</v>
       </c>
       <c r="L11">
-        <v>0.71451299999999995</v>
+        <v>0.49543999999999999</v>
       </c>
       <c r="M11">
-        <v>0.72124699999999997</v>
+        <v>0.49384400000000001</v>
       </c>
       <c r="N11">
-        <v>0.71589199999999997</v>
+        <v>0.49250500000000003</v>
       </c>
       <c r="O11">
-        <v>0.70212699999999995</v>
+        <v>0.47853600000000002</v>
       </c>
       <c r="P11">
-        <v>0.70759300000000003</v>
+        <v>0.48383999999999999</v>
       </c>
       <c r="Q11">
-        <v>0.69906800000000002</v>
+        <v>0.46402199999999999</v>
       </c>
       <c r="R11">
-        <v>0.682338</v>
+        <v>0.47033000000000003</v>
       </c>
       <c r="S11">
-        <v>0.68105199999999999</v>
+        <v>0.44489899999999999</v>
       </c>
       <c r="T11">
-        <v>0.66129599999999999</v>
+        <v>0.43580799999999997</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A12">
-        <v>0.71605600000000003</v>
+        <v>0.47981200000000002</v>
       </c>
       <c r="B12">
-        <v>0.72062700000000002</v>
+        <v>0.49047099999999999</v>
       </c>
       <c r="C12">
-        <v>0.72032799999999997</v>
+        <v>0.48441000000000001</v>
       </c>
       <c r="D12">
-        <v>0.71852199999999999</v>
+        <v>0.48388700000000001</v>
       </c>
       <c r="E12">
-        <v>0.72190200000000004</v>
+        <v>0.48811399999999999</v>
       </c>
       <c r="F12">
-        <v>0.722939</v>
+        <v>0.48688199999999998</v>
       </c>
       <c r="G12">
-        <v>0.72070599999999996</v>
+        <v>0.495643</v>
       </c>
       <c r="H12">
-        <v>0.718476</v>
+        <v>0.48686699999999999</v>
       </c>
       <c r="I12">
-        <v>0.72284499999999996</v>
+        <v>0.48394199999999998</v>
       </c>
       <c r="J12">
-        <v>0.71371700000000005</v>
+        <v>0.48094700000000001</v>
       </c>
       <c r="K12">
-        <v>0.71773200000000004</v>
+        <v>0.47885100000000003</v>
       </c>
       <c r="L12">
-        <v>0.72034799999999999</v>
+        <v>0.46906199999999998</v>
       </c>
       <c r="M12">
-        <v>0.72884199999999999</v>
+        <v>0.46969499999999997</v>
       </c>
       <c r="N12">
-        <v>0.72532799999999997</v>
+        <v>0.46391199999999999</v>
       </c>
       <c r="O12">
-        <v>0.70772999999999997</v>
+        <v>0.45081199999999999</v>
       </c>
       <c r="P12">
-        <v>0.71315799999999996</v>
+        <v>0.45109300000000002</v>
       </c>
       <c r="Q12">
-        <v>0.70629799999999998</v>
+        <v>0.43270399999999998</v>
       </c>
       <c r="R12">
-        <v>0.68691899999999995</v>
+        <v>0.43139899999999998</v>
       </c>
       <c r="S12">
-        <v>0.68765299999999996</v>
+        <v>0.40990700000000002</v>
       </c>
       <c r="T12">
-        <v>0.68007099999999998</v>
+        <v>0.40124399999999999</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A13">
-        <v>0.71741900000000003</v>
+        <v>0.46534599999999998</v>
       </c>
       <c r="B13">
-        <v>0.72153500000000004</v>
+        <v>0.47927500000000001</v>
       </c>
       <c r="C13">
-        <v>0.72150300000000001</v>
+        <v>0.47457700000000003</v>
       </c>
       <c r="D13">
-        <v>0.72069399999999995</v>
+        <v>0.46935100000000002</v>
       </c>
       <c r="E13">
-        <v>0.72544900000000001</v>
+        <v>0.47724100000000003</v>
       </c>
       <c r="F13">
-        <v>0.72531299999999999</v>
+        <v>0.47779899999999997</v>
       </c>
       <c r="G13">
-        <v>0.72207500000000002</v>
+        <v>0.49218099999999998</v>
       </c>
       <c r="H13">
-        <v>0.72057700000000002</v>
+        <v>0.48404799999999998</v>
       </c>
       <c r="I13">
-        <v>0.72742200000000001</v>
+        <v>0.48467700000000002</v>
       </c>
       <c r="J13">
-        <v>0.71805099999999999</v>
+        <v>0.47539500000000001</v>
       </c>
       <c r="K13">
-        <v>0.72331000000000001</v>
+        <v>0.476026</v>
       </c>
       <c r="L13">
-        <v>0.72804000000000002</v>
+        <v>0.467165</v>
       </c>
       <c r="M13">
-        <v>0.73980299999999999</v>
+        <v>0.46322999999999998</v>
       </c>
       <c r="N13">
-        <v>0.73631100000000005</v>
+        <v>0.45901399999999998</v>
       </c>
       <c r="O13">
-        <v>0.72006499999999996</v>
+        <v>0.44580599999999998</v>
       </c>
       <c r="P13">
-        <v>0.72744799999999998</v>
+        <v>0.43926799999999999</v>
       </c>
       <c r="Q13">
-        <v>0.72459499999999999</v>
+        <v>0.42343700000000001</v>
       </c>
       <c r="R13">
-        <v>0.706959</v>
+        <v>0.42683700000000002</v>
       </c>
       <c r="S13">
-        <v>0.69620000000000004</v>
+        <v>0.40575899999999998</v>
       </c>
       <c r="T13">
-        <v>0.68921699999999997</v>
+        <v>0.39872400000000002</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A14">
-        <v>0.72202999999999995</v>
+        <v>0.43574200000000002</v>
       </c>
       <c r="B14">
-        <v>0.72760000000000002</v>
+        <v>0.44492199999999998</v>
       </c>
       <c r="C14">
-        <v>0.72856799999999999</v>
+        <v>0.44073200000000001</v>
       </c>
       <c r="D14">
-        <v>0.72872899999999996</v>
+        <v>0.43575399999999997</v>
       </c>
       <c r="E14">
-        <v>0.73537300000000005</v>
+        <v>0.43829600000000002</v>
       </c>
       <c r="F14">
-        <v>0.73304400000000003</v>
+        <v>0.43965799999999999</v>
       </c>
       <c r="G14">
-        <v>0.73041100000000003</v>
+        <v>0.44037700000000002</v>
       </c>
       <c r="H14">
-        <v>0.73019800000000001</v>
+        <v>0.43443100000000001</v>
       </c>
       <c r="I14">
-        <v>0.73254600000000003</v>
+        <v>0.43546299999999999</v>
       </c>
       <c r="J14">
-        <v>0.72437700000000005</v>
+        <v>0.42809199999999997</v>
       </c>
       <c r="K14">
-        <v>0.73156699999999997</v>
+        <v>0.43006</v>
       </c>
       <c r="L14">
-        <v>0.73800900000000003</v>
+        <v>0.42209200000000002</v>
       </c>
       <c r="M14">
-        <v>0.75005900000000003</v>
+        <v>0.41984700000000003</v>
       </c>
       <c r="N14">
-        <v>0.74793600000000005</v>
+        <v>0.41726799999999997</v>
       </c>
       <c r="O14">
-        <v>0.732491</v>
+        <v>0.40543499999999999</v>
       </c>
       <c r="P14">
-        <v>0.74269600000000002</v>
+        <v>0.40112500000000001</v>
       </c>
       <c r="Q14">
-        <v>0.74166799999999999</v>
+        <v>0.38792900000000002</v>
       </c>
       <c r="R14">
-        <v>0.72856500000000002</v>
+        <v>0.392314</v>
       </c>
       <c r="S14">
-        <v>0.72197699999999998</v>
+        <v>0.37528299999999998</v>
       </c>
       <c r="T14">
-        <v>0.70225599999999999</v>
+        <v>0.369058</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A15">
-        <v>0.75023099999999998</v>
+        <v>0.43123699999999998</v>
       </c>
       <c r="B15">
-        <v>0.75834699999999999</v>
+        <v>0.43611899999999998</v>
       </c>
       <c r="C15">
-        <v>0.75783299999999998</v>
+        <v>0.43271199999999999</v>
       </c>
       <c r="D15">
-        <v>0.75668999999999997</v>
+        <v>0.42841200000000002</v>
       </c>
       <c r="E15">
-        <v>0.75897599999999998</v>
+        <v>0.424122</v>
       </c>
       <c r="F15">
-        <v>0.754104</v>
+        <v>0.42796099999999998</v>
       </c>
       <c r="G15">
-        <v>0.75265899999999997</v>
+        <v>0.42193900000000001</v>
       </c>
       <c r="H15">
-        <v>0.75473299999999999</v>
+        <v>0.41686299999999998</v>
       </c>
       <c r="I15">
-        <v>0.75233799999999995</v>
+        <v>0.41956700000000002</v>
       </c>
       <c r="J15">
-        <v>0.74437699999999996</v>
+        <v>0.41368899999999997</v>
       </c>
       <c r="K15">
-        <v>0.75085999999999997</v>
+        <v>0.41803099999999999</v>
       </c>
       <c r="L15">
-        <v>0.76165499999999997</v>
+        <v>0.410968</v>
       </c>
       <c r="M15">
-        <v>0.77762900000000001</v>
+        <v>0.41213300000000003</v>
       </c>
       <c r="N15">
-        <v>0.77456899999999995</v>
+        <v>0.40233799999999997</v>
       </c>
       <c r="O15">
-        <v>0.75907599999999997</v>
+        <v>0.39245099999999999</v>
       </c>
       <c r="P15">
-        <v>0.75814499999999996</v>
+        <v>0.39138000000000001</v>
       </c>
       <c r="Q15">
-        <v>0.76327599999999995</v>
+        <v>0.37870500000000001</v>
       </c>
       <c r="R15">
-        <v>0.75057700000000005</v>
+        <v>0.37650899999999998</v>
       </c>
       <c r="S15">
-        <v>0.74193699999999996</v>
+        <v>0.37106899999999998</v>
       </c>
       <c r="T15">
-        <v>0.70867000000000002</v>
+        <v>0.36835200000000001</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A16">
-        <v>0.74201399999999995</v>
+        <v>0.38094600000000001</v>
       </c>
       <c r="B16">
-        <v>0.75212100000000004</v>
+        <v>0.386768</v>
       </c>
       <c r="C16">
-        <v>0.74831099999999995</v>
+        <v>0.38409700000000002</v>
       </c>
       <c r="D16">
-        <v>0.747722</v>
+        <v>0.38103100000000001</v>
       </c>
       <c r="E16">
-        <v>0.75118600000000002</v>
+        <v>0.37758199999999997</v>
       </c>
       <c r="F16">
-        <v>0.74695699999999998</v>
+        <v>0.37340400000000001</v>
       </c>
       <c r="G16">
-        <v>0.74714199999999997</v>
+        <v>0.368697</v>
       </c>
       <c r="H16">
-        <v>0.75083599999999995</v>
+        <v>0.36465399999999998</v>
       </c>
       <c r="I16">
-        <v>0.750417</v>
+        <v>0.36810900000000002</v>
       </c>
       <c r="J16">
-        <v>0.74283299999999997</v>
+        <v>0.36337900000000001</v>
       </c>
       <c r="K16">
-        <v>0.75189399999999995</v>
+        <v>0.36793799999999999</v>
       </c>
       <c r="L16">
-        <v>0.76086600000000004</v>
+        <v>0.36213800000000002</v>
       </c>
       <c r="M16">
-        <v>0.778447</v>
+        <v>0.36389700000000003</v>
       </c>
       <c r="N16">
-        <v>0.77241199999999999</v>
+        <v>0.35554599999999997</v>
       </c>
       <c r="O16">
-        <v>0.75756999999999997</v>
+        <v>0.34828799999999999</v>
       </c>
       <c r="P16">
-        <v>0.75503900000000002</v>
+        <v>0.349358</v>
       </c>
       <c r="Q16">
-        <v>0.75894399999999995</v>
+        <v>0.33844600000000002</v>
       </c>
       <c r="R16">
-        <v>0.75446999999999997</v>
+        <v>0.33827800000000002</v>
       </c>
       <c r="S16">
-        <v>0.75149500000000002</v>
+        <v>0.33430100000000001</v>
       </c>
       <c r="T16">
-        <v>0.70629299999999995</v>
+        <v>0.33405600000000002</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A17">
-        <v>0.74586399999999997</v>
+        <v>0.35418300000000003</v>
       </c>
       <c r="B17">
-        <v>0.75412400000000002</v>
+        <v>0.36201699999999998</v>
       </c>
       <c r="C17">
-        <v>0.74978900000000004</v>
+        <v>0.35976399999999997</v>
       </c>
       <c r="D17">
-        <v>0.75106899999999999</v>
+        <v>0.35750900000000002</v>
       </c>
       <c r="E17">
-        <v>0.75866699999999998</v>
+        <v>0.35462199999999999</v>
       </c>
       <c r="F17">
-        <v>0.754637</v>
+        <v>0.35154200000000002</v>
       </c>
       <c r="G17">
-        <v>0.75100900000000004</v>
+        <v>0.34751399999999999</v>
       </c>
       <c r="H17">
-        <v>0.75811399999999995</v>
+        <v>0.34412500000000001</v>
       </c>
       <c r="I17">
-        <v>0.75894399999999995</v>
+        <v>0.33985799999999999</v>
       </c>
       <c r="J17">
-        <v>0.75234000000000001</v>
+        <v>0.33610200000000001</v>
       </c>
       <c r="K17">
-        <v>0.76736899999999997</v>
+        <v>0.34279300000000001</v>
       </c>
       <c r="L17">
-        <v>0.78331799999999996</v>
+        <v>0.33782400000000001</v>
       </c>
       <c r="M17">
-        <v>0.79724099999999998</v>
+        <v>0.34309699999999999</v>
       </c>
       <c r="N17">
-        <v>0.78745399999999999</v>
+        <v>0.33626400000000001</v>
       </c>
       <c r="O17">
-        <v>0.77364100000000002</v>
+        <v>0.32950699999999999</v>
       </c>
       <c r="P17">
-        <v>0.77683100000000005</v>
+        <v>0.33351999999999998</v>
       </c>
       <c r="Q17">
-        <v>0.77669900000000003</v>
+        <v>0.32367299999999999</v>
       </c>
       <c r="R17">
-        <v>0.76816300000000004</v>
+        <v>0.32665</v>
       </c>
       <c r="S17">
-        <v>0.76185999999999998</v>
+        <v>0.32645800000000003</v>
       </c>
       <c r="T17">
-        <v>0.71723499999999996</v>
+        <v>0.329818</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A18">
-        <v>0.73245000000000005</v>
+        <v>0.33015499999999998</v>
       </c>
       <c r="B18">
-        <v>0.73768699999999998</v>
+        <v>0.32813799999999999</v>
       </c>
       <c r="C18">
-        <v>0.73482400000000003</v>
+        <v>0.32626899999999998</v>
       </c>
       <c r="D18">
-        <v>0.73880100000000004</v>
+        <v>0.32437199999999999</v>
       </c>
       <c r="E18">
-        <v>0.75278199999999995</v>
+        <v>0.32208500000000001</v>
       </c>
       <c r="F18">
-        <v>0.74883900000000003</v>
+        <v>0.31964199999999998</v>
       </c>
       <c r="G18">
-        <v>0.74587999999999999</v>
+        <v>0.31597900000000001</v>
       </c>
       <c r="H18">
-        <v>0.74094599999999999</v>
+        <v>0.31311</v>
       </c>
       <c r="I18">
-        <v>0.74548199999999998</v>
+        <v>0.31010100000000002</v>
       </c>
       <c r="J18">
-        <v>0.74148599999999998</v>
+        <v>0.307145</v>
       </c>
       <c r="K18">
-        <v>0.75681399999999999</v>
+        <v>0.31614799999999998</v>
       </c>
       <c r="L18">
-        <v>0.78372900000000001</v>
+        <v>0.31199100000000002</v>
       </c>
       <c r="M18">
-        <v>0.77525100000000002</v>
+        <v>0.320803</v>
       </c>
       <c r="N18">
-        <v>0.767822</v>
+        <v>0.31479299999999999</v>
       </c>
       <c r="O18">
-        <v>0.75506499999999999</v>
+        <v>0.30968000000000001</v>
       </c>
       <c r="P18">
-        <v>0.75406499999999999</v>
+        <v>0.31709100000000001</v>
       </c>
       <c r="Q18">
-        <v>0.76786600000000005</v>
+        <v>0.30910799999999999</v>
       </c>
       <c r="R18">
-        <v>0.75867799999999996</v>
+        <v>0.30169200000000002</v>
       </c>
       <c r="S18">
-        <v>0.73536400000000002</v>
+        <v>0.307174</v>
       </c>
       <c r="T18">
-        <v>0.68667800000000001</v>
+        <v>0.31407400000000002</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A19">
-        <v>0.75150399999999995</v>
+        <v>0.33413900000000002</v>
       </c>
       <c r="B19">
-        <v>0.76620699999999997</v>
+        <v>0.33194299999999999</v>
       </c>
       <c r="C19">
-        <v>0.76278100000000004</v>
+        <v>0.33101900000000001</v>
       </c>
       <c r="D19">
-        <v>0.76003799999999999</v>
+        <v>0.32919500000000002</v>
       </c>
       <c r="E19">
-        <v>0.77584399999999998</v>
+        <v>0.32688800000000001</v>
       </c>
       <c r="F19">
-        <v>0.77234000000000003</v>
+        <v>0.324631</v>
       </c>
       <c r="G19">
-        <v>0.77093800000000001</v>
+        <v>0.32182100000000002</v>
       </c>
       <c r="H19">
-        <v>0.76742900000000003</v>
+        <v>0.32024999999999998</v>
       </c>
       <c r="I19">
-        <v>0.78516200000000003</v>
+        <v>0.31768999999999997</v>
       </c>
       <c r="J19">
-        <v>0.78157299999999996</v>
+        <v>0.31515700000000002</v>
       </c>
       <c r="K19">
-        <v>0.80011100000000002</v>
+        <v>0.31365700000000002</v>
       </c>
       <c r="L19">
-        <v>0.82048100000000002</v>
+        <v>0.31082199999999999</v>
       </c>
       <c r="M19">
-        <v>0.81218900000000005</v>
+        <v>0.32701599999999997</v>
       </c>
       <c r="N19">
-        <v>0.80614799999999998</v>
+        <v>0.32109300000000002</v>
       </c>
       <c r="O19">
-        <v>0.797068</v>
+        <v>0.31700400000000001</v>
       </c>
       <c r="P19">
-        <v>0.78872600000000004</v>
+        <v>0.33568900000000002</v>
       </c>
       <c r="Q19">
-        <v>0.82653699999999997</v>
+        <v>0.32886399999999999</v>
       </c>
       <c r="R19">
-        <v>0.80965200000000004</v>
+        <v>0.321436</v>
       </c>
       <c r="S19">
-        <v>0.77970499999999998</v>
+        <v>0.33901700000000001</v>
       </c>
       <c r="T19">
-        <v>0.74179099999999998</v>
+        <v>0.32986700000000002</v>
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A20">
-        <v>0.56753299999999995</v>
+        <v>0.29999599999999998</v>
       </c>
       <c r="B20">
-        <v>0.56753299999999995</v>
+        <v>0.29838999999999999</v>
       </c>
       <c r="C20">
-        <v>0.56642899999999996</v>
+        <v>0.29814200000000002</v>
       </c>
       <c r="D20">
-        <v>0.56532400000000005</v>
+        <v>0.29677799999999999</v>
       </c>
       <c r="E20">
-        <v>0.56532400000000005</v>
+        <v>0.29571500000000001</v>
       </c>
       <c r="F20">
-        <v>0.56532400000000005</v>
+        <v>0.29391899999999999</v>
       </c>
       <c r="G20">
-        <v>0.56532400000000005</v>
+        <v>0.29171000000000002</v>
       </c>
       <c r="H20">
-        <v>0.56089999999999995</v>
+        <v>0.29019299999999998</v>
       </c>
       <c r="I20">
-        <v>0.55979299999999999</v>
+        <v>0.28856100000000001</v>
       </c>
       <c r="J20">
-        <v>0.55979299999999999</v>
+        <v>0.28725000000000001</v>
       </c>
       <c r="K20">
-        <v>0.59992000000000001</v>
+        <v>0.28618300000000002</v>
       </c>
       <c r="L20">
-        <v>0.59992000000000001</v>
+        <v>0.283858</v>
       </c>
       <c r="M20">
-        <v>0.59523999999999999</v>
+        <v>0.28098299999999998</v>
       </c>
       <c r="N20">
-        <v>0.591723</v>
+        <v>0.27679300000000001</v>
       </c>
       <c r="O20">
-        <v>0.58467599999999997</v>
+        <v>0.27353300000000003</v>
       </c>
       <c r="P20">
-        <v>0.58114399999999999</v>
+        <v>0.29346699999999998</v>
       </c>
       <c r="Q20">
-        <v>0.61815100000000001</v>
+        <v>0.28802499999999998</v>
       </c>
       <c r="R20">
-        <v>0.614371</v>
+        <v>0.282804</v>
       </c>
       <c r="S20">
-        <v>0.59664600000000001</v>
+        <v>0.27640799999999999</v>
       </c>
       <c r="T20">
-        <v>0.55298899999999995</v>
+        <v>0.270648</v>
       </c>
     </row>
   </sheetData>

--- a/TMVA/FOM_small.xlsx
+++ b/TMVA/FOM_small.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24729"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\purol\OneDrive\바탕 화면\github\Belle2_script\TMVA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18772F22-8C8F-48CE-B741-B3436F775359}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA52C16A-F099-41DA-8A80-780B893054AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -357,1242 +357,1242 @@
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A1" s="1">
-        <v>0.50592499999999996</v>
+        <v>0.43414399999999997</v>
       </c>
       <c r="B1">
-        <v>0.50761299999999998</v>
+        <v>0.437361</v>
       </c>
       <c r="C1">
-        <v>0.503772</v>
+        <v>0.437502</v>
       </c>
       <c r="D1">
-        <v>0.50446199999999997</v>
+        <v>0.43696699999999999</v>
       </c>
       <c r="E1">
-        <v>0.51208299999999995</v>
+        <v>0.44292599999999999</v>
       </c>
       <c r="F1">
-        <v>0.506772</v>
+        <v>0.44220700000000002</v>
       </c>
       <c r="G1">
-        <v>0.50120200000000004</v>
+        <v>0.43998399999999999</v>
       </c>
       <c r="H1">
-        <v>0.49375999999999998</v>
+        <v>0.43897399999999998</v>
       </c>
       <c r="I1">
-        <v>0.49417499999999998</v>
+        <v>0.44041000000000002</v>
       </c>
       <c r="J1">
-        <v>0.48901800000000001</v>
+        <v>0.434894</v>
       </c>
       <c r="K1">
-        <v>0.49048900000000001</v>
+        <v>0.42910599999999999</v>
       </c>
       <c r="L1">
-        <v>0.48291800000000001</v>
+        <v>0.42380299999999999</v>
       </c>
       <c r="M1">
-        <v>0.48261300000000001</v>
+        <v>0.41408899999999998</v>
       </c>
       <c r="N1">
-        <v>0.48232799999999998</v>
+        <v>0.40472399999999997</v>
       </c>
       <c r="O1">
-        <v>0.47475299999999998</v>
+        <v>0.41284999999999999</v>
       </c>
       <c r="P1">
-        <v>0.46905799999999997</v>
+        <v>0.40485100000000002</v>
       </c>
       <c r="Q1">
-        <v>0.45779900000000001</v>
+        <v>0.37024400000000002</v>
       </c>
       <c r="R1">
-        <v>0.46878799999999998</v>
+        <v>0.31113299999999999</v>
       </c>
       <c r="S1">
-        <v>0.46063199999999999</v>
+        <v>0.24176800000000001</v>
       </c>
       <c r="T1">
-        <v>0.45801399999999998</v>
+        <v>7.9716999999999996E-2</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A2">
-        <v>0.50601099999999999</v>
+        <v>0.43667400000000001</v>
       </c>
       <c r="B2">
-        <v>0.50973299999999999</v>
+        <v>0.43952000000000002</v>
       </c>
       <c r="C2">
-        <v>0.50605599999999995</v>
+        <v>0.43945899999999999</v>
       </c>
       <c r="D2">
-        <v>0.50903600000000004</v>
+        <v>0.43892900000000001</v>
       </c>
       <c r="E2">
-        <v>0.51889099999999999</v>
+        <v>0.444797</v>
       </c>
       <c r="F2">
-        <v>0.51348000000000005</v>
+        <v>0.44468099999999999</v>
       </c>
       <c r="G2">
-        <v>0.50959299999999996</v>
+        <v>0.44300200000000001</v>
       </c>
       <c r="H2">
-        <v>0.50214099999999995</v>
+        <v>0.44213000000000002</v>
       </c>
       <c r="I2">
-        <v>0.50441400000000003</v>
+        <v>0.44265500000000002</v>
       </c>
       <c r="J2">
-        <v>0.50133000000000005</v>
+        <v>0.43648199999999998</v>
       </c>
       <c r="K2">
-        <v>0.50699700000000003</v>
+        <v>0.43144399999999999</v>
       </c>
       <c r="L2">
-        <v>0.50229199999999996</v>
+        <v>0.42630699999999999</v>
       </c>
       <c r="M2">
-        <v>0.50239400000000001</v>
+        <v>0.41585899999999998</v>
       </c>
       <c r="N2">
-        <v>0.49777100000000002</v>
+        <v>0.406385</v>
       </c>
       <c r="O2">
-        <v>0.48991499999999999</v>
+        <v>0.41577700000000001</v>
       </c>
       <c r="P2">
-        <v>0.48594799999999999</v>
+        <v>0.40754600000000002</v>
       </c>
       <c r="Q2">
-        <v>0.47431000000000001</v>
+        <v>0.37091200000000002</v>
       </c>
       <c r="R2">
-        <v>0.48974200000000001</v>
+        <v>0.31323600000000001</v>
       </c>
       <c r="S2">
-        <v>0.47890500000000003</v>
+        <v>0.2417</v>
       </c>
       <c r="T2">
-        <v>0.46513500000000002</v>
+        <v>7.9716999999999996E-2</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A3">
-        <v>0.50470199999999998</v>
+        <v>0.43941999999999998</v>
       </c>
       <c r="B3">
-        <v>0.51049500000000003</v>
+        <v>0.44200299999999998</v>
       </c>
       <c r="C3">
-        <v>0.50817599999999996</v>
+        <v>0.44192900000000002</v>
       </c>
       <c r="D3">
-        <v>0.51185999999999998</v>
+        <v>0.44183</v>
       </c>
       <c r="E3">
-        <v>0.52581199999999995</v>
+        <v>0.44855600000000001</v>
       </c>
       <c r="F3">
-        <v>0.52022500000000005</v>
+        <v>0.44867699999999999</v>
       </c>
       <c r="G3">
-        <v>0.51832</v>
+        <v>0.44658500000000001</v>
       </c>
       <c r="H3">
-        <v>0.511965</v>
+        <v>0.44478699999999999</v>
       </c>
       <c r="I3">
-        <v>0.51757699999999995</v>
+        <v>0.44565700000000003</v>
       </c>
       <c r="J3">
-        <v>0.51321399999999995</v>
+        <v>0.43776799999999999</v>
       </c>
       <c r="K3">
-        <v>0.51856400000000002</v>
+        <v>0.43342900000000001</v>
       </c>
       <c r="L3">
-        <v>0.51207199999999997</v>
+        <v>0.42816700000000002</v>
       </c>
       <c r="M3">
-        <v>0.51323200000000002</v>
+        <v>0.417717</v>
       </c>
       <c r="N3">
-        <v>0.51157300000000006</v>
+        <v>0.40915099999999999</v>
       </c>
       <c r="O3">
-        <v>0.50326499999999996</v>
+        <v>0.42009999999999997</v>
       </c>
       <c r="P3">
-        <v>0.50486900000000001</v>
+        <v>0.409661</v>
       </c>
       <c r="Q3">
-        <v>0.49760100000000002</v>
+        <v>0.375365</v>
       </c>
       <c r="R3">
-        <v>0.510934</v>
+        <v>0.31268200000000002</v>
       </c>
       <c r="S3">
-        <v>0.485072</v>
+        <v>0.2417</v>
       </c>
       <c r="T3">
-        <v>0.46980699999999997</v>
+        <v>7.9716999999999996E-2</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A4">
-        <v>0.51188999999999996</v>
+        <v>0.44189299999999998</v>
       </c>
       <c r="B4">
-        <v>0.51800100000000004</v>
+        <v>0.44526399999999999</v>
       </c>
       <c r="C4">
-        <v>0.51555399999999996</v>
+        <v>0.44493300000000002</v>
       </c>
       <c r="D4">
-        <v>0.52208500000000002</v>
+        <v>0.44501099999999999</v>
       </c>
       <c r="E4">
-        <v>0.53731099999999998</v>
+        <v>0.45043</v>
       </c>
       <c r="F4">
-        <v>0.53298800000000002</v>
+        <v>0.44971800000000001</v>
       </c>
       <c r="G4">
-        <v>0.53410100000000005</v>
+        <v>0.44770599999999999</v>
       </c>
       <c r="H4">
-        <v>0.52504600000000001</v>
+        <v>0.44584800000000002</v>
       </c>
       <c r="I4">
-        <v>0.53573000000000004</v>
+        <v>0.44536799999999999</v>
       </c>
       <c r="J4">
-        <v>0.53165099999999998</v>
+        <v>0.43699700000000002</v>
       </c>
       <c r="K4">
-        <v>0.53718200000000005</v>
+        <v>0.433701</v>
       </c>
       <c r="L4">
-        <v>0.53301100000000001</v>
+        <v>0.42799900000000002</v>
       </c>
       <c r="M4">
-        <v>0.53995499999999996</v>
+        <v>0.41786899999999999</v>
       </c>
       <c r="N4">
-        <v>0.53967900000000002</v>
+        <v>0.410802</v>
       </c>
       <c r="O4">
-        <v>0.53137699999999999</v>
+        <v>0.42307600000000001</v>
       </c>
       <c r="P4">
-        <v>0.52441400000000005</v>
+        <v>0.41246899999999997</v>
       </c>
       <c r="Q4">
-        <v>0.50474399999999997</v>
+        <v>0.37669900000000001</v>
       </c>
       <c r="R4">
-        <v>0.52348099999999997</v>
+        <v>0.311614</v>
       </c>
       <c r="S4">
-        <v>0.488398</v>
+        <v>0.241369</v>
       </c>
       <c r="T4">
-        <v>0.471057</v>
+        <v>7.9716999999999996E-2</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A5">
-        <v>0.51228499999999999</v>
+        <v>0.44366100000000003</v>
       </c>
       <c r="B5">
-        <v>0.52090499999999995</v>
+        <v>0.44746200000000003</v>
       </c>
       <c r="C5">
-        <v>0.51583800000000002</v>
+        <v>0.44725999999999999</v>
       </c>
       <c r="D5">
-        <v>0.51950600000000002</v>
+        <v>0.44679799999999997</v>
       </c>
       <c r="E5">
-        <v>0.53621399999999997</v>
+        <v>0.45206600000000002</v>
       </c>
       <c r="F5">
-        <v>0.53339099999999995</v>
+        <v>0.45050299999999999</v>
       </c>
       <c r="G5">
-        <v>0.53434300000000001</v>
+        <v>0.44903599999999999</v>
       </c>
       <c r="H5">
-        <v>0.52662500000000001</v>
+        <v>0.44804300000000002</v>
       </c>
       <c r="I5">
-        <v>0.54164400000000001</v>
+        <v>0.44876199999999999</v>
       </c>
       <c r="J5">
-        <v>0.53742100000000004</v>
+        <v>0.44026100000000001</v>
       </c>
       <c r="K5">
-        <v>0.54058499999999998</v>
+        <v>0.43712499999999999</v>
       </c>
       <c r="L5">
-        <v>0.53877200000000003</v>
+        <v>0.43141600000000002</v>
       </c>
       <c r="M5">
-        <v>0.55140800000000001</v>
+        <v>0.41962699999999997</v>
       </c>
       <c r="N5">
-        <v>0.55553600000000003</v>
+        <v>0.41206900000000002</v>
       </c>
       <c r="O5">
-        <v>0.54602799999999996</v>
+        <v>0.42642600000000003</v>
       </c>
       <c r="P5">
-        <v>0.54372299999999996</v>
+        <v>0.414406</v>
       </c>
       <c r="Q5">
-        <v>0.52580400000000005</v>
+        <v>0.37554900000000002</v>
       </c>
       <c r="R5">
-        <v>0.54369800000000001</v>
+        <v>0.31253300000000001</v>
       </c>
       <c r="S5">
-        <v>0.50882099999999997</v>
+        <v>0.24063799999999999</v>
       </c>
       <c r="T5">
-        <v>0.493647</v>
+        <v>7.9716999999999996E-2</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A6">
-        <v>0.50527500000000003</v>
+        <v>0.44535799999999998</v>
       </c>
       <c r="B6">
-        <v>0.5161</v>
+        <v>0.44951999999999998</v>
       </c>
       <c r="C6">
-        <v>0.511799</v>
+        <v>0.45014100000000001</v>
       </c>
       <c r="D6">
-        <v>0.51327599999999995</v>
+        <v>0.44951099999999999</v>
       </c>
       <c r="E6">
-        <v>0.53118200000000004</v>
+        <v>0.45451000000000003</v>
       </c>
       <c r="F6">
-        <v>0.52971400000000002</v>
+        <v>0.45334799999999997</v>
       </c>
       <c r="G6">
-        <v>0.532439</v>
+        <v>0.451903</v>
       </c>
       <c r="H6">
-        <v>0.525617</v>
+        <v>0.45040200000000002</v>
       </c>
       <c r="I6">
-        <v>0.53893800000000003</v>
+        <v>0.45126699999999997</v>
       </c>
       <c r="J6">
-        <v>0.53681400000000001</v>
+        <v>0.44349499999999997</v>
       </c>
       <c r="K6">
-        <v>0.54008299999999998</v>
+        <v>0.44033</v>
       </c>
       <c r="L6">
-        <v>0.53244899999999995</v>
+        <v>0.43573899999999999</v>
       </c>
       <c r="M6">
-        <v>0.54591699999999999</v>
+        <v>0.423898</v>
       </c>
       <c r="N6">
-        <v>0.55331699999999995</v>
+        <v>0.417348</v>
       </c>
       <c r="O6">
-        <v>0.54596599999999995</v>
+        <v>0.43061500000000003</v>
       </c>
       <c r="P6">
-        <v>0.54209600000000002</v>
+        <v>0.42242600000000002</v>
       </c>
       <c r="Q6">
-        <v>0.52664100000000003</v>
+        <v>0.38004399999999999</v>
       </c>
       <c r="R6">
-        <v>0.55154000000000003</v>
+        <v>0.31606299999999998</v>
       </c>
       <c r="S6">
-        <v>0.51694799999999996</v>
+        <v>0.244616</v>
       </c>
       <c r="T6">
-        <v>0.50457099999999999</v>
+        <v>7.9716999999999996E-2</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A7">
-        <v>0.51550700000000005</v>
+        <v>0.44935900000000001</v>
       </c>
       <c r="B7">
-        <v>0.52627699999999999</v>
+        <v>0.45362799999999998</v>
       </c>
       <c r="C7">
-        <v>0.52037199999999995</v>
+        <v>0.45473799999999998</v>
       </c>
       <c r="D7">
-        <v>0.52527500000000005</v>
+        <v>0.455675</v>
       </c>
       <c r="E7">
-        <v>0.54182799999999998</v>
+        <v>0.46054299999999998</v>
       </c>
       <c r="F7">
-        <v>0.54316399999999998</v>
+        <v>0.459928</v>
       </c>
       <c r="G7">
-        <v>0.55083000000000004</v>
+        <v>0.45806400000000003</v>
       </c>
       <c r="H7">
-        <v>0.54570300000000005</v>
+        <v>0.45787899999999998</v>
       </c>
       <c r="I7">
-        <v>0.55862599999999996</v>
+        <v>0.458756</v>
       </c>
       <c r="J7">
-        <v>0.556454</v>
+        <v>0.45123099999999999</v>
       </c>
       <c r="K7">
-        <v>0.55567900000000003</v>
+        <v>0.448828</v>
       </c>
       <c r="L7">
-        <v>0.55028999999999995</v>
+        <v>0.44278600000000001</v>
       </c>
       <c r="M7">
-        <v>0.55671599999999999</v>
+        <v>0.43049399999999999</v>
       </c>
       <c r="N7">
-        <v>0.55863399999999996</v>
+        <v>0.42318099999999997</v>
       </c>
       <c r="O7">
-        <v>0.54818699999999998</v>
+        <v>0.43526199999999998</v>
       </c>
       <c r="P7">
-        <v>0.547925</v>
+        <v>0.42523300000000003</v>
       </c>
       <c r="Q7">
-        <v>0.53527999999999998</v>
+        <v>0.38187100000000002</v>
       </c>
       <c r="R7">
-        <v>0.554979</v>
+        <v>0.31686799999999998</v>
       </c>
       <c r="S7">
-        <v>0.52086299999999996</v>
+        <v>0.24409</v>
       </c>
       <c r="T7">
-        <v>0.51136599999999999</v>
+        <v>7.9528000000000001E-2</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A8">
-        <v>0.50436300000000001</v>
+        <v>0.44983499999999998</v>
       </c>
       <c r="B8">
-        <v>0.51432199999999995</v>
+        <v>0.454627</v>
       </c>
       <c r="C8">
-        <v>0.50629199999999996</v>
+        <v>0.45556200000000002</v>
       </c>
       <c r="D8">
-        <v>0.51008600000000004</v>
+        <v>0.45590999999999998</v>
       </c>
       <c r="E8">
-        <v>0.52237599999999995</v>
+        <v>0.46057199999999998</v>
       </c>
       <c r="F8">
-        <v>0.52571999999999997</v>
+        <v>0.46013999999999999</v>
       </c>
       <c r="G8">
-        <v>0.53487200000000001</v>
+        <v>0.45771200000000001</v>
       </c>
       <c r="H8">
-        <v>0.53131600000000001</v>
+        <v>0.45842100000000002</v>
       </c>
       <c r="I8">
-        <v>0.54296900000000003</v>
+        <v>0.46021600000000001</v>
       </c>
       <c r="J8">
-        <v>0.54269699999999998</v>
+        <v>0.45072600000000002</v>
       </c>
       <c r="K8">
-        <v>0.53957900000000003</v>
+        <v>0.44868999999999998</v>
       </c>
       <c r="L8">
-        <v>0.53044100000000005</v>
+        <v>0.44101800000000002</v>
       </c>
       <c r="M8">
-        <v>0.52840399999999998</v>
+        <v>0.42931900000000001</v>
       </c>
       <c r="N8">
-        <v>0.53165200000000001</v>
+        <v>0.42183399999999999</v>
       </c>
       <c r="O8">
-        <v>0.523316</v>
+        <v>0.43685600000000002</v>
       </c>
       <c r="P8">
-        <v>0.52510699999999999</v>
+        <v>0.42828899999999998</v>
       </c>
       <c r="Q8">
-        <v>0.51411200000000001</v>
+        <v>0.38719100000000001</v>
       </c>
       <c r="R8">
-        <v>0.53496100000000002</v>
+        <v>0.32244499999999998</v>
       </c>
       <c r="S8">
-        <v>0.50246900000000005</v>
+        <v>0.24929799999999999</v>
       </c>
       <c r="T8">
-        <v>0.49483899999999997</v>
+        <v>7.9528000000000001E-2</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A9">
-        <v>0.51416200000000001</v>
+        <v>0.44675599999999999</v>
       </c>
       <c r="B9">
-        <v>0.52125999999999995</v>
+        <v>0.45115300000000003</v>
       </c>
       <c r="C9">
-        <v>0.51365000000000005</v>
+        <v>0.452345</v>
       </c>
       <c r="D9">
-        <v>0.51697499999999996</v>
+        <v>0.45304800000000001</v>
       </c>
       <c r="E9">
-        <v>0.522818</v>
+        <v>0.457847</v>
       </c>
       <c r="F9">
-        <v>0.525393</v>
+        <v>0.45805400000000002</v>
       </c>
       <c r="G9">
-        <v>0.53937500000000005</v>
+        <v>0.45638899999999999</v>
       </c>
       <c r="H9">
-        <v>0.53278800000000004</v>
+        <v>0.45759300000000003</v>
       </c>
       <c r="I9">
-        <v>0.54553200000000002</v>
+        <v>0.460368</v>
       </c>
       <c r="J9">
-        <v>0.54325400000000001</v>
+        <v>0.45248899999999997</v>
       </c>
       <c r="K9">
-        <v>0.53650799999999998</v>
+        <v>0.45063999999999999</v>
       </c>
       <c r="L9">
-        <v>0.52324400000000004</v>
+        <v>0.442469</v>
       </c>
       <c r="M9">
-        <v>0.51786699999999997</v>
+        <v>0.42978699999999997</v>
       </c>
       <c r="N9">
-        <v>0.52452699999999997</v>
+        <v>0.420298</v>
       </c>
       <c r="O9">
-        <v>0.51931300000000002</v>
+        <v>0.43945899999999999</v>
       </c>
       <c r="P9">
-        <v>0.51765600000000001</v>
+        <v>0.42697099999999999</v>
       </c>
       <c r="Q9">
-        <v>0.50187599999999999</v>
+        <v>0.387878</v>
       </c>
       <c r="R9">
-        <v>0.51749500000000004</v>
+        <v>0.31884699999999999</v>
       </c>
       <c r="S9">
-        <v>0.48666799999999999</v>
+        <v>0.247811</v>
       </c>
       <c r="T9">
-        <v>0.48220200000000002</v>
+        <v>7.9528000000000001E-2</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A10">
-        <v>0.510988</v>
+        <v>0.45084400000000002</v>
       </c>
       <c r="B10">
-        <v>0.51701900000000001</v>
+        <v>0.45491599999999999</v>
       </c>
       <c r="C10">
-        <v>0.50956599999999996</v>
+        <v>0.45727499999999999</v>
       </c>
       <c r="D10">
-        <v>0.51101200000000002</v>
+        <v>0.45891500000000002</v>
       </c>
       <c r="E10">
-        <v>0.515324</v>
+        <v>0.46494400000000002</v>
       </c>
       <c r="F10">
-        <v>0.51575199999999999</v>
+        <v>0.46553600000000001</v>
       </c>
       <c r="G10">
-        <v>0.52884100000000001</v>
+        <v>0.46395700000000001</v>
       </c>
       <c r="H10">
-        <v>0.52357399999999998</v>
+        <v>0.46359099999999998</v>
       </c>
       <c r="I10">
-        <v>0.52850699999999995</v>
+        <v>0.46624199999999999</v>
       </c>
       <c r="J10">
-        <v>0.52216600000000002</v>
+        <v>0.45994600000000002</v>
       </c>
       <c r="K10">
-        <v>0.51720999999999995</v>
+        <v>0.460401</v>
       </c>
       <c r="L10">
-        <v>0.50488599999999995</v>
+        <v>0.45324399999999998</v>
       </c>
       <c r="M10">
-        <v>0.50075999999999998</v>
+        <v>0.44258500000000001</v>
       </c>
       <c r="N10">
-        <v>0.50341100000000005</v>
+        <v>0.43371999999999999</v>
       </c>
       <c r="O10">
-        <v>0.501448</v>
+        <v>0.451322</v>
       </c>
       <c r="P10">
-        <v>0.50271600000000005</v>
+        <v>0.43176900000000001</v>
       </c>
       <c r="Q10">
-        <v>0.48965500000000001</v>
+        <v>0.39422800000000002</v>
       </c>
       <c r="R10">
-        <v>0.50155400000000006</v>
+        <v>0.326345</v>
       </c>
       <c r="S10">
-        <v>0.47289199999999998</v>
+        <v>0.257579</v>
       </c>
       <c r="T10">
-        <v>0.46136500000000003</v>
+        <v>7.9528000000000001E-2</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A11">
-        <v>0.48989100000000002</v>
+        <v>0.44873800000000003</v>
       </c>
       <c r="B11">
-        <v>0.49783300000000003</v>
+        <v>0.451546</v>
       </c>
       <c r="C11">
-        <v>0.49122700000000002</v>
+        <v>0.45468799999999998</v>
       </c>
       <c r="D11">
-        <v>0.49401499999999998</v>
+        <v>0.45634200000000003</v>
       </c>
       <c r="E11">
-        <v>0.49562699999999998</v>
+        <v>0.46193299999999998</v>
       </c>
       <c r="F11">
-        <v>0.497948</v>
+        <v>0.46353699999999998</v>
       </c>
       <c r="G11">
-        <v>0.51552900000000002</v>
+        <v>0.46198299999999998</v>
       </c>
       <c r="H11">
-        <v>0.51197300000000001</v>
+        <v>0.46209600000000001</v>
       </c>
       <c r="I11">
-        <v>0.514208</v>
+        <v>0.46526699999999999</v>
       </c>
       <c r="J11">
-        <v>0.51004499999999997</v>
+        <v>0.46057700000000001</v>
       </c>
       <c r="K11">
-        <v>0.50625200000000004</v>
+        <v>0.46408300000000002</v>
       </c>
       <c r="L11">
-        <v>0.49543999999999999</v>
+        <v>0.45807900000000001</v>
       </c>
       <c r="M11">
-        <v>0.49384400000000001</v>
+        <v>0.44841900000000001</v>
       </c>
       <c r="N11">
-        <v>0.49250500000000003</v>
+        <v>0.43547999999999998</v>
       </c>
       <c r="O11">
-        <v>0.47853600000000002</v>
+        <v>0.44608599999999998</v>
       </c>
       <c r="P11">
-        <v>0.48383999999999999</v>
+        <v>0.42655399999999999</v>
       </c>
       <c r="Q11">
-        <v>0.46402199999999999</v>
+        <v>0.39493899999999998</v>
       </c>
       <c r="R11">
-        <v>0.47033000000000003</v>
+        <v>0.32586199999999999</v>
       </c>
       <c r="S11">
-        <v>0.44489899999999999</v>
+        <v>0.254915</v>
       </c>
       <c r="T11">
-        <v>0.43580799999999997</v>
+        <v>7.9528000000000001E-2</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A12">
-        <v>0.47981200000000002</v>
+        <v>0.44529600000000003</v>
       </c>
       <c r="B12">
-        <v>0.49047099999999999</v>
+        <v>0.44919199999999998</v>
       </c>
       <c r="C12">
-        <v>0.48441000000000001</v>
+        <v>0.45253500000000002</v>
       </c>
       <c r="D12">
-        <v>0.48388700000000001</v>
+        <v>0.45401999999999998</v>
       </c>
       <c r="E12">
-        <v>0.48811399999999999</v>
+        <v>0.460839</v>
       </c>
       <c r="F12">
-        <v>0.48688199999999998</v>
+        <v>0.46172800000000003</v>
       </c>
       <c r="G12">
-        <v>0.495643</v>
+        <v>0.45868900000000001</v>
       </c>
       <c r="H12">
-        <v>0.48686699999999999</v>
+        <v>0.45728200000000002</v>
       </c>
       <c r="I12">
-        <v>0.48394199999999998</v>
+        <v>0.458866</v>
       </c>
       <c r="J12">
-        <v>0.48094700000000001</v>
+        <v>0.45297500000000002</v>
       </c>
       <c r="K12">
-        <v>0.47885100000000003</v>
+        <v>0.45780900000000002</v>
       </c>
       <c r="L12">
-        <v>0.46906199999999998</v>
+        <v>0.45292500000000002</v>
       </c>
       <c r="M12">
-        <v>0.46969499999999997</v>
+        <v>0.44263400000000003</v>
       </c>
       <c r="N12">
-        <v>0.46391199999999999</v>
+        <v>0.433471</v>
       </c>
       <c r="O12">
-        <v>0.45081199999999999</v>
+        <v>0.44608900000000001</v>
       </c>
       <c r="P12">
-        <v>0.45109300000000002</v>
+        <v>0.41981400000000002</v>
       </c>
       <c r="Q12">
-        <v>0.43270399999999998</v>
+        <v>0.38732</v>
       </c>
       <c r="R12">
-        <v>0.43139899999999998</v>
+        <v>0.32502599999999998</v>
       </c>
       <c r="S12">
-        <v>0.40990700000000002</v>
+        <v>0.25528299999999998</v>
       </c>
       <c r="T12">
-        <v>0.40124399999999999</v>
+        <v>7.9528000000000001E-2</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A13">
-        <v>0.46534599999999998</v>
+        <v>0.45001799999999997</v>
       </c>
       <c r="B13">
-        <v>0.47927500000000001</v>
+        <v>0.455403</v>
       </c>
       <c r="C13">
-        <v>0.47457700000000003</v>
+        <v>0.45729799999999998</v>
       </c>
       <c r="D13">
-        <v>0.46935100000000002</v>
+        <v>0.45928600000000003</v>
       </c>
       <c r="E13">
-        <v>0.47724100000000003</v>
+        <v>0.46460899999999999</v>
       </c>
       <c r="F13">
-        <v>0.47779899999999997</v>
+        <v>0.46552199999999999</v>
       </c>
       <c r="G13">
-        <v>0.49218099999999998</v>
+        <v>0.46050799999999997</v>
       </c>
       <c r="H13">
-        <v>0.48404799999999998</v>
+        <v>0.460787</v>
       </c>
       <c r="I13">
-        <v>0.48467700000000002</v>
+        <v>0.463474</v>
       </c>
       <c r="J13">
-        <v>0.47539500000000001</v>
+        <v>0.45896199999999998</v>
       </c>
       <c r="K13">
-        <v>0.476026</v>
+        <v>0.46387099999999998</v>
       </c>
       <c r="L13">
-        <v>0.467165</v>
+        <v>0.45549499999999998</v>
       </c>
       <c r="M13">
-        <v>0.46322999999999998</v>
+        <v>0.44328499999999998</v>
       </c>
       <c r="N13">
-        <v>0.45901399999999998</v>
+        <v>0.43281599999999998</v>
       </c>
       <c r="O13">
-        <v>0.44580599999999998</v>
+        <v>0.444185</v>
       </c>
       <c r="P13">
-        <v>0.43926799999999999</v>
+        <v>0.41375499999999998</v>
       </c>
       <c r="Q13">
-        <v>0.42343700000000001</v>
+        <v>0.38113000000000002</v>
       </c>
       <c r="R13">
-        <v>0.42683700000000002</v>
+        <v>0.31672899999999998</v>
       </c>
       <c r="S13">
-        <v>0.40575899999999998</v>
+        <v>0.24626999999999999</v>
       </c>
       <c r="T13">
-        <v>0.39872400000000002</v>
+        <v>7.9031000000000004E-2</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A14">
-        <v>0.43574200000000002</v>
+        <v>0.44212499999999999</v>
       </c>
       <c r="B14">
-        <v>0.44492199999999998</v>
+        <v>0.44818999999999998</v>
       </c>
       <c r="C14">
-        <v>0.44073200000000001</v>
+        <v>0.45055000000000001</v>
       </c>
       <c r="D14">
-        <v>0.43575399999999997</v>
+        <v>0.45228400000000002</v>
       </c>
       <c r="E14">
-        <v>0.43829600000000002</v>
+        <v>0.45849099999999998</v>
       </c>
       <c r="F14">
-        <v>0.43965799999999999</v>
+        <v>0.46153</v>
       </c>
       <c r="G14">
-        <v>0.44037700000000002</v>
+        <v>0.45915600000000001</v>
       </c>
       <c r="H14">
-        <v>0.43443100000000001</v>
+        <v>0.46333600000000003</v>
       </c>
       <c r="I14">
-        <v>0.43546299999999999</v>
+        <v>0.46842800000000001</v>
       </c>
       <c r="J14">
-        <v>0.42809199999999997</v>
+        <v>0.464528</v>
       </c>
       <c r="K14">
-        <v>0.43006</v>
+        <v>0.46947299999999997</v>
       </c>
       <c r="L14">
-        <v>0.42209200000000002</v>
+        <v>0.45814199999999999</v>
       </c>
       <c r="M14">
-        <v>0.41984700000000003</v>
+        <v>0.44790999999999997</v>
       </c>
       <c r="N14">
-        <v>0.41726799999999997</v>
+        <v>0.431973</v>
       </c>
       <c r="O14">
-        <v>0.40543499999999999</v>
+        <v>0.44339899999999999</v>
       </c>
       <c r="P14">
-        <v>0.40112500000000001</v>
+        <v>0.41406300000000001</v>
       </c>
       <c r="Q14">
-        <v>0.38792900000000002</v>
+        <v>0.377942</v>
       </c>
       <c r="R14">
-        <v>0.392314</v>
+        <v>0.31298300000000001</v>
       </c>
       <c r="S14">
-        <v>0.37528299999999998</v>
+        <v>0.23347799999999999</v>
       </c>
       <c r="T14">
-        <v>0.369058</v>
+        <v>7.8840999999999994E-2</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A15">
-        <v>0.43123699999999998</v>
+        <v>0.43036600000000003</v>
       </c>
       <c r="B15">
-        <v>0.43611899999999998</v>
+        <v>0.43709700000000001</v>
       </c>
       <c r="C15">
-        <v>0.43271199999999999</v>
+        <v>0.440251</v>
       </c>
       <c r="D15">
-        <v>0.42841200000000002</v>
+        <v>0.44545600000000002</v>
       </c>
       <c r="E15">
-        <v>0.424122</v>
+        <v>0.452982</v>
       </c>
       <c r="F15">
-        <v>0.42796099999999998</v>
+        <v>0.45541199999999998</v>
       </c>
       <c r="G15">
-        <v>0.42193900000000001</v>
+        <v>0.45325199999999999</v>
       </c>
       <c r="H15">
-        <v>0.41686299999999998</v>
+        <v>0.45651599999999998</v>
       </c>
       <c r="I15">
-        <v>0.41956700000000002</v>
+        <v>0.46271499999999999</v>
       </c>
       <c r="J15">
-        <v>0.41368899999999997</v>
+        <v>0.45451799999999998</v>
       </c>
       <c r="K15">
-        <v>0.41803099999999999</v>
+        <v>0.45841900000000002</v>
       </c>
       <c r="L15">
-        <v>0.410968</v>
+        <v>0.45013999999999998</v>
       </c>
       <c r="M15">
-        <v>0.41213300000000003</v>
+        <v>0.44418099999999999</v>
       </c>
       <c r="N15">
-        <v>0.40233799999999997</v>
+        <v>0.43244500000000002</v>
       </c>
       <c r="O15">
-        <v>0.39245099999999999</v>
+        <v>0.45878099999999999</v>
       </c>
       <c r="P15">
-        <v>0.39138000000000001</v>
+        <v>0.42834100000000003</v>
       </c>
       <c r="Q15">
-        <v>0.37870500000000001</v>
+        <v>0.37821500000000002</v>
       </c>
       <c r="R15">
-        <v>0.37650899999999998</v>
+        <v>0.32070300000000002</v>
       </c>
       <c r="S15">
-        <v>0.37106899999999998</v>
+        <v>0.227685</v>
       </c>
       <c r="T15">
-        <v>0.36835200000000001</v>
+        <v>7.7588000000000004E-2</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A16">
-        <v>0.38094600000000001</v>
+        <v>0.41175800000000001</v>
       </c>
       <c r="B16">
-        <v>0.386768</v>
+        <v>0.41640700000000003</v>
       </c>
       <c r="C16">
-        <v>0.38409700000000002</v>
+        <v>0.415769</v>
       </c>
       <c r="D16">
-        <v>0.38103100000000001</v>
+        <v>0.42407400000000001</v>
       </c>
       <c r="E16">
-        <v>0.37758199999999997</v>
+        <v>0.43427900000000003</v>
       </c>
       <c r="F16">
-        <v>0.37340400000000001</v>
+        <v>0.44014900000000001</v>
       </c>
       <c r="G16">
-        <v>0.368697</v>
+        <v>0.44012099999999998</v>
       </c>
       <c r="H16">
-        <v>0.36465399999999998</v>
+        <v>0.44389699999999999</v>
       </c>
       <c r="I16">
-        <v>0.36810900000000002</v>
+        <v>0.44891399999999998</v>
       </c>
       <c r="J16">
-        <v>0.36337900000000001</v>
+        <v>0.44139899999999999</v>
       </c>
       <c r="K16">
-        <v>0.36793799999999999</v>
+        <v>0.44465100000000002</v>
       </c>
       <c r="L16">
-        <v>0.36213800000000002</v>
+        <v>0.43782199999999999</v>
       </c>
       <c r="M16">
-        <v>0.36389700000000003</v>
+        <v>0.436143</v>
       </c>
       <c r="N16">
-        <v>0.35554599999999997</v>
+        <v>0.42306700000000003</v>
       </c>
       <c r="O16">
-        <v>0.34828799999999999</v>
+        <v>0.44218400000000002</v>
       </c>
       <c r="P16">
-        <v>0.349358</v>
+        <v>0.40110000000000001</v>
       </c>
       <c r="Q16">
-        <v>0.33844600000000002</v>
+        <v>0.36058000000000001</v>
       </c>
       <c r="R16">
-        <v>0.33827800000000002</v>
+        <v>0.29842000000000002</v>
       </c>
       <c r="S16">
-        <v>0.33430100000000001</v>
+        <v>0.211397</v>
       </c>
       <c r="T16">
-        <v>0.33405600000000002</v>
+        <v>8.8363999999999998E-2</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A17">
-        <v>0.35418300000000003</v>
+        <v>0.376695</v>
       </c>
       <c r="B17">
-        <v>0.36201699999999998</v>
+        <v>0.38206099999999998</v>
       </c>
       <c r="C17">
-        <v>0.35976399999999997</v>
+        <v>0.38258199999999998</v>
       </c>
       <c r="D17">
-        <v>0.35750900000000002</v>
+        <v>0.38894699999999999</v>
       </c>
       <c r="E17">
-        <v>0.35462199999999999</v>
+        <v>0.40315699999999999</v>
       </c>
       <c r="F17">
-        <v>0.35154200000000002</v>
+        <v>0.404333</v>
       </c>
       <c r="G17">
-        <v>0.34751399999999999</v>
+        <v>0.40135700000000002</v>
       </c>
       <c r="H17">
-        <v>0.34412500000000001</v>
+        <v>0.401696</v>
       </c>
       <c r="I17">
-        <v>0.33985799999999999</v>
+        <v>0.41095700000000002</v>
       </c>
       <c r="J17">
-        <v>0.33610200000000001</v>
+        <v>0.40226600000000001</v>
       </c>
       <c r="K17">
-        <v>0.34279300000000001</v>
+        <v>0.40166299999999999</v>
       </c>
       <c r="L17">
-        <v>0.33782400000000001</v>
+        <v>0.39801500000000001</v>
       </c>
       <c r="M17">
-        <v>0.34309699999999999</v>
+        <v>0.40685900000000003</v>
       </c>
       <c r="N17">
-        <v>0.33626400000000001</v>
+        <v>0.395681</v>
       </c>
       <c r="O17">
-        <v>0.32950699999999999</v>
+        <v>0.42150700000000002</v>
       </c>
       <c r="P17">
-        <v>0.33351999999999998</v>
+        <v>0.39206600000000003</v>
       </c>
       <c r="Q17">
-        <v>0.32367299999999999</v>
+        <v>0.33843600000000001</v>
       </c>
       <c r="R17">
-        <v>0.32665</v>
+        <v>0.28212900000000002</v>
       </c>
       <c r="S17">
-        <v>0.32645800000000003</v>
+        <v>0.18613399999999999</v>
       </c>
       <c r="T17">
-        <v>0.329818</v>
+        <v>0.108752</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A18">
-        <v>0.33015499999999998</v>
+        <v>0.317776</v>
       </c>
       <c r="B18">
-        <v>0.32813799999999999</v>
+        <v>0.32280999999999999</v>
       </c>
       <c r="C18">
-        <v>0.32626899999999998</v>
+        <v>0.32467000000000001</v>
       </c>
       <c r="D18">
-        <v>0.32437199999999999</v>
+        <v>0.32998300000000003</v>
       </c>
       <c r="E18">
-        <v>0.32208500000000001</v>
+        <v>0.33201999999999998</v>
       </c>
       <c r="F18">
-        <v>0.31964199999999998</v>
+        <v>0.32872299999999999</v>
       </c>
       <c r="G18">
-        <v>0.31597900000000001</v>
+        <v>0.32746399999999998</v>
       </c>
       <c r="H18">
-        <v>0.31311</v>
+        <v>0.323409</v>
       </c>
       <c r="I18">
-        <v>0.31010100000000002</v>
+        <v>0.350796</v>
       </c>
       <c r="J18">
-        <v>0.307145</v>
+        <v>0.34686400000000001</v>
       </c>
       <c r="K18">
-        <v>0.31614799999999998</v>
+        <v>0.35871399999999998</v>
       </c>
       <c r="L18">
-        <v>0.31199100000000002</v>
+        <v>0.35766399999999998</v>
       </c>
       <c r="M18">
-        <v>0.320803</v>
+        <v>0.38529799999999997</v>
       </c>
       <c r="N18">
-        <v>0.31479299999999999</v>
+        <v>0.37160799999999999</v>
       </c>
       <c r="O18">
-        <v>0.30968000000000001</v>
+        <v>0.38460299999999997</v>
       </c>
       <c r="P18">
-        <v>0.31709100000000001</v>
+        <v>0.35555900000000001</v>
       </c>
       <c r="Q18">
-        <v>0.30910799999999999</v>
+        <v>0.31336900000000001</v>
       </c>
       <c r="R18">
-        <v>0.30169200000000002</v>
+        <v>0.25294100000000003</v>
       </c>
       <c r="S18">
-        <v>0.307174</v>
+        <v>0.16467899999999999</v>
       </c>
       <c r="T18">
-        <v>0.31407400000000002</v>
+        <v>8.2452999999999999E-2</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A19">
-        <v>0.33413900000000002</v>
+        <v>0.24873799999999999</v>
       </c>
       <c r="B19">
-        <v>0.33194299999999999</v>
+        <v>0.25570100000000001</v>
       </c>
       <c r="C19">
-        <v>0.33101900000000001</v>
+        <v>0.263015</v>
       </c>
       <c r="D19">
-        <v>0.32919500000000002</v>
+        <v>0.28496500000000002</v>
       </c>
       <c r="E19">
-        <v>0.32688800000000001</v>
+        <v>0.28128199999999998</v>
       </c>
       <c r="F19">
-        <v>0.324631</v>
+        <v>0.27554299999999998</v>
       </c>
       <c r="G19">
-        <v>0.32182100000000002</v>
+        <v>0.27274700000000002</v>
       </c>
       <c r="H19">
-        <v>0.32024999999999998</v>
+        <v>0.26564700000000002</v>
       </c>
       <c r="I19">
-        <v>0.31768999999999997</v>
+        <v>0.30924600000000002</v>
       </c>
       <c r="J19">
-        <v>0.31515700000000002</v>
+        <v>0.30218600000000001</v>
       </c>
       <c r="K19">
-        <v>0.31365700000000002</v>
+        <v>0.29321900000000001</v>
       </c>
       <c r="L19">
-        <v>0.31082199999999999</v>
+        <v>0.30357400000000001</v>
       </c>
       <c r="M19">
-        <v>0.32701599999999997</v>
+        <v>0.29095500000000002</v>
       </c>
       <c r="N19">
-        <v>0.32109300000000002</v>
+        <v>0.27385799999999999</v>
       </c>
       <c r="O19">
-        <v>0.31700400000000001</v>
+        <v>0.28197100000000003</v>
       </c>
       <c r="P19">
-        <v>0.33568900000000002</v>
+        <v>0.25932100000000002</v>
       </c>
       <c r="Q19">
-        <v>0.32886399999999999</v>
+        <v>0.22481300000000001</v>
       </c>
       <c r="R19">
-        <v>0.321436</v>
+        <v>0.19678399999999999</v>
       </c>
       <c r="S19">
-        <v>0.33901700000000001</v>
+        <v>0.144984</v>
       </c>
       <c r="T19">
-        <v>0.32986700000000002</v>
+        <v>4.4933000000000001E-2</v>
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A20">
-        <v>0.29999599999999998</v>
+        <v>0.21664900000000001</v>
       </c>
       <c r="B20">
-        <v>0.29838999999999999</v>
+        <v>0.214562</v>
       </c>
       <c r="C20">
-        <v>0.29814200000000002</v>
+        <v>0.21351100000000001</v>
       </c>
       <c r="D20">
-        <v>0.29677799999999999</v>
+        <v>0.212455</v>
       </c>
       <c r="E20">
-        <v>0.29571500000000001</v>
+        <v>0.212455</v>
       </c>
       <c r="F20">
-        <v>0.29391899999999999</v>
+        <v>0.211648</v>
       </c>
       <c r="G20">
-        <v>0.29171000000000002</v>
+        <v>0.211648</v>
       </c>
       <c r="H20">
-        <v>0.29019299999999998</v>
+        <v>0.21058299999999999</v>
       </c>
       <c r="I20">
-        <v>0.28856100000000001</v>
+        <v>0.20843500000000001</v>
       </c>
       <c r="J20">
-        <v>0.28725000000000001</v>
+        <v>0.20735200000000001</v>
       </c>
       <c r="K20">
-        <v>0.28618300000000002</v>
+        <v>0.20164799999999999</v>
       </c>
       <c r="L20">
-        <v>0.283858</v>
+        <v>0.19483800000000001</v>
       </c>
       <c r="M20">
-        <v>0.28098299999999998</v>
+        <v>0.19044900000000001</v>
       </c>
       <c r="N20">
-        <v>0.27679300000000001</v>
+        <v>0.184223</v>
       </c>
       <c r="O20">
-        <v>0.27353300000000003</v>
+        <v>0.18052099999999999</v>
       </c>
       <c r="P20">
-        <v>0.29346699999999998</v>
+        <v>0.17546200000000001</v>
       </c>
       <c r="Q20">
-        <v>0.28802499999999998</v>
+        <v>0.164964</v>
       </c>
       <c r="R20">
-        <v>0.282804</v>
+        <v>0.149566</v>
       </c>
       <c r="S20">
-        <v>0.27640799999999999</v>
+        <v>0.11287999999999999</v>
       </c>
       <c r="T20">
-        <v>0.270648</v>
+        <v>6.4287999999999998E-2</v>
       </c>
     </row>
   </sheetData>

--- a/TMVA/FOM_small.xlsx
+++ b/TMVA/FOM_small.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\purol\OneDrive\바탕 화면\github\Belle2_script\TMVA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA52C16A-F099-41DA-8A80-780B893054AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F86DEF6E-C81D-4F99-8236-BB36B9035086}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -357,1180 +357,1180 @@
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A1" s="1">
-        <v>0.43414399999999997</v>
+        <v>0.43266300000000002</v>
       </c>
       <c r="B1">
-        <v>0.437361</v>
+        <v>0.43478800000000001</v>
       </c>
       <c r="C1">
-        <v>0.437502</v>
+        <v>0.43496200000000002</v>
       </c>
       <c r="D1">
-        <v>0.43696699999999999</v>
+        <v>0.434834</v>
       </c>
       <c r="E1">
-        <v>0.44292599999999999</v>
+        <v>0.43738500000000002</v>
       </c>
       <c r="F1">
-        <v>0.44220700000000002</v>
+        <v>0.43719999999999998</v>
       </c>
       <c r="G1">
-        <v>0.43998399999999999</v>
+        <v>0.43309500000000001</v>
       </c>
       <c r="H1">
-        <v>0.43897399999999998</v>
+        <v>0.43142900000000001</v>
       </c>
       <c r="I1">
-        <v>0.44041000000000002</v>
+        <v>0.42924800000000002</v>
       </c>
       <c r="J1">
-        <v>0.434894</v>
+        <v>0.424178</v>
       </c>
       <c r="K1">
-        <v>0.42910599999999999</v>
+        <v>0.41926600000000003</v>
       </c>
       <c r="L1">
-        <v>0.42380299999999999</v>
+        <v>0.41420600000000002</v>
       </c>
       <c r="M1">
-        <v>0.41408899999999998</v>
+        <v>0.40661399999999998</v>
       </c>
       <c r="N1">
-        <v>0.40472399999999997</v>
+        <v>0.39665</v>
       </c>
       <c r="O1">
-        <v>0.41284999999999999</v>
+        <v>0.39949699999999999</v>
       </c>
       <c r="P1">
-        <v>0.40485100000000002</v>
+        <v>0.38565500000000003</v>
       </c>
       <c r="Q1">
-        <v>0.37024400000000002</v>
+        <v>0.355491</v>
       </c>
       <c r="R1">
-        <v>0.31113299999999999</v>
+        <v>0.309803</v>
       </c>
       <c r="S1">
-        <v>0.24176800000000001</v>
+        <v>0.231934</v>
       </c>
       <c r="T1">
-        <v>7.9716999999999996E-2</v>
+        <v>7.2558999999999998E-2</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A2">
-        <v>0.43667400000000001</v>
+        <v>0.434533</v>
       </c>
       <c r="B2">
-        <v>0.43952000000000002</v>
+        <v>0.43634299999999998</v>
       </c>
       <c r="C2">
-        <v>0.43945899999999999</v>
+        <v>0.43632100000000001</v>
       </c>
       <c r="D2">
-        <v>0.43892900000000001</v>
+        <v>0.43614999999999998</v>
       </c>
       <c r="E2">
-        <v>0.444797</v>
+        <v>0.438886</v>
       </c>
       <c r="F2">
-        <v>0.44468099999999999</v>
+        <v>0.43900699999999998</v>
       </c>
       <c r="G2">
-        <v>0.44300200000000001</v>
+        <v>0.43540299999999998</v>
       </c>
       <c r="H2">
-        <v>0.44213000000000002</v>
+        <v>0.43419799999999997</v>
       </c>
       <c r="I2">
-        <v>0.44265500000000002</v>
+        <v>0.43141099999999999</v>
       </c>
       <c r="J2">
-        <v>0.43648199999999998</v>
+        <v>0.42566399999999999</v>
       </c>
       <c r="K2">
-        <v>0.43144399999999999</v>
+        <v>0.42165599999999998</v>
       </c>
       <c r="L2">
-        <v>0.42630699999999999</v>
+        <v>0.41616199999999998</v>
       </c>
       <c r="M2">
-        <v>0.41585899999999998</v>
+        <v>0.40734199999999998</v>
       </c>
       <c r="N2">
-        <v>0.406385</v>
+        <v>0.39703300000000002</v>
       </c>
       <c r="O2">
-        <v>0.41577700000000001</v>
+        <v>0.401723</v>
       </c>
       <c r="P2">
-        <v>0.40754600000000002</v>
+        <v>0.38817600000000002</v>
       </c>
       <c r="Q2">
-        <v>0.37091200000000002</v>
+        <v>0.358796</v>
       </c>
       <c r="R2">
-        <v>0.31323600000000001</v>
+        <v>0.31132399999999999</v>
       </c>
       <c r="S2">
-        <v>0.2417</v>
+        <v>0.231874</v>
       </c>
       <c r="T2">
-        <v>7.9716999999999996E-2</v>
+        <v>7.2558999999999998E-2</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A3">
-        <v>0.43941999999999998</v>
+        <v>0.43617400000000001</v>
       </c>
       <c r="B3">
-        <v>0.44200299999999998</v>
+        <v>0.43787599999999999</v>
       </c>
       <c r="C3">
-        <v>0.44192900000000002</v>
+        <v>0.43775199999999997</v>
       </c>
       <c r="D3">
-        <v>0.44183</v>
+        <v>0.43763600000000002</v>
       </c>
       <c r="E3">
-        <v>0.44855600000000001</v>
+        <v>0.44079600000000002</v>
       </c>
       <c r="F3">
-        <v>0.44867699999999999</v>
+        <v>0.44084499999999999</v>
       </c>
       <c r="G3">
-        <v>0.44658500000000001</v>
+        <v>0.43728400000000001</v>
       </c>
       <c r="H3">
-        <v>0.44478699999999999</v>
+        <v>0.43589499999999998</v>
       </c>
       <c r="I3">
-        <v>0.44565700000000003</v>
+        <v>0.43348799999999998</v>
       </c>
       <c r="J3">
-        <v>0.43776799999999999</v>
+        <v>0.42707099999999998</v>
       </c>
       <c r="K3">
-        <v>0.43342900000000001</v>
+        <v>0.42361100000000002</v>
       </c>
       <c r="L3">
-        <v>0.42816700000000002</v>
+        <v>0.41852600000000001</v>
       </c>
       <c r="M3">
-        <v>0.417717</v>
+        <v>0.41000900000000001</v>
       </c>
       <c r="N3">
+        <v>0.40077299999999999</v>
+      </c>
+      <c r="O3">
         <v>0.40915099999999999</v>
       </c>
-      <c r="O3">
-        <v>0.42009999999999997</v>
-      </c>
       <c r="P3">
-        <v>0.409661</v>
+        <v>0.39123599999999997</v>
       </c>
       <c r="Q3">
-        <v>0.375365</v>
+        <v>0.361705</v>
       </c>
       <c r="R3">
-        <v>0.31268200000000002</v>
+        <v>0.31211699999999998</v>
       </c>
       <c r="S3">
-        <v>0.2417</v>
+        <v>0.23170199999999999</v>
       </c>
       <c r="T3">
-        <v>7.9716999999999996E-2</v>
+        <v>7.2558999999999998E-2</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A4">
-        <v>0.44189299999999998</v>
+        <v>0.43941400000000003</v>
       </c>
       <c r="B4">
-        <v>0.44526399999999999</v>
+        <v>0.441718</v>
       </c>
       <c r="C4">
-        <v>0.44493300000000002</v>
+        <v>0.44137199999999999</v>
       </c>
       <c r="D4">
-        <v>0.44501099999999999</v>
+        <v>0.441637</v>
       </c>
       <c r="E4">
-        <v>0.45043</v>
+        <v>0.44350400000000001</v>
       </c>
       <c r="F4">
-        <v>0.44971800000000001</v>
+        <v>0.442639</v>
       </c>
       <c r="G4">
-        <v>0.44770599999999999</v>
+        <v>0.439473</v>
       </c>
       <c r="H4">
-        <v>0.44584800000000002</v>
+        <v>0.43868200000000002</v>
       </c>
       <c r="I4">
-        <v>0.44536799999999999</v>
+        <v>0.43519400000000003</v>
       </c>
       <c r="J4">
-        <v>0.43699700000000002</v>
+        <v>0.427925</v>
       </c>
       <c r="K4">
-        <v>0.433701</v>
+        <v>0.42416599999999999</v>
       </c>
       <c r="L4">
-        <v>0.42799900000000002</v>
+        <v>0.41996600000000001</v>
       </c>
       <c r="M4">
-        <v>0.41786899999999999</v>
+        <v>0.41199999999999998</v>
       </c>
       <c r="N4">
-        <v>0.410802</v>
+        <v>0.40366000000000002</v>
       </c>
       <c r="O4">
-        <v>0.42307600000000001</v>
+        <v>0.41446300000000003</v>
       </c>
       <c r="P4">
-        <v>0.41246899999999997</v>
+        <v>0.39749899999999999</v>
       </c>
       <c r="Q4">
-        <v>0.37669900000000001</v>
+        <v>0.36521999999999999</v>
       </c>
       <c r="R4">
-        <v>0.311614</v>
+        <v>0.31063800000000003</v>
       </c>
       <c r="S4">
-        <v>0.241369</v>
+        <v>0.231409</v>
       </c>
       <c r="T4">
-        <v>7.9716999999999996E-2</v>
+        <v>7.2558999999999998E-2</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A5">
-        <v>0.44366100000000003</v>
+        <v>0.44196000000000002</v>
       </c>
       <c r="B5">
-        <v>0.44746200000000003</v>
+        <v>0.44484600000000002</v>
       </c>
       <c r="C5">
-        <v>0.44725999999999999</v>
+        <v>0.444131</v>
       </c>
       <c r="D5">
-        <v>0.44679799999999997</v>
+        <v>0.44399100000000002</v>
       </c>
       <c r="E5">
-        <v>0.45206600000000002</v>
+        <v>0.44622400000000001</v>
       </c>
       <c r="F5">
-        <v>0.45050299999999999</v>
+        <v>0.44449</v>
       </c>
       <c r="G5">
-        <v>0.44903599999999999</v>
+        <v>0.44190600000000002</v>
       </c>
       <c r="H5">
-        <v>0.44804300000000002</v>
+        <v>0.442158</v>
       </c>
       <c r="I5">
-        <v>0.44876199999999999</v>
+        <v>0.43962699999999999</v>
       </c>
       <c r="J5">
-        <v>0.44026100000000001</v>
+        <v>0.43240400000000001</v>
       </c>
       <c r="K5">
-        <v>0.43712499999999999</v>
+        <v>0.42953200000000002</v>
       </c>
       <c r="L5">
-        <v>0.43141600000000002</v>
+        <v>0.42582199999999998</v>
       </c>
       <c r="M5">
-        <v>0.41962699999999997</v>
+        <v>0.41591299999999998</v>
       </c>
       <c r="N5">
-        <v>0.41206900000000002</v>
+        <v>0.40692699999999998</v>
       </c>
       <c r="O5">
-        <v>0.42642600000000003</v>
+        <v>0.418599</v>
       </c>
       <c r="P5">
-        <v>0.414406</v>
+        <v>0.39935599999999999</v>
       </c>
       <c r="Q5">
-        <v>0.37554900000000002</v>
+        <v>0.365402</v>
       </c>
       <c r="R5">
-        <v>0.31253300000000001</v>
+        <v>0.31027300000000002</v>
       </c>
       <c r="S5">
-        <v>0.24063799999999999</v>
+        <v>0.23047100000000001</v>
       </c>
       <c r="T5">
-        <v>7.9716999999999996E-2</v>
+        <v>7.2558999999999998E-2</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A6">
-        <v>0.44535799999999998</v>
+        <v>0.44479999999999997</v>
       </c>
       <c r="B6">
-        <v>0.44951999999999998</v>
+        <v>0.44793300000000003</v>
       </c>
       <c r="C6">
-        <v>0.45014100000000001</v>
+        <v>0.44826100000000002</v>
       </c>
       <c r="D6">
-        <v>0.44951099999999999</v>
+        <v>0.44797500000000001</v>
       </c>
       <c r="E6">
-        <v>0.45451000000000003</v>
+        <v>0.450243</v>
       </c>
       <c r="F6">
-        <v>0.45334799999999997</v>
+        <v>0.44893899999999998</v>
       </c>
       <c r="G6">
-        <v>0.451903</v>
+        <v>0.445353</v>
       </c>
       <c r="H6">
-        <v>0.45040200000000002</v>
+        <v>0.44647799999999999</v>
       </c>
       <c r="I6">
-        <v>0.45126699999999997</v>
+        <v>0.44454199999999999</v>
       </c>
       <c r="J6">
-        <v>0.44349499999999997</v>
+        <v>0.43756</v>
       </c>
       <c r="K6">
-        <v>0.44033</v>
+        <v>0.43387599999999998</v>
       </c>
       <c r="L6">
-        <v>0.43573899999999999</v>
+        <v>0.43020199999999997</v>
       </c>
       <c r="M6">
-        <v>0.423898</v>
+        <v>0.41941099999999998</v>
       </c>
       <c r="N6">
-        <v>0.417348</v>
+        <v>0.411273</v>
       </c>
       <c r="O6">
-        <v>0.43061500000000003</v>
+        <v>0.42248200000000002</v>
       </c>
       <c r="P6">
-        <v>0.42242600000000002</v>
+        <v>0.40733200000000003</v>
       </c>
       <c r="Q6">
-        <v>0.38004399999999999</v>
+        <v>0.37260199999999999</v>
       </c>
       <c r="R6">
-        <v>0.31606299999999998</v>
+        <v>0.31408799999999998</v>
       </c>
       <c r="S6">
-        <v>0.244616</v>
+        <v>0.232906</v>
       </c>
       <c r="T6">
-        <v>7.9716999999999996E-2</v>
+        <v>7.2558999999999998E-2</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A7">
-        <v>0.44935900000000001</v>
+        <v>0.44725500000000001</v>
       </c>
       <c r="B7">
-        <v>0.45362799999999998</v>
+        <v>0.45068599999999998</v>
       </c>
       <c r="C7">
-        <v>0.45473799999999998</v>
+        <v>0.450631</v>
       </c>
       <c r="D7">
-        <v>0.455675</v>
+        <v>0.45139000000000001</v>
       </c>
       <c r="E7">
-        <v>0.46054299999999998</v>
+        <v>0.45383800000000002</v>
       </c>
       <c r="F7">
-        <v>0.459928</v>
+        <v>0.45248500000000003</v>
       </c>
       <c r="G7">
-        <v>0.45806400000000003</v>
+        <v>0.44900600000000002</v>
       </c>
       <c r="H7">
-        <v>0.45787899999999998</v>
+        <v>0.45105499999999998</v>
       </c>
       <c r="I7">
-        <v>0.458756</v>
+        <v>0.44939400000000002</v>
       </c>
       <c r="J7">
-        <v>0.45123099999999999</v>
+        <v>0.44275300000000001</v>
       </c>
       <c r="K7">
-        <v>0.448828</v>
+        <v>0.44004900000000002</v>
       </c>
       <c r="L7">
-        <v>0.44278600000000001</v>
+        <v>0.436054</v>
       </c>
       <c r="M7">
-        <v>0.43049399999999999</v>
+        <v>0.425562</v>
       </c>
       <c r="N7">
-        <v>0.42318099999999997</v>
+        <v>0.41537000000000002</v>
       </c>
       <c r="O7">
-        <v>0.43526199999999998</v>
+        <v>0.426568</v>
       </c>
       <c r="P7">
-        <v>0.42523300000000003</v>
+        <v>0.41191</v>
       </c>
       <c r="Q7">
-        <v>0.38187100000000002</v>
+        <v>0.37628499999999998</v>
       </c>
       <c r="R7">
-        <v>0.31686799999999998</v>
+        <v>0.31559599999999999</v>
       </c>
       <c r="S7">
-        <v>0.24409</v>
+        <v>0.23202400000000001</v>
       </c>
       <c r="T7">
-        <v>7.9528000000000001E-2</v>
+        <v>7.2394E-2</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A8">
-        <v>0.44983499999999998</v>
+        <v>0.44477499999999998</v>
       </c>
       <c r="B8">
-        <v>0.454627</v>
+        <v>0.44898199999999999</v>
       </c>
       <c r="C8">
-        <v>0.45556200000000002</v>
+        <v>0.449048</v>
       </c>
       <c r="D8">
-        <v>0.45590999999999998</v>
+        <v>0.449376</v>
       </c>
       <c r="E8">
-        <v>0.46057199999999998</v>
+        <v>0.45207399999999998</v>
       </c>
       <c r="F8">
-        <v>0.46013999999999999</v>
+        <v>0.45044000000000001</v>
       </c>
       <c r="G8">
-        <v>0.45771200000000001</v>
+        <v>0.44654100000000002</v>
       </c>
       <c r="H8">
-        <v>0.45842100000000002</v>
+        <v>0.448847</v>
       </c>
       <c r="I8">
-        <v>0.46021600000000001</v>
+        <v>0.44845800000000002</v>
       </c>
       <c r="J8">
-        <v>0.45072600000000002</v>
+        <v>0.44067400000000001</v>
       </c>
       <c r="K8">
-        <v>0.44868999999999998</v>
+        <v>0.43809100000000001</v>
       </c>
       <c r="L8">
-        <v>0.44101800000000002</v>
+        <v>0.43110799999999999</v>
       </c>
       <c r="M8">
-        <v>0.42931900000000001</v>
+        <v>0.42184100000000002</v>
       </c>
       <c r="N8">
-        <v>0.42183399999999999</v>
+        <v>0.411657</v>
       </c>
       <c r="O8">
-        <v>0.43685600000000002</v>
+        <v>0.426037</v>
       </c>
       <c r="P8">
-        <v>0.42828899999999998</v>
+        <v>0.41141800000000001</v>
       </c>
       <c r="Q8">
-        <v>0.38719100000000001</v>
+        <v>0.37803500000000001</v>
       </c>
       <c r="R8">
-        <v>0.32244499999999998</v>
+        <v>0.31767000000000001</v>
       </c>
       <c r="S8">
-        <v>0.24929799999999999</v>
+        <v>0.23480699999999999</v>
       </c>
       <c r="T8">
-        <v>7.9528000000000001E-2</v>
+        <v>7.2228000000000001E-2</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A9">
-        <v>0.44675599999999999</v>
+        <v>0.44209599999999999</v>
       </c>
       <c r="B9">
-        <v>0.45115300000000003</v>
+        <v>0.44637700000000002</v>
       </c>
       <c r="C9">
-        <v>0.452345</v>
+        <v>0.44669700000000001</v>
       </c>
       <c r="D9">
-        <v>0.45304800000000001</v>
+        <v>0.44701200000000002</v>
       </c>
       <c r="E9">
-        <v>0.457847</v>
+        <v>0.45004499999999997</v>
       </c>
       <c r="F9">
-        <v>0.45805400000000002</v>
+        <v>0.449299</v>
       </c>
       <c r="G9">
-        <v>0.45638899999999999</v>
+        <v>0.44611299999999998</v>
       </c>
       <c r="H9">
-        <v>0.45759300000000003</v>
+        <v>0.44831599999999999</v>
       </c>
       <c r="I9">
-        <v>0.460368</v>
+        <v>0.44894499999999998</v>
       </c>
       <c r="J9">
-        <v>0.45248899999999997</v>
+        <v>0.44197599999999998</v>
       </c>
       <c r="K9">
-        <v>0.45063999999999999</v>
+        <v>0.440446</v>
       </c>
       <c r="L9">
-        <v>0.442469</v>
+        <v>0.43242900000000001</v>
       </c>
       <c r="M9">
-        <v>0.42978699999999997</v>
+        <v>0.42171999999999998</v>
       </c>
       <c r="N9">
-        <v>0.420298</v>
+        <v>0.40898699999999999</v>
       </c>
       <c r="O9">
-        <v>0.43945899999999999</v>
+        <v>0.42757800000000001</v>
       </c>
       <c r="P9">
-        <v>0.42697099999999999</v>
+        <v>0.41108499999999998</v>
       </c>
       <c r="Q9">
-        <v>0.387878</v>
+        <v>0.382687</v>
       </c>
       <c r="R9">
-        <v>0.31884699999999999</v>
+        <v>0.32314300000000001</v>
       </c>
       <c r="S9">
-        <v>0.247811</v>
+        <v>0.24151600000000001</v>
       </c>
       <c r="T9">
-        <v>7.9528000000000001E-2</v>
+        <v>7.2062000000000001E-2</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A10">
-        <v>0.45084400000000002</v>
+        <v>0.44562800000000002</v>
       </c>
       <c r="B10">
-        <v>0.45491599999999999</v>
+        <v>0.45034800000000003</v>
       </c>
       <c r="C10">
-        <v>0.45727499999999999</v>
+        <v>0.45209700000000003</v>
       </c>
       <c r="D10">
-        <v>0.45891500000000002</v>
+        <v>0.4531</v>
       </c>
       <c r="E10">
-        <v>0.46494400000000002</v>
+        <v>0.45775500000000002</v>
       </c>
       <c r="F10">
-        <v>0.46553600000000001</v>
+        <v>0.45759100000000003</v>
       </c>
       <c r="G10">
-        <v>0.46395700000000001</v>
+        <v>0.45354899999999998</v>
       </c>
       <c r="H10">
-        <v>0.46359099999999998</v>
+        <v>0.45424999999999999</v>
       </c>
       <c r="I10">
-        <v>0.46624199999999999</v>
+        <v>0.455017</v>
       </c>
       <c r="J10">
-        <v>0.45994600000000002</v>
+        <v>0.44910099999999997</v>
       </c>
       <c r="K10">
-        <v>0.460401</v>
+        <v>0.45033000000000001</v>
       </c>
       <c r="L10">
-        <v>0.45324399999999998</v>
+        <v>0.443048</v>
       </c>
       <c r="M10">
-        <v>0.44258500000000001</v>
+        <v>0.433612</v>
       </c>
       <c r="N10">
-        <v>0.43371999999999999</v>
+        <v>0.421711</v>
       </c>
       <c r="O10">
-        <v>0.451322</v>
+        <v>0.43695699999999998</v>
       </c>
       <c r="P10">
-        <v>0.43176900000000001</v>
+        <v>0.41303899999999999</v>
       </c>
       <c r="Q10">
-        <v>0.39422800000000002</v>
+        <v>0.38519799999999998</v>
       </c>
       <c r="R10">
-        <v>0.326345</v>
+        <v>0.32679799999999998</v>
       </c>
       <c r="S10">
-        <v>0.257579</v>
+        <v>0.24773500000000001</v>
       </c>
       <c r="T10">
-        <v>7.9528000000000001E-2</v>
+        <v>7.2062000000000001E-2</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A11">
-        <v>0.44873800000000003</v>
+        <v>0.44437500000000002</v>
       </c>
       <c r="B11">
-        <v>0.451546</v>
+        <v>0.44757999999999998</v>
       </c>
       <c r="C11">
-        <v>0.45468799999999998</v>
+        <v>0.44961499999999999</v>
       </c>
       <c r="D11">
-        <v>0.45634200000000003</v>
+        <v>0.45116800000000001</v>
       </c>
       <c r="E11">
-        <v>0.46193299999999998</v>
+        <v>0.45555299999999999</v>
       </c>
       <c r="F11">
-        <v>0.46353699999999998</v>
+        <v>0.456345</v>
       </c>
       <c r="G11">
-        <v>0.46198299999999998</v>
+        <v>0.45269700000000002</v>
       </c>
       <c r="H11">
-        <v>0.46209600000000001</v>
+        <v>0.45223999999999998</v>
       </c>
       <c r="I11">
-        <v>0.46526699999999999</v>
+        <v>0.452872</v>
       </c>
       <c r="J11">
-        <v>0.46057700000000001</v>
+        <v>0.44913599999999998</v>
       </c>
       <c r="K11">
-        <v>0.46408300000000002</v>
+        <v>0.45246399999999998</v>
       </c>
       <c r="L11">
-        <v>0.45807900000000001</v>
+        <v>0.44655099999999998</v>
       </c>
       <c r="M11">
-        <v>0.44841900000000001</v>
+        <v>0.43745600000000001</v>
       </c>
       <c r="N11">
-        <v>0.43547999999999998</v>
+        <v>0.42330299999999998</v>
       </c>
       <c r="O11">
-        <v>0.44608599999999998</v>
+        <v>0.43117100000000003</v>
       </c>
       <c r="P11">
-        <v>0.42655399999999999</v>
+        <v>0.40874500000000002</v>
       </c>
       <c r="Q11">
-        <v>0.39493899999999998</v>
+        <v>0.38509399999999999</v>
       </c>
       <c r="R11">
-        <v>0.32586199999999999</v>
+        <v>0.32530300000000001</v>
       </c>
       <c r="S11">
-        <v>0.254915</v>
+        <v>0.24928</v>
       </c>
       <c r="T11">
-        <v>7.9528000000000001E-2</v>
+        <v>7.2062000000000001E-2</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A12">
-        <v>0.44529600000000003</v>
+        <v>0.43937399999999999</v>
       </c>
       <c r="B12">
-        <v>0.44919199999999998</v>
+        <v>0.44353999999999999</v>
       </c>
       <c r="C12">
-        <v>0.45253500000000002</v>
+        <v>0.445629</v>
       </c>
       <c r="D12">
-        <v>0.45401999999999998</v>
+        <v>0.44710699999999998</v>
       </c>
       <c r="E12">
-        <v>0.460839</v>
+        <v>0.45254</v>
       </c>
       <c r="F12">
-        <v>0.46172800000000003</v>
+        <v>0.45337300000000003</v>
       </c>
       <c r="G12">
-        <v>0.45868900000000001</v>
+        <v>0.44895800000000002</v>
       </c>
       <c r="H12">
-        <v>0.45728200000000002</v>
+        <v>0.448131</v>
       </c>
       <c r="I12">
-        <v>0.458866</v>
+        <v>0.44739099999999998</v>
       </c>
       <c r="J12">
-        <v>0.45297500000000002</v>
+        <v>0.44298700000000002</v>
       </c>
       <c r="K12">
-        <v>0.45780900000000002</v>
+        <v>0.44646000000000002</v>
       </c>
       <c r="L12">
-        <v>0.45292500000000002</v>
+        <v>0.44170100000000001</v>
       </c>
       <c r="M12">
-        <v>0.44263400000000003</v>
+        <v>0.43255100000000002</v>
       </c>
       <c r="N12">
-        <v>0.433471</v>
+        <v>0.42158499999999999</v>
       </c>
       <c r="O12">
-        <v>0.44608900000000001</v>
+        <v>0.43328</v>
       </c>
       <c r="P12">
-        <v>0.41981400000000002</v>
+        <v>0.40648000000000001</v>
       </c>
       <c r="Q12">
-        <v>0.38732</v>
+        <v>0.38312600000000002</v>
       </c>
       <c r="R12">
-        <v>0.32502599999999998</v>
+        <v>0.327542</v>
       </c>
       <c r="S12">
-        <v>0.25528299999999998</v>
+        <v>0.24765799999999999</v>
       </c>
       <c r="T12">
-        <v>7.9528000000000001E-2</v>
+        <v>7.2062000000000001E-2</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A13">
-        <v>0.45001799999999997</v>
+        <v>0.44309799999999999</v>
       </c>
       <c r="B13">
-        <v>0.455403</v>
+        <v>0.44870500000000002</v>
       </c>
       <c r="C13">
-        <v>0.45729799999999998</v>
+        <v>0.44951799999999997</v>
       </c>
       <c r="D13">
-        <v>0.45928600000000003</v>
+        <v>0.45154100000000003</v>
       </c>
       <c r="E13">
-        <v>0.46460899999999999</v>
+        <v>0.45577899999999999</v>
       </c>
       <c r="F13">
-        <v>0.46552199999999999</v>
+        <v>0.457567</v>
       </c>
       <c r="G13">
-        <v>0.46050799999999997</v>
+        <v>0.45186700000000002</v>
       </c>
       <c r="H13">
-        <v>0.460787</v>
+        <v>0.45281100000000002</v>
       </c>
       <c r="I13">
-        <v>0.463474</v>
+        <v>0.45379599999999998</v>
       </c>
       <c r="J13">
-        <v>0.45896199999999998</v>
+        <v>0.45073099999999999</v>
       </c>
       <c r="K13">
-        <v>0.46387099999999998</v>
+        <v>0.45643899999999998</v>
       </c>
       <c r="L13">
-        <v>0.45549499999999998</v>
+        <v>0.44738299999999998</v>
       </c>
       <c r="M13">
-        <v>0.44328499999999998</v>
+        <v>0.43407899999999999</v>
       </c>
       <c r="N13">
-        <v>0.43281599999999998</v>
+        <v>0.42093399999999997</v>
       </c>
       <c r="O13">
-        <v>0.444185</v>
+        <v>0.43434699999999998</v>
       </c>
       <c r="P13">
-        <v>0.41375499999999998</v>
+        <v>0.40041199999999999</v>
       </c>
       <c r="Q13">
-        <v>0.38113000000000002</v>
+        <v>0.379496</v>
       </c>
       <c r="R13">
-        <v>0.31672899999999998</v>
+        <v>0.32291799999999998</v>
       </c>
       <c r="S13">
-        <v>0.24626999999999999</v>
+        <v>0.24279000000000001</v>
       </c>
       <c r="T13">
-        <v>7.9031000000000004E-2</v>
+        <v>7.1626999999999996E-2</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A14">
-        <v>0.44212499999999999</v>
+        <v>0.43640200000000001</v>
       </c>
       <c r="B14">
-        <v>0.44818999999999998</v>
+        <v>0.442639</v>
       </c>
       <c r="C14">
-        <v>0.45055000000000001</v>
+        <v>0.44415100000000002</v>
       </c>
       <c r="D14">
-        <v>0.45228400000000002</v>
+        <v>0.44673400000000002</v>
       </c>
       <c r="E14">
-        <v>0.45849099999999998</v>
+        <v>0.45172699999999999</v>
       </c>
       <c r="F14">
-        <v>0.46153</v>
+        <v>0.454538</v>
       </c>
       <c r="G14">
-        <v>0.45915600000000001</v>
+        <v>0.45167400000000002</v>
       </c>
       <c r="H14">
-        <v>0.46333600000000003</v>
+        <v>0.45643400000000001</v>
       </c>
       <c r="I14">
-        <v>0.46842800000000001</v>
+        <v>0.45959800000000001</v>
       </c>
       <c r="J14">
-        <v>0.464528</v>
+        <v>0.45871899999999999</v>
       </c>
       <c r="K14">
-        <v>0.46947299999999997</v>
+        <v>0.464196</v>
       </c>
       <c r="L14">
-        <v>0.45814199999999999</v>
+        <v>0.45405600000000002</v>
       </c>
       <c r="M14">
-        <v>0.44790999999999997</v>
+        <v>0.442633</v>
       </c>
       <c r="N14">
-        <v>0.431973</v>
+        <v>0.424483</v>
       </c>
       <c r="O14">
-        <v>0.44339899999999999</v>
+        <v>0.434002</v>
       </c>
       <c r="P14">
-        <v>0.41406300000000001</v>
+        <v>0.40223500000000001</v>
       </c>
       <c r="Q14">
-        <v>0.377942</v>
+        <v>0.37257800000000002</v>
       </c>
       <c r="R14">
-        <v>0.31298300000000001</v>
+        <v>0.31498100000000001</v>
       </c>
       <c r="S14">
-        <v>0.23347799999999999</v>
+        <v>0.228549</v>
       </c>
       <c r="T14">
-        <v>7.8840999999999994E-2</v>
+        <v>7.1460999999999997E-2</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A15">
-        <v>0.43036600000000003</v>
+        <v>0.42523100000000003</v>
       </c>
       <c r="B15">
-        <v>0.43709700000000001</v>
+        <v>0.43305900000000003</v>
       </c>
       <c r="C15">
-        <v>0.440251</v>
+        <v>0.43595699999999998</v>
       </c>
       <c r="D15">
-        <v>0.44545600000000002</v>
+        <v>0.44159500000000002</v>
       </c>
       <c r="E15">
-        <v>0.452982</v>
+        <v>0.44847500000000001</v>
       </c>
       <c r="F15">
-        <v>0.45541199999999998</v>
+        <v>0.449374</v>
       </c>
       <c r="G15">
-        <v>0.45325199999999999</v>
+        <v>0.44739800000000002</v>
       </c>
       <c r="H15">
-        <v>0.45651599999999998</v>
+        <v>0.45149299999999998</v>
       </c>
       <c r="I15">
-        <v>0.46271499999999999</v>
+        <v>0.45532499999999998</v>
       </c>
       <c r="J15">
-        <v>0.45451799999999998</v>
+        <v>0.45096399999999998</v>
       </c>
       <c r="K15">
-        <v>0.45841900000000002</v>
+        <v>0.45588299999999998</v>
       </c>
       <c r="L15">
-        <v>0.45013999999999998</v>
+        <v>0.44821499999999997</v>
       </c>
       <c r="M15">
-        <v>0.44418099999999999</v>
+        <v>0.44199899999999998</v>
       </c>
       <c r="N15">
-        <v>0.43244500000000002</v>
+        <v>0.42853999999999998</v>
       </c>
       <c r="O15">
-        <v>0.45878099999999999</v>
+        <v>0.44467499999999999</v>
       </c>
       <c r="P15">
-        <v>0.42834100000000003</v>
+        <v>0.410134</v>
       </c>
       <c r="Q15">
-        <v>0.37821500000000002</v>
+        <v>0.37035000000000001</v>
       </c>
       <c r="R15">
-        <v>0.32070300000000002</v>
+        <v>0.31517099999999998</v>
       </c>
       <c r="S15">
-        <v>0.227685</v>
+        <v>0.21908</v>
       </c>
       <c r="T15">
-        <v>7.7588000000000004E-2</v>
+        <v>7.0198999999999998E-2</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A16">
-        <v>0.41175800000000001</v>
+        <v>0.41032999999999997</v>
       </c>
       <c r="B16">
-        <v>0.41640700000000003</v>
+        <v>0.41537099999999999</v>
       </c>
       <c r="C16">
-        <v>0.415769</v>
+        <v>0.41552899999999998</v>
       </c>
       <c r="D16">
-        <v>0.42407400000000001</v>
+        <v>0.42399100000000001</v>
       </c>
       <c r="E16">
-        <v>0.43427900000000003</v>
+        <v>0.43287900000000001</v>
       </c>
       <c r="F16">
-        <v>0.44014900000000001</v>
+        <v>0.43740099999999998</v>
       </c>
       <c r="G16">
-        <v>0.44012099999999998</v>
+        <v>0.43630999999999998</v>
       </c>
       <c r="H16">
-        <v>0.44389699999999999</v>
+        <v>0.44261499999999998</v>
       </c>
       <c r="I16">
-        <v>0.44891399999999998</v>
+        <v>0.446266</v>
       </c>
       <c r="J16">
-        <v>0.44139899999999999</v>
+        <v>0.44036399999999998</v>
       </c>
       <c r="K16">
-        <v>0.44465100000000002</v>
+        <v>0.44185999999999998</v>
       </c>
       <c r="L16">
-        <v>0.43782199999999999</v>
+        <v>0.43655899999999997</v>
       </c>
       <c r="M16">
-        <v>0.436143</v>
+        <v>0.43297099999999999</v>
       </c>
       <c r="N16">
-        <v>0.42306700000000003</v>
+        <v>0.41865200000000002</v>
       </c>
       <c r="O16">
-        <v>0.44218400000000002</v>
+        <v>0.43040800000000001</v>
       </c>
       <c r="P16">
-        <v>0.40110000000000001</v>
+        <v>0.38856000000000002</v>
       </c>
       <c r="Q16">
-        <v>0.36058000000000001</v>
+        <v>0.35796899999999998</v>
       </c>
       <c r="R16">
-        <v>0.29842000000000002</v>
+        <v>0.29776599999999998</v>
       </c>
       <c r="S16">
-        <v>0.211397</v>
+        <v>0.205207</v>
       </c>
       <c r="T16">
-        <v>8.8363999999999998E-2</v>
+        <v>9.1758000000000006E-2</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A17">
-        <v>0.376695</v>
+        <v>0.37710900000000003</v>
       </c>
       <c r="B17">
-        <v>0.38206099999999998</v>
+        <v>0.38186900000000001</v>
       </c>
       <c r="C17">
-        <v>0.38258199999999998</v>
+        <v>0.38201600000000002</v>
       </c>
       <c r="D17">
-        <v>0.38894699999999999</v>
+        <v>0.38739000000000001</v>
       </c>
       <c r="E17">
-        <v>0.40315699999999999</v>
+        <v>0.40027499999999999</v>
       </c>
       <c r="F17">
-        <v>0.404333</v>
+        <v>0.400669</v>
       </c>
       <c r="G17">
-        <v>0.40135700000000002</v>
+        <v>0.39709299999999997</v>
       </c>
       <c r="H17">
-        <v>0.401696</v>
+        <v>0.39938800000000002</v>
       </c>
       <c r="I17">
-        <v>0.41095700000000002</v>
+        <v>0.40744900000000001</v>
       </c>
       <c r="J17">
-        <v>0.40226600000000001</v>
+        <v>0.40168999999999999</v>
       </c>
       <c r="K17">
-        <v>0.40166299999999999</v>
+        <v>0.40042299999999997</v>
       </c>
       <c r="L17">
-        <v>0.39801500000000001</v>
+        <v>0.39597500000000002</v>
       </c>
       <c r="M17">
-        <v>0.40685900000000003</v>
+        <v>0.40269199999999999</v>
       </c>
       <c r="N17">
-        <v>0.395681</v>
+        <v>0.39049</v>
       </c>
       <c r="O17">
-        <v>0.42150700000000002</v>
+        <v>0.41084300000000001</v>
       </c>
       <c r="P17">
-        <v>0.39206600000000003</v>
+        <v>0.37989699999999998</v>
       </c>
       <c r="Q17">
-        <v>0.33843600000000001</v>
+        <v>0.33223200000000003</v>
       </c>
       <c r="R17">
-        <v>0.28212900000000002</v>
+        <v>0.28109200000000001</v>
       </c>
       <c r="S17">
-        <v>0.18613399999999999</v>
+        <v>0.18310599999999999</v>
       </c>
       <c r="T17">
-        <v>0.108752</v>
+        <v>0.112627</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A18">
-        <v>0.317776</v>
+        <v>0.31618600000000002</v>
       </c>
       <c r="B18">
-        <v>0.32280999999999999</v>
+        <v>0.32075999999999999</v>
       </c>
       <c r="C18">
-        <v>0.32467000000000001</v>
+        <v>0.32212200000000002</v>
       </c>
       <c r="D18">
-        <v>0.32998300000000003</v>
+        <v>0.32667000000000002</v>
       </c>
       <c r="E18">
-        <v>0.33201999999999998</v>
+        <v>0.32833299999999999</v>
       </c>
       <c r="F18">
-        <v>0.32872299999999999</v>
+        <v>0.32483099999999998</v>
       </c>
       <c r="G18">
-        <v>0.32746399999999998</v>
+        <v>0.32332100000000003</v>
       </c>
       <c r="H18">
-        <v>0.323409</v>
+        <v>0.31921699999999997</v>
       </c>
       <c r="I18">
-        <v>0.350796</v>
+        <v>0.34433399999999997</v>
       </c>
       <c r="J18">
-        <v>0.34686400000000001</v>
+        <v>0.34531600000000001</v>
       </c>
       <c r="K18">
-        <v>0.35871399999999998</v>
+        <v>0.35638799999999998</v>
       </c>
       <c r="L18">
-        <v>0.35766399999999998</v>
+        <v>0.35469400000000001</v>
       </c>
       <c r="M18">
-        <v>0.38529799999999997</v>
+        <v>0.379913</v>
       </c>
       <c r="N18">
-        <v>0.37160799999999999</v>
+        <v>0.36578100000000002</v>
       </c>
       <c r="O18">
-        <v>0.38460299999999997</v>
+        <v>0.37571599999999999</v>
       </c>
       <c r="P18">
-        <v>0.35555900000000001</v>
+        <v>0.346329</v>
       </c>
       <c r="Q18">
-        <v>0.31336900000000001</v>
+        <v>0.30437399999999998</v>
       </c>
       <c r="R18">
-        <v>0.25294100000000003</v>
+        <v>0.25575599999999998</v>
       </c>
       <c r="S18">
-        <v>0.16467899999999999</v>
+        <v>0.16641300000000001</v>
       </c>
       <c r="T18">
-        <v>8.2452999999999999E-2</v>
+        <v>8.3711999999999995E-2</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A19">
-        <v>0.24873799999999999</v>
+        <v>0.249446</v>
       </c>
       <c r="B19">
-        <v>0.25570100000000001</v>
+        <v>0.25643500000000002</v>
       </c>
       <c r="C19">
-        <v>0.263015</v>
+        <v>0.26377699999999998</v>
       </c>
       <c r="D19">
-        <v>0.28496500000000002</v>
+        <v>0.28579500000000002</v>
       </c>
       <c r="E19">
-        <v>0.28128199999999998</v>
+        <v>0.28211199999999997</v>
       </c>
       <c r="F19">
-        <v>0.27554299999999998</v>
+        <v>0.27627099999999999</v>
       </c>
       <c r="G19">
-        <v>0.27274700000000002</v>
+        <v>0.273476</v>
       </c>
       <c r="H19">
-        <v>0.26564700000000002</v>
+        <v>0.26637699999999997</v>
       </c>
       <c r="I19">
-        <v>0.30924600000000002</v>
+        <v>0.31010799999999999</v>
       </c>
       <c r="J19">
-        <v>0.30218600000000001</v>
+        <v>0.30305100000000001</v>
       </c>
       <c r="K19">
-        <v>0.29321900000000001</v>
+        <v>0.29408699999999999</v>
       </c>
       <c r="L19">
-        <v>0.30357400000000001</v>
+        <v>0.30451</v>
       </c>
       <c r="M19">
-        <v>0.29095500000000002</v>
+        <v>0.29189599999999999</v>
       </c>
       <c r="N19">
-        <v>0.27385799999999999</v>
+        <v>0.27480599999999999</v>
       </c>
       <c r="O19">
-        <v>0.28197100000000003</v>
+        <v>0.28271499999999999</v>
       </c>
       <c r="P19">
-        <v>0.25932100000000002</v>
+        <v>0.260073</v>
       </c>
       <c r="Q19">
-        <v>0.22481300000000001</v>
+        <v>0.225577</v>
       </c>
       <c r="R19">
-        <v>0.19678399999999999</v>
+        <v>0.19749</v>
       </c>
       <c r="S19">
-        <v>0.144984</v>
+        <v>0.14585699999999999</v>
       </c>
       <c r="T19">
-        <v>4.4933000000000001E-2</v>
+        <v>4.6240000000000003E-2</v>
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.45">
